--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -12,7 +12,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CO$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -21,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -37,6 +38,11 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,11 +73,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -135,61 +136,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,6 +198,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -272,6 +297,108 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO15" headerRowCount="1">
+  <autoFilter ref="A1:CO15"/>
+  <tableColumns count="93">
+    <tableColumn id="1" name="pick_id"/>
+    <tableColumn id="2" name="created_at_utc"/>
+    <tableColumn id="3" name="event_start_utc"/>
+    <tableColumn id="4" name="event_id"/>
+    <tableColumn id="5" name="league"/>
+    <tableColumn id="6" name="away_team"/>
+    <tableColumn id="7" name="home_team"/>
+    <tableColumn id="8" name="market_type"/>
+    <tableColumn id="9" name="selection"/>
+    <tableColumn id="10" name="line"/>
+    <tableColumn id="11" name="sportsbook"/>
+    <tableColumn id="12" name="american_odds"/>
+    <tableColumn id="13" name="decimal_odds"/>
+    <tableColumn id="14" name="market_implied_probability"/>
+    <tableColumn id="15" name="model_probability"/>
+    <tableColumn id="16" name="model_uncertainty"/>
+    <tableColumn id="17" name="edge"/>
+    <tableColumn id="18" name="confidence_score"/>
+    <tableColumn id="19" name="units"/>
+    <tableColumn id="20" name="model_version"/>
+    <tableColumn id="21" name="status"/>
+    <tableColumn id="22" name="result"/>
+    <tableColumn id="23" name="away_score"/>
+    <tableColumn id="24" name="home_score"/>
+    <tableColumn id="25" name="closing_line"/>
+    <tableColumn id="26" name="closing_american_odds"/>
+    <tableColumn id="27" name="closing_implied_probability"/>
+    <tableColumn id="28" name="probability_clv"/>
+    <tableColumn id="29" name="pnl_units"/>
+    <tableColumn id="30" name="settled_at_utc"/>
+    <tableColumn id="31" name="rationale"/>
+    <tableColumn id="32" name="risks"/>
+    <tableColumn id="33" name="review_status"/>
+    <tableColumn id="34" name="loss_classification"/>
+    <tableColumn id="35" name="loss_cause"/>
+    <tableColumn id="36" name="corrective_action"/>
+    <tableColumn id="37" name="call_type"/>
+    <tableColumn id="38" name="ledger_schema_version"/>
+    <tableColumn id="39" name="record_type"/>
+    <tableColumn id="40" name="decision"/>
+    <tableColumn id="41" name="reason_code"/>
+    <tableColumn id="42" name="canonical_away_team_id"/>
+    <tableColumn id="43" name="canonical_away_team_name"/>
+    <tableColumn id="44" name="original_away_team"/>
+    <tableColumn id="45" name="canonical_home_team_id"/>
+    <tableColumn id="46" name="canonical_home_team_name"/>
+    <tableColumn id="47" name="original_home_team"/>
+    <tableColumn id="48" name="banned_team_id"/>
+    <tableColumn id="49" name="banned_team_name"/>
+    <tableColumn id="50" name="model_origin"/>
+    <tableColumn id="51" name="baseline_identifier"/>
+    <tableColumn id="52" name="model_state_at_decision"/>
+    <tableColumn id="53" name="model_artifact_hash"/>
+    <tableColumn id="54" name="calibration_method"/>
+    <tableColumn id="55" name="calibration_version"/>
+    <tableColumn id="56" name="calibration_artifact_hash"/>
+    <tableColumn id="57" name="feature_schema_version"/>
+    <tableColumn id="58" name="entity_map_version"/>
+    <tableColumn id="59" name="code_revision"/>
+    <tableColumn id="60" name="observed_at_utc"/>
+    <tableColumn id="61" name="correlation_tags"/>
+    <tableColumn id="62" name="decision_line"/>
+    <tableColumn id="63" name="decision_american_odds"/>
+    <tableColumn id="64" name="decision_decimal_odds"/>
+    <tableColumn id="65" name="decision_raw_implied_probability"/>
+    <tableColumn id="66" name="decision_no_vig_probability"/>
+    <tableColumn id="67" name="decision_consensus_probability"/>
+    <tableColumn id="68" name="decision_consensus_line"/>
+    <tableColumn id="69" name="closing_decimal_odds"/>
+    <tableColumn id="70" name="closing_raw_implied_probability"/>
+    <tableColumn id="71" name="closing_no_vig_probability"/>
+    <tableColumn id="72" name="closing_consensus_probability"/>
+    <tableColumn id="73" name="closing_consensus_line"/>
+    <tableColumn id="74" name="legacy_units"/>
+    <tableColumn id="75" name="void_reason"/>
+    <tableColumn id="76" name="research_score_units"/>
+    <tableColumn id="77" name="research_pnl_units"/>
+    <tableColumn id="78" name="research_scored_at_utc"/>
+    <tableColumn id="79" name="research_scoring_note"/>
+    <tableColumn id="80" name="migrated_from_version"/>
+    <tableColumn id="81" name="elo_probability"/>
+    <tableColumn id="82" name="trend_gap"/>
+    <tableColumn id="83" name="park_factor"/>
+    <tableColumn id="84" name="weather_factor"/>
+    <tableColumn id="85" name="pitcher_era_gap"/>
+    <tableColumn id="86" name="probable_starter_era_gap"/>
+    <tableColumn id="87" name="unavailable_features"/>
+    <tableColumn id="88" name="defensive_trend_gap"/>
+    <tableColumn id="89" name="neutral_elo_rating_difference"/>
+    <tableColumn id="90" name="rest_disparity"/>
+    <tableColumn id="91" name="back_to_back_gap"/>
+    <tableColumn id="92" name="games_last_7_gap"/>
+    <tableColumn id="93" name="schedule_missingness"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -625,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$2)</f>
+        <f>COUNTA('Picks'!$A$2:$A$15)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -665,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$2,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")/(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$2)/SUM('Picks'!$BX$2:$BX$2),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
         <v/>
       </c>
     </row>
@@ -705,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$2)</f>
+        <f>SUM('Picks'!$BY$2:$BY$15)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$2,"&lt;&gt;",'Picks'!$AB$2:$AB$2),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$2,'Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -772,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -788,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -803,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -819,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -834,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -850,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -883,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO1"/>
+  <dimension ref="A1:CO15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1448,9 +1575,3735 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>873d2a5526b04b7d</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:27:42.175744Z</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>62511</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="n"/>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M2" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N2" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O2" s="28" t="n">
+        <v>0.521452</v>
+      </c>
+      <c r="P2" s="28" t="n"/>
+      <c r="Q2" s="28" t="n">
+        <v>-0.05838</v>
+      </c>
+      <c r="R2" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U2" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="25" t="n"/>
+      <c r="Z2" s="26" t="n"/>
+      <c r="AA2" s="28" t="n"/>
+      <c r="AB2" s="28" t="n"/>
+      <c r="AC2" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:09:07.565768Z</t>
+        </is>
+      </c>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-stx-nemiga-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG2" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH2" s="24" t="n"/>
+      <c r="AI2" s="31" t="n"/>
+      <c r="AJ2" s="31" t="n"/>
+      <c r="AK2" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN2" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO2" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP2" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AQ2" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AR2" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AS2" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AT2" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AU2" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AV2" s="24" t="n"/>
+      <c r="AW2" s="24" t="n"/>
+      <c r="AX2" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY2" s="24" t="n"/>
+      <c r="AZ2" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA2" s="24" t="inlineStr">
+        <is>
+          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
+        </is>
+      </c>
+      <c r="BB2" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC2" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD2" s="24" t="inlineStr">
+        <is>
+          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
+        </is>
+      </c>
+      <c r="BE2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG2" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:27:35.450448Z</t>
+        </is>
+      </c>
+      <c r="BI2" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ2" s="25" t="n"/>
+      <c r="BK2" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL2" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM2" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN2" s="28" t="n"/>
+      <c r="BO2" s="28" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
+      <c r="BR2" s="28" t="n"/>
+      <c r="BS2" s="28" t="n"/>
+      <c r="BT2" s="28" t="n"/>
+      <c r="BU2" s="25" t="n"/>
+      <c r="BV2" s="29" t="n"/>
+      <c r="BW2" s="24" t="n"/>
+      <c r="BX2" s="30" t="n"/>
+      <c r="BY2" s="27" t="n"/>
+      <c r="BZ2" s="24" t="n"/>
+      <c r="CA2" s="31" t="n"/>
+      <c r="CB2" s="24" t="n"/>
+      <c r="CC2" s="24" t="n"/>
+      <c r="CD2" s="24" t="n"/>
+      <c r="CE2" s="24" t="n"/>
+      <c r="CF2" s="24" t="n"/>
+      <c r="CG2" s="24" t="n"/>
+      <c r="CH2" s="24" t="n"/>
+      <c r="CI2" s="24" t="n"/>
+      <c r="CJ2" s="24" t="n"/>
+      <c r="CK2" s="24" t="n"/>
+      <c r="CL2" s="24" t="n"/>
+      <c r="CM2" s="24" t="n"/>
+      <c r="CN2" s="24" t="n"/>
+      <c r="CO2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>796e62e9750d41fc</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:27:42.175744Z</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>63054</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>Daxak Team</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>YBN Team</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L3" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M3" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N3" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O3" s="28" t="n">
+        <v>0.521452</v>
+      </c>
+      <c r="P3" s="28" t="n"/>
+      <c r="Q3" s="28" t="n">
+        <v>-0.05838</v>
+      </c>
+      <c r="R3" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U3" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="26" t="n"/>
+      <c r="AA3" s="28" t="n"/>
+      <c r="AB3" s="28" t="n"/>
+      <c r="AC3" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:09:08.721581Z</t>
+        </is>
+      </c>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-ybn-dxk-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG3" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH3" s="24" t="n"/>
+      <c r="AI3" s="31" t="n"/>
+      <c r="AJ3" s="31" t="n"/>
+      <c r="AK3" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN3" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO3" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP3" s="24" t="inlineStr">
+        <is>
+          <t>Daxak Team</t>
+        </is>
+      </c>
+      <c r="AQ3" s="24" t="inlineStr">
+        <is>
+          <t>Daxak Team</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
+          <t>Daxak Team</t>
+        </is>
+      </c>
+      <c r="AS3" s="24" t="inlineStr">
+        <is>
+          <t>YBN Team</t>
+        </is>
+      </c>
+      <c r="AT3" s="24" t="inlineStr">
+        <is>
+          <t>YBN Team</t>
+        </is>
+      </c>
+      <c r="AU3" s="24" t="inlineStr">
+        <is>
+          <t>YBN Team</t>
+        </is>
+      </c>
+      <c r="AV3" s="24" t="n"/>
+      <c r="AW3" s="24" t="n"/>
+      <c r="AX3" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY3" s="24" t="n"/>
+      <c r="AZ3" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA3" s="24" t="inlineStr">
+        <is>
+          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
+        </is>
+      </c>
+      <c r="BB3" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC3" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD3" s="24" t="inlineStr">
+        <is>
+          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
+        </is>
+      </c>
+      <c r="BE3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG3" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:27:35.968074Z</t>
+        </is>
+      </c>
+      <c r="BI3" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ3" s="25" t="n"/>
+      <c r="BK3" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL3" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM3" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN3" s="28" t="n"/>
+      <c r="BO3" s="28" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
+      <c r="BR3" s="28" t="n"/>
+      <c r="BS3" s="28" t="n"/>
+      <c r="BT3" s="28" t="n"/>
+      <c r="BU3" s="25" t="n"/>
+      <c r="BV3" s="29" t="n"/>
+      <c r="BW3" s="24" t="n"/>
+      <c r="BX3" s="30" t="n"/>
+      <c r="BY3" s="27" t="n"/>
+      <c r="BZ3" s="24" t="n"/>
+      <c r="CA3" s="31" t="n"/>
+      <c r="CB3" s="24" t="n"/>
+      <c r="CC3" s="24" t="n"/>
+      <c r="CD3" s="24" t="n"/>
+      <c r="CE3" s="24" t="n"/>
+      <c r="CF3" s="24" t="n"/>
+      <c r="CG3" s="24" t="n"/>
+      <c r="CH3" s="24" t="n"/>
+      <c r="CI3" s="24" t="n"/>
+      <c r="CJ3" s="24" t="n"/>
+      <c r="CK3" s="24" t="n"/>
+      <c r="CL3" s="24" t="n"/>
+      <c r="CM3" s="24" t="n"/>
+      <c r="CN3" s="24" t="n"/>
+      <c r="CO3" s="24" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>fcf7c3af1eca4efd</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:32:02.513705Z</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>63055</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Rostik Team</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I4" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L4" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="M4" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N4" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="O4" s="28" t="n">
+        <v>0.523739</v>
+      </c>
+      <c r="P4" s="28" t="n"/>
+      <c r="Q4" s="28" t="n">
+        <v>0.164027</v>
+      </c>
+      <c r="R4" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S4" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U4" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W4" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="26" t="n"/>
+      <c r="AA4" s="28" t="n"/>
+      <c r="AB4" s="28" t="n"/>
+      <c r="AC4" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:47:21.041247Z</t>
+        </is>
+      </c>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-dota2-ns-rt-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG4" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH4" s="24" t="n"/>
+      <c r="AI4" s="31" t="n"/>
+      <c r="AJ4" s="31" t="n"/>
+      <c r="AK4" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN4" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO4" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP4" s="24" t="inlineStr">
+        <is>
+          <t>Rostik Team</t>
+        </is>
+      </c>
+      <c r="AQ4" s="24" t="inlineStr">
+        <is>
+          <t>Rostik Team</t>
+        </is>
+      </c>
+      <c r="AR4" s="24" t="inlineStr">
+        <is>
+          <t>Rostik Team</t>
+        </is>
+      </c>
+      <c r="AS4" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="AT4" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="AU4" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="AV4" s="24" t="n"/>
+      <c r="AW4" s="24" t="n"/>
+      <c r="AX4" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY4" s="24" t="n"/>
+      <c r="AZ4" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA4" s="24" t="inlineStr">
+        <is>
+          <t>364cc42b22c3dca8b67013f8d5f39ea2a25268e5ee37712a8f8745913632a7c2</t>
+        </is>
+      </c>
+      <c r="BB4" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC4" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD4" s="24" t="inlineStr">
+        <is>
+          <t>364cc42b22c3dca8b67013f8d5f39ea2a25268e5ee37712a8f8745913632a7c2</t>
+        </is>
+      </c>
+      <c r="BE4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG4" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:31:56.327646Z</t>
+        </is>
+      </c>
+      <c r="BI4" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ4" s="25" t="n"/>
+      <c r="BK4" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL4" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BM4" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="BN4" s="28" t="n"/>
+      <c r="BO4" s="28" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
+      <c r="BR4" s="28" t="n"/>
+      <c r="BS4" s="28" t="n"/>
+      <c r="BT4" s="28" t="n"/>
+      <c r="BU4" s="25" t="n"/>
+      <c r="BV4" s="29" t="n"/>
+      <c r="BW4" s="24" t="n"/>
+      <c r="BX4" s="30" t="n"/>
+      <c r="BY4" s="27" t="n"/>
+      <c r="BZ4" s="24" t="n"/>
+      <c r="CA4" s="31" t="n"/>
+      <c r="CB4" s="24" t="n"/>
+      <c r="CC4" s="24" t="n"/>
+      <c r="CD4" s="24" t="n"/>
+      <c r="CE4" s="24" t="n"/>
+      <c r="CF4" s="24" t="n"/>
+      <c r="CG4" s="24" t="n"/>
+      <c r="CH4" s="24" t="n"/>
+      <c r="CI4" s="24" t="n"/>
+      <c r="CJ4" s="24" t="n"/>
+      <c r="CK4" s="24" t="n"/>
+      <c r="CL4" s="24" t="n"/>
+      <c r="CM4" s="24" t="n"/>
+      <c r="CN4" s="24" t="n"/>
+      <c r="CO4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>a9b7e6562dec4458</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:32:02.513705Z</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>62512</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L5" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N5" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O5" s="28" t="n">
+        <v>0.523739</v>
+      </c>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="28" t="n">
+        <v>0.103571</v>
+      </c>
+      <c r="R5" s="26" t="n">
+        <v>72</v>
+      </c>
+      <c r="S5" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U5" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="n"/>
+      <c r="W5" s="26" t="n"/>
+      <c r="X5" s="26" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="26" t="n"/>
+      <c r="AA5" s="28" t="n"/>
+      <c r="AB5" s="28" t="n"/>
+      <c r="AC5" s="30" t="n"/>
+      <c r="AD5" s="24" t="n"/>
+      <c r="AE5" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-dota2-tje-ill-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF5" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG5" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH5" s="24" t="n"/>
+      <c r="AI5" s="31" t="n"/>
+      <c r="AJ5" s="31" t="n"/>
+      <c r="AK5" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN5" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO5" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP5" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AQ5" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AR5" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AS5" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AT5" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AU5" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AV5" s="24" t="n"/>
+      <c r="AW5" s="24" t="n"/>
+      <c r="AX5" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY5" s="24" t="n"/>
+      <c r="AZ5" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA5" s="24" t="inlineStr">
+        <is>
+          <t>364cc42b22c3dca8b67013f8d5f39ea2a25268e5ee37712a8f8745913632a7c2</t>
+        </is>
+      </c>
+      <c r="BB5" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC5" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD5" s="24" t="inlineStr">
+        <is>
+          <t>364cc42b22c3dca8b67013f8d5f39ea2a25268e5ee37712a8f8745913632a7c2</t>
+        </is>
+      </c>
+      <c r="BE5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG5" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:31:56.921798Z</t>
+        </is>
+      </c>
+      <c r="BI5" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ5" s="25" t="n"/>
+      <c r="BK5" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL5" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM5" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN5" s="28" t="n"/>
+      <c r="BO5" s="28" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
+      <c r="BR5" s="28" t="n"/>
+      <c r="BS5" s="28" t="n"/>
+      <c r="BT5" s="28" t="n"/>
+      <c r="BU5" s="25" t="n"/>
+      <c r="BV5" s="29" t="n"/>
+      <c r="BW5" s="24" t="n"/>
+      <c r="BX5" s="30" t="n"/>
+      <c r="BY5" s="27" t="n"/>
+      <c r="BZ5" s="24" t="n"/>
+      <c r="CA5" s="31" t="n"/>
+      <c r="CB5" s="24" t="n"/>
+      <c r="CC5" s="24" t="n"/>
+      <c r="CD5" s="24" t="n"/>
+      <c r="CE5" s="24" t="n"/>
+      <c r="CF5" s="24" t="n"/>
+      <c r="CG5" s="24" t="n"/>
+      <c r="CH5" s="24" t="n"/>
+      <c r="CI5" s="24" t="n"/>
+      <c r="CJ5" s="24" t="n"/>
+      <c r="CK5" s="24" t="n"/>
+      <c r="CL5" s="24" t="n"/>
+      <c r="CM5" s="24" t="n"/>
+      <c r="CN5" s="24" t="n"/>
+      <c r="CO5" s="24" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>584074ed11fa4131</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:38:19.923501Z</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>62513</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O6" s="28" t="n">
+        <v>0.643378</v>
+      </c>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="28" t="n">
+        <v>0.09382799999999999</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <v>67</v>
+      </c>
+      <c r="S6" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U6" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n"/>
+      <c r="X6" s="26" t="n"/>
+      <c r="Y6" s="25" t="n"/>
+      <c r="Z6" s="26" t="n"/>
+      <c r="AA6" s="28" t="n"/>
+      <c r="AB6" s="28" t="n"/>
+      <c r="AC6" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:57:07.091830Z</t>
+        </is>
+      </c>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-dota2-bald-kw-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG6" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH6" s="24" t="n"/>
+      <c r="AI6" s="31" t="n"/>
+      <c r="AJ6" s="31" t="n"/>
+      <c r="AK6" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN6" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP6" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="AQ6" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="AR6" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="AS6" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AT6" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AU6" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AV6" s="24" t="n"/>
+      <c r="AW6" s="24" t="n"/>
+      <c r="AX6" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY6" s="24" t="n"/>
+      <c r="AZ6" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA6" s="24" t="inlineStr">
+        <is>
+          <t>713355eeac1c7f851a8fe35e939969377fe0747dd60b1ddb9f28fd4faae96635</t>
+        </is>
+      </c>
+      <c r="BB6" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC6" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD6" s="24" t="inlineStr">
+        <is>
+          <t>713355eeac1c7f851a8fe35e939969377fe0747dd60b1ddb9f28fd4faae96635</t>
+        </is>
+      </c>
+      <c r="BE6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG6" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:38:14.567529Z</t>
+        </is>
+      </c>
+      <c r="BI6" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ6" s="25" t="n"/>
+      <c r="BK6" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL6" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM6" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN6" s="28" t="n"/>
+      <c r="BO6" s="28" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
+      <c r="BR6" s="28" t="n"/>
+      <c r="BS6" s="28" t="n"/>
+      <c r="BT6" s="28" t="n"/>
+      <c r="BU6" s="25" t="n"/>
+      <c r="BV6" s="29" t="n"/>
+      <c r="BW6" s="24" t="inlineStr">
+        <is>
+          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
+        </is>
+      </c>
+      <c r="BX6" s="30" t="n"/>
+      <c r="BY6" s="27" t="n"/>
+      <c r="BZ6" s="24" t="n"/>
+      <c r="CA6" s="31" t="n"/>
+      <c r="CB6" s="24" t="n"/>
+      <c r="CC6" s="24" t="n"/>
+      <c r="CD6" s="24" t="n"/>
+      <c r="CE6" s="24" t="n"/>
+      <c r="CF6" s="24" t="n"/>
+      <c r="CG6" s="24" t="n"/>
+      <c r="CH6" s="24" t="n"/>
+      <c r="CI6" s="24" t="n"/>
+      <c r="CJ6" s="24" t="n"/>
+      <c r="CK6" s="24" t="n"/>
+      <c r="CL6" s="24" t="n"/>
+      <c r="CM6" s="24" t="n"/>
+      <c r="CN6" s="24" t="n"/>
+      <c r="CO6" s="24" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>87df2d01ec0145ee</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:38:19.923501Z</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>63056</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>VooDooSh Team</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N7" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O7" s="28" t="n">
+        <v>0.537873</v>
+      </c>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="28" t="n">
+        <v>-0.001298</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="S7" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="25" t="n"/>
+      <c r="Z7" s="26" t="n"/>
+      <c r="AA7" s="28" t="n"/>
+      <c r="AB7" s="28" t="n"/>
+      <c r="AC7" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:57:08.268935Z</t>
+        </is>
+      </c>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-dota2-vds-avi-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG7" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH7" s="24" t="n"/>
+      <c r="AI7" s="31" t="n"/>
+      <c r="AJ7" s="31" t="n"/>
+      <c r="AK7" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN7" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO7" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP7" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="AQ7" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="AR7" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="AS7" s="24" t="inlineStr">
+        <is>
+          <t>VooDooSh Team</t>
+        </is>
+      </c>
+      <c r="AT7" s="24" t="inlineStr">
+        <is>
+          <t>VooDooSh Team</t>
+        </is>
+      </c>
+      <c r="AU7" s="24" t="inlineStr">
+        <is>
+          <t>VooDooSh Team</t>
+        </is>
+      </c>
+      <c r="AV7" s="24" t="n"/>
+      <c r="AW7" s="24" t="n"/>
+      <c r="AX7" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY7" s="24" t="n"/>
+      <c r="AZ7" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA7" s="24" t="inlineStr">
+        <is>
+          <t>713355eeac1c7f851a8fe35e939969377fe0747dd60b1ddb9f28fd4faae96635</t>
+        </is>
+      </c>
+      <c r="BB7" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC7" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD7" s="24" t="inlineStr">
+        <is>
+          <t>713355eeac1c7f851a8fe35e939969377fe0747dd60b1ddb9f28fd4faae96635</t>
+        </is>
+      </c>
+      <c r="BE7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG7" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:38:15.036899Z</t>
+        </is>
+      </c>
+      <c r="BI7" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ7" s="25" t="n"/>
+      <c r="BK7" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL7" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM7" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN7" s="28" t="n"/>
+      <c r="BO7" s="28" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
+      <c r="BR7" s="28" t="n"/>
+      <c r="BS7" s="28" t="n"/>
+      <c r="BT7" s="28" t="n"/>
+      <c r="BU7" s="25" t="n"/>
+      <c r="BV7" s="29" t="n"/>
+      <c r="BW7" s="24" t="n"/>
+      <c r="BX7" s="30" t="n"/>
+      <c r="BY7" s="27" t="n"/>
+      <c r="BZ7" s="24" t="n"/>
+      <c r="CA7" s="31" t="n"/>
+      <c r="CB7" s="24" t="n"/>
+      <c r="CC7" s="24" t="n"/>
+      <c r="CD7" s="24" t="n"/>
+      <c r="CE7" s="24" t="n"/>
+      <c r="CF7" s="24" t="n"/>
+      <c r="CG7" s="24" t="n"/>
+      <c r="CH7" s="24" t="n"/>
+      <c r="CI7" s="24" t="n"/>
+      <c r="CJ7" s="24" t="n"/>
+      <c r="CK7" s="24" t="n"/>
+      <c r="CL7" s="24" t="n"/>
+      <c r="CM7" s="24" t="n"/>
+      <c r="CN7" s="24" t="n"/>
+      <c r="CO7" s="24" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>fb7dd1ca4fab4789</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:11.100365Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>62515</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.523841</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>0.054357</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>47</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="n"/>
+      <c r="W8" s="26" t="n"/>
+      <c r="X8" s="26" t="n"/>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n"/>
+      <c r="AD8" s="24" t="n"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-dota2-bald-lvlup-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:06.898700Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN8" s="28" t="n"/>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+      <c r="CB8" s="24" t="n"/>
+      <c r="CC8" s="24" t="n"/>
+      <c r="CD8" s="24" t="n"/>
+      <c r="CE8" s="24" t="n"/>
+      <c r="CF8" s="24" t="n"/>
+      <c r="CG8" s="24" t="n"/>
+      <c r="CH8" s="24" t="n"/>
+      <c r="CI8" s="24" t="n"/>
+      <c r="CJ8" s="24" t="n"/>
+      <c r="CK8" s="24" t="n"/>
+      <c r="CL8" s="24" t="n"/>
+      <c r="CM8" s="24" t="n"/>
+      <c r="CN8" s="24" t="n"/>
+      <c r="CO8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>87788333ffb546e7</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:11.100365Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>63057</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Travoman Team</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.6704329999999999</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.010569</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-dota2-ns-tt-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>Travoman Team</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>Travoman Team</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>Travoman Team</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:07.498043Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>81db9b754ec644f4</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:11.100365Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>63844</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.5611120000000001</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>-0.01872</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="n"/>
+      <c r="W10" s="26" t="n"/>
+      <c r="X10" s="26" t="n"/>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n"/>
+      <c r="AD10" s="24" t="n"/>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-nh-pckcp-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:08.215820Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>e8b7c2b854a543d8</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:11.100365Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>63059</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Rostik Team</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.62541</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.005638</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>23</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-dota2-stray-rt-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>Rostik Team</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>Rostik Team</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>Rostik Team</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:08.768159Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>f38314eaf1264f38</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:11.100365Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>62516</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.549793</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>-0.030039</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="26" t="n"/>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n"/>
+      <c r="AD12" s="24" t="n"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-pckcp-kw-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:09.374516Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>425898baf836412f</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:11.100365Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>63058</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Daxak Team</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>VooDooSh Team</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.537873</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>-0.062127</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-vds-dxk-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>Daxak Team</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Daxak Team</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Daxak Team</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>VooDooSh Team</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>VooDooSh Team</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>VooDooSh Team</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:10.023286Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>fc2e66136d484926</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:11.100365Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>62517</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.640306</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>1.8e-05</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="n"/>
+      <c r="W14" s="26" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-dota2-agm-tje-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:10.593388Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>112b7f3d42d14b71</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:11.100365Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>63060</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>YBN Team</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.682083</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.291458</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-ybn-avi-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>YBN Team</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>YBN Team</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>YBN Team</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:11.099344Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:CO1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO15" headerRowCount="1">
-  <autoFilter ref="A1:CO15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO13" headerRowCount="1">
+  <autoFilter ref="A1:CO13"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$15)</f>
+        <f>COUNTA('Picks'!$A$2:$A$13)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$13,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$13,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")/(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$13)/SUM('Picks'!$BX$2:$BX$13),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$15)</f>
+        <f>SUM('Picks'!$BY$2:$BY$13)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$13,"&lt;&gt;",'Picks'!$AB$2:$AB$13),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$13,'Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO15"/>
+  <dimension ref="A1:CO13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3214,12 +3214,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>fb7dd1ca4fab4789</t>
+          <t>902b2feca020418f</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:11.100365Z</t>
+          <t>2026-07-28T11:18:10.759539Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>62515</t>
+          <t>63057</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>Travoman Team</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>NS Team</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
@@ -3264,26 +3264,26 @@
         </is>
       </c>
       <c r="L8" s="26" t="n">
-        <v>113</v>
+        <v>-203</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>2.13</v>
+        <v>1.492611</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.669967</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>0.523841</v>
+        <v>0.6704329999999999</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.054357</v>
+        <v>0.000466</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="S8" s="29" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="T8" s="24" t="inlineStr">
         <is>
@@ -3292,21 +3292,35 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="AC8" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:58:59.922687Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-dota2-bald-lvlup-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-ns-tt-2026-07-28).</t>
         </is>
       </c>
       <c r="AF8" s="31" t="inlineStr">
@@ -3324,7 +3338,7 @@
       <c r="AJ8" s="31" t="n"/>
       <c r="AK8" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL8" s="26" t="n">
@@ -3332,47 +3346,47 @@
       </c>
       <c r="AM8" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN8" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO8" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP8" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>Travoman Team</t>
         </is>
       </c>
       <c r="AQ8" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>Travoman Team</t>
         </is>
       </c>
       <c r="AR8" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>Travoman Team</t>
         </is>
       </c>
       <c r="AS8" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>NS Team</t>
         </is>
       </c>
       <c r="AT8" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>NS Team</t>
         </is>
       </c>
       <c r="AU8" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>NS Team</t>
         </is>
       </c>
       <c r="AV8" s="24" t="n"/>
@@ -3390,7 +3404,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3405,7 +3419,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3425,7 +3439,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:06.898700Z</t>
+          <t>2026-07-28T11:18:04.086930Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3435,13 +3449,13 @@
       </c>
       <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
-        <v>113</v>
+        <v>-203</v>
       </c>
       <c r="BL8" s="27" t="n">
-        <v>2.13</v>
+        <v>1.492611</v>
       </c>
       <c r="BM8" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.669967</v>
       </c>
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
@@ -3475,12 +3489,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>87788333ffb546e7</t>
+          <t>d48ed423cea34f7b</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:11.100365Z</t>
+          <t>2026-07-28T11:18:10.759539Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3490,7 +3504,7 @@
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>63057</t>
+          <t>62515</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3500,12 +3514,12 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>Travoman Team</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Team Bald</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -3525,26 +3539,26 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>-194</v>
+        <v>100</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>1.515464</v>
+        <v>2</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.5</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.6704329999999999</v>
+        <v>0.523841</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.010569</v>
+        <v>0.023841</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="S9" s="29" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="T9" s="24" t="inlineStr">
         <is>
@@ -3567,7 +3581,7 @@
       <c r="AD9" s="24" t="n"/>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-dota2-ns-tt-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-dota2-bald-lvlup-2026-07-28).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3585,7 +3599,7 @@
       <c r="AJ9" s="31" t="n"/>
       <c r="AK9" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL9" s="26" t="n">
@@ -3593,47 +3607,47 @@
       </c>
       <c r="AM9" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN9" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO9" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP9" s="24" t="inlineStr">
         <is>
-          <t>Travoman Team</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="AQ9" s="24" t="inlineStr">
         <is>
-          <t>Travoman Team</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="AR9" s="24" t="inlineStr">
         <is>
-          <t>Travoman Team</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="AS9" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Team Bald</t>
         </is>
       </c>
       <c r="AT9" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Team Bald</t>
         </is>
       </c>
       <c r="AU9" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Team Bald</t>
         </is>
       </c>
       <c r="AV9" s="24" t="n"/>
@@ -3651,7 +3665,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3666,7 +3680,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3686,7 +3700,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:07.498043Z</t>
+          <t>2026-07-28T11:18:04.530689Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3696,13 +3710,13 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>-194</v>
+        <v>100</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>1.515464</v>
+        <v>2</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
@@ -3736,12 +3750,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>81db9b754ec644f4</t>
+          <t>f0ada500c4cb47c3</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:11.100365Z</t>
+          <t>2026-07-28T11:18:10.759539Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -3786,23 +3800,23 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.75188</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.570815</v>
       </c>
       <c r="O10" s="28" t="n">
         <v>0.5611120000000001</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>-0.01872</v>
+        <v>-0.009703</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="S10" s="29" t="n">
         <v>0</v>
@@ -3814,21 +3828,35 @@
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:59:02.226867Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-nh-pckcp-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-nh-pckcp-2026-07-28).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -3838,7 +3866,7 @@
       </c>
       <c r="AG10" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH10" s="24" t="n"/>
@@ -3912,7 +3940,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -3927,7 +3955,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -3947,7 +3975,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:08.215820Z</t>
+          <t>2026-07-28T11:18:04.968998Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -3957,13 +3985,13 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.75188</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.570815</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
@@ -3997,12 +4025,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>e8b7c2b854a543d8</t>
+          <t>f5c00befbba444f2</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:11.100365Z</t>
+          <t>2026-07-28T14:24:21.986372Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4012,7 +4040,7 @@
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>63059</t>
+          <t>62516</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4022,12 +4050,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Rostik Team</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>Stray Team</t>
+          <t>PuckChamp</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4037,7 +4065,7 @@
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J11" s="25" t="n"/>
@@ -4047,23 +4075,23 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>-163</v>
+        <v>-186</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.537634</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.65035</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.62541</v>
+        <v>0.549451</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.005638</v>
+        <v>-0.100899</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="S11" s="29" t="n">
         <v>0</v>
@@ -4089,7 +4117,7 @@
       <c r="AD11" s="24" t="n"/>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-dota2-stray-rt-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-dota2-pckcp-kw-2026-07-28).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4130,32 +4158,32 @@
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>Rostik Team</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>Rostik Team</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>Rostik Team</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>Stray Team</t>
+          <t>PuckChamp</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>Stray Team</t>
+          <t>PuckChamp</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>Stray Team</t>
+          <t>PuckChamp</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4173,7 +4201,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+          <t>cf077a212d603eddc5f2d2b29269bd9cb650529ae64fa38c21f4a7e24723110e</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4188,7 +4216,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+          <t>cf077a212d603eddc5f2d2b29269bd9cb650529ae64fa38c21f4a7e24723110e</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4208,7 +4236,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:08.768159Z</t>
+          <t>2026-07-28T14:24:16.158232Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4218,13 +4246,13 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>-163</v>
+        <v>-186</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.537634</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.65035</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
@@ -4258,12 +4286,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>f38314eaf1264f38</t>
+          <t>a4f4a01d01a04a68</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:11.100365Z</t>
+          <t>2026-07-28T14:24:21.986372Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4273,7 +4301,7 @@
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>62516</t>
+          <t>63059</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4283,12 +4311,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>Rostik Team</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>PuckChamp</t>
+          <t>Stray Team</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4298,7 +4326,7 @@
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J12" s="25" t="n"/>
@@ -4308,23 +4336,23 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-138</v>
+        <v>-156</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.641026</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.609375</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.549793</v>
+        <v>0.625006</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>-0.030039</v>
+        <v>0.015631</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="S12" s="29" t="n">
         <v>0</v>
@@ -4350,7 +4378,7 @@
       <c r="AD12" s="24" t="n"/>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-pckcp-kw-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-stray-rt-2026-07-28).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4391,32 +4419,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>Rostik Team</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>Rostik Team</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>Rostik Team</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>PuckChamp</t>
+          <t>Stray Team</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>PuckChamp</t>
+          <t>Stray Team</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>PuckChamp</t>
+          <t>Stray Team</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4434,7 +4462,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+          <t>cf077a212d603eddc5f2d2b29269bd9cb650529ae64fa38c21f4a7e24723110e</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4449,7 +4477,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+          <t>cf077a212d603eddc5f2d2b29269bd9cb650529ae64fa38c21f4a7e24723110e</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4469,7 +4497,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:09.374516Z</t>
+          <t>2026-07-28T14:24:16.628016Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4479,13 +4507,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-138</v>
+        <v>-156</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.641026</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.609375</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4519,12 +4547,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>425898baf836412f</t>
+          <t>9c63058d7cac4902</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:11.100365Z</t>
+          <t>2026-07-28T14:24:21.986372Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4569,20 +4597,20 @@
         </is>
       </c>
       <c r="L13" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="N13" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.537873</v>
+        <v>0.537763</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>-0.062127</v>
+        <v>-0.052401</v>
       </c>
       <c r="R13" s="26" t="n">
         <v>0</v>
@@ -4611,7 +4639,7 @@
       <c r="AD13" s="24" t="n"/>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-vds-dxk-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-vds-dxk-2026-07-28).</t>
         </is>
       </c>
       <c r="AF13" s="31" t="inlineStr">
@@ -4695,7 +4723,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+          <t>cf077a212d603eddc5f2d2b29269bd9cb650529ae64fa38c21f4a7e24723110e</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4710,7 +4738,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+          <t>cf077a212d603eddc5f2d2b29269bd9cb650529ae64fa38c21f4a7e24723110e</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4730,7 +4758,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:10.023286Z</t>
+          <t>2026-07-28T14:24:17.095198Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4740,13 +4768,13 @@
       </c>
       <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="BL13" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="BM13" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
@@ -4777,528 +4805,6 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
     </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>fc2e66136d484926</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:11.100365Z</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>62517</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F14" s="24" t="inlineStr">
-        <is>
-          <t>Team Jenz</t>
-        </is>
-      </c>
-      <c r="G14" s="24" t="inlineStr">
-        <is>
-          <t>Amaru Gaming</t>
-        </is>
-      </c>
-      <c r="H14" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L14" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M14" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N14" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O14" s="28" t="n">
-        <v>0.640306</v>
-      </c>
-      <c r="P14" s="28" t="n"/>
-      <c r="Q14" s="28" t="n">
-        <v>1.8e-05</v>
-      </c>
-      <c r="R14" s="26" t="n">
-        <v>20</v>
-      </c>
-      <c r="S14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U14" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
-      <c r="Y14" s="25" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="28" t="n"/>
-      <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="24" t="n"/>
-      <c r="AE14" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-dota2-agm-tje-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF14" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG14" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH14" s="24" t="n"/>
-      <c r="AI14" s="31" t="n"/>
-      <c r="AJ14" s="31" t="n"/>
-      <c r="AK14" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL14" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM14" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN14" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO14" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP14" s="24" t="inlineStr">
-        <is>
-          <t>Team Jenz</t>
-        </is>
-      </c>
-      <c r="AQ14" s="24" t="inlineStr">
-        <is>
-          <t>Team Jenz</t>
-        </is>
-      </c>
-      <c r="AR14" s="24" t="inlineStr">
-        <is>
-          <t>Team Jenz</t>
-        </is>
-      </c>
-      <c r="AS14" s="24" t="inlineStr">
-        <is>
-          <t>Amaru Gaming</t>
-        </is>
-      </c>
-      <c r="AT14" s="24" t="inlineStr">
-        <is>
-          <t>Amaru Gaming</t>
-        </is>
-      </c>
-      <c r="AU14" s="24" t="inlineStr">
-        <is>
-          <t>Amaru Gaming</t>
-        </is>
-      </c>
-      <c r="AV14" s="24" t="n"/>
-      <c r="AW14" s="24" t="n"/>
-      <c r="AX14" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY14" s="24" t="n"/>
-      <c r="AZ14" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA14" s="24" t="inlineStr">
-        <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
-        </is>
-      </c>
-      <c r="BB14" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC14" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD14" s="24" t="inlineStr">
-        <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
-        </is>
-      </c>
-      <c r="BE14" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF14" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG14" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH14" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:10.593388Z</t>
-        </is>
-      </c>
-      <c r="BI14" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ14" s="25" t="n"/>
-      <c r="BK14" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL14" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM14" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN14" s="28" t="n"/>
-      <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
-      <c r="BR14" s="28" t="n"/>
-      <c r="BS14" s="28" t="n"/>
-      <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="25" t="n"/>
-      <c r="BV14" s="29" t="n"/>
-      <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="30" t="n"/>
-      <c r="BY14" s="27" t="n"/>
-      <c r="BZ14" s="24" t="n"/>
-      <c r="CA14" s="31" t="n"/>
-      <c r="CB14" s="24" t="n"/>
-      <c r="CC14" s="24" t="n"/>
-      <c r="CD14" s="24" t="n"/>
-      <c r="CE14" s="24" t="n"/>
-      <c r="CF14" s="24" t="n"/>
-      <c r="CG14" s="24" t="n"/>
-      <c r="CH14" s="24" t="n"/>
-      <c r="CI14" s="24" t="n"/>
-      <c r="CJ14" s="24" t="n"/>
-      <c r="CK14" s="24" t="n"/>
-      <c r="CL14" s="24" t="n"/>
-      <c r="CM14" s="24" t="n"/>
-      <c r="CN14" s="24" t="n"/>
-      <c r="CO14" s="24" t="n"/>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>112b7f3d42d14b71</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:11.100365Z</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>63060</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
-        <is>
-          <t>avice Team</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
-        <is>
-          <t>YBN Team</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L15" s="26" t="n">
-        <v>156</v>
-      </c>
-      <c r="M15" s="27" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="N15" s="28" t="n">
-        <v>0.390625</v>
-      </c>
-      <c r="O15" s="28" t="n">
-        <v>0.682083</v>
-      </c>
-      <c r="P15" s="28" t="n"/>
-      <c r="Q15" s="28" t="n">
-        <v>0.291458</v>
-      </c>
-      <c r="R15" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U15" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
-      <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
-      <c r="AE15" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-ybn-avi-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF15" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG15" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH15" s="24" t="n"/>
-      <c r="AI15" s="31" t="n"/>
-      <c r="AJ15" s="31" t="n"/>
-      <c r="AK15" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL15" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM15" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN15" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO15" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP15" s="24" t="inlineStr">
-        <is>
-          <t>avice Team</t>
-        </is>
-      </c>
-      <c r="AQ15" s="24" t="inlineStr">
-        <is>
-          <t>avice Team</t>
-        </is>
-      </c>
-      <c r="AR15" s="24" t="inlineStr">
-        <is>
-          <t>avice Team</t>
-        </is>
-      </c>
-      <c r="AS15" s="24" t="inlineStr">
-        <is>
-          <t>YBN Team</t>
-        </is>
-      </c>
-      <c r="AT15" s="24" t="inlineStr">
-        <is>
-          <t>YBN Team</t>
-        </is>
-      </c>
-      <c r="AU15" s="24" t="inlineStr">
-        <is>
-          <t>YBN Team</t>
-        </is>
-      </c>
-      <c r="AV15" s="24" t="n"/>
-      <c r="AW15" s="24" t="n"/>
-      <c r="AX15" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY15" s="24" t="n"/>
-      <c r="AZ15" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA15" s="24" t="inlineStr">
-        <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
-        </is>
-      </c>
-      <c r="BB15" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC15" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD15" s="24" t="inlineStr">
-        <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
-        </is>
-      </c>
-      <c r="BE15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG15" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH15" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:11.099344Z</t>
-        </is>
-      </c>
-      <c r="BI15" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ15" s="25" t="n"/>
-      <c r="BK15" s="26" t="n">
-        <v>156</v>
-      </c>
-      <c r="BL15" s="27" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BM15" s="28" t="n">
-        <v>0.390625</v>
-      </c>
-      <c r="BN15" s="28" t="n"/>
-      <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
-      <c r="BS15" s="28" t="n"/>
-      <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
-      <c r="BV15" s="29" t="n"/>
-      <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n"/>
-      <c r="BY15" s="27" t="n"/>
-      <c r="BZ15" s="24" t="n"/>
-      <c r="CA15" s="31" t="n"/>
-      <c r="CB15" s="24" t="n"/>
-      <c r="CC15" s="24" t="n"/>
-      <c r="CD15" s="24" t="n"/>
-      <c r="CE15" s="24" t="n"/>
-      <c r="CF15" s="24" t="n"/>
-      <c r="CG15" s="24" t="n"/>
-      <c r="CH15" s="24" t="n"/>
-      <c r="CI15" s="24" t="n"/>
-      <c r="CJ15" s="24" t="n"/>
-      <c r="CK15" s="24" t="n"/>
-      <c r="CL15" s="24" t="n"/>
-      <c r="CM15" s="24" t="n"/>
-      <c r="CN15" s="24" t="n"/>
-      <c r="CO15" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO13" headerRowCount="1">
-  <autoFilter ref="A1:CO13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO29" headerRowCount="1">
+  <autoFilter ref="A1:CO29"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$13)</f>
+        <f>COUNTA('Picks'!$A$2:$A$29)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$13,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$29,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$13,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$29,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")/(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")/(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$13)/SUM('Picks'!$BX$2:$BX$13),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$29)/SUM('Picks'!$BX$2:$BX$29),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$13)</f>
+        <f>SUM('Picks'!$BY$2:$BY$29)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$13,"&lt;&gt;",'Picks'!$AB$2:$AB$13),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$29,"&lt;&gt;",'Picks'!$AB$2:$AB$29),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$13,'Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$29,'Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO13"/>
+  <dimension ref="A1:CO29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2481,18 +2481,28 @@
       </c>
       <c r="U5" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V5" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W5" s="26" t="n"/>
       <c r="X5" s="26" t="n"/>
       <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="24" t="n"/>
+      <c r="AC5" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T23:36:55.745240Z</t>
+        </is>
+      </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-dota2-tje-ill-2026-07-27).</t>
@@ -2641,7 +2651,11 @@
       <c r="BT5" s="28" t="n"/>
       <c r="BU5" s="25" t="n"/>
       <c r="BV5" s="29" t="n"/>
-      <c r="BW5" s="24" t="n"/>
+      <c r="BW5" s="24" t="inlineStr">
+        <is>
+          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
+        </is>
+      </c>
       <c r="BX5" s="30" t="n"/>
       <c r="BY5" s="27" t="n"/>
       <c r="BZ5" s="24" t="n"/>
@@ -3567,18 +3581,28 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W9" s="26" t="n"/>
       <c r="X9" s="26" t="n"/>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:31:03.963365Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-dota2-bald-lvlup-2026-07-28).</t>
@@ -3727,7 +3751,11 @@
       <c r="BT9" s="28" t="n"/>
       <c r="BU9" s="25" t="n"/>
       <c r="BV9" s="29" t="n"/>
-      <c r="BW9" s="24" t="n"/>
+      <c r="BW9" s="24" t="inlineStr">
+        <is>
+          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
+        </is>
+      </c>
       <c r="BX9" s="30" t="n"/>
       <c r="BY9" s="27" t="n"/>
       <c r="BZ9" s="24" t="n"/>
@@ -4103,18 +4131,32 @@
       </c>
       <c r="U11" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
+      <c r="AC11" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:24:45.971684Z</t>
+        </is>
+      </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-dota2-pckcp-kw-2026-07-28).</t>
@@ -4364,18 +4406,32 @@
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
+      <c r="AC12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:31:05.130267Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-stray-rt-2026-07-28).</t>
@@ -4388,7 +4444,7 @@
       </c>
       <c r="AG12" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH12" s="24" t="n"/>
@@ -4625,18 +4681,32 @@
       </c>
       <c r="U13" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y13" s="25" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
+      <c r="AC13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:31:06.213379Z</t>
+        </is>
+      </c>
       <c r="AE13" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-vds-dxk-2026-07-28).</t>
@@ -4649,7 +4719,7 @@
       </c>
       <c r="AG13" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH13" s="24" t="n"/>
@@ -4805,6 +4875,4266 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
     </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>3f0a8c05ed684ff2</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:30:23.509787Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>63060</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>YBN Team</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.68116</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>0.300932</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T23:36:56.948442Z</t>
+        </is>
+      </c>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-dota2-ybn-avi-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>YBN Team</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>YBN Team</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>YBN Team</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>d5654d4f52e87448d68cdf73205dec099fa0dc5a5637072a26a63fb8afd8476d</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>d5654d4f52e87448d68cdf73205dec099fa0dc5a5637072a26a63fb8afd8476d</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:30:19.228024Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>9f728f10d58d400a</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:30:23.509787Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>62517</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.639298</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.108782</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:34:22.760087Z</t>
+        </is>
+      </c>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-agm-tje-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>d5654d4f52e87448d68cdf73205dec099fa0dc5a5637072a26a63fb8afd8476d</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>d5654d4f52e87448d68cdf73205dec099fa0dc5a5637072a26a63fb8afd8476d</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:30:19.772763Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="inlineStr">
+        <is>
+          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
+        </is>
+      </c>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>900bc27a5bc54481</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T08:57:41.131320Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>62625</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.545326</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.035522</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:04:45.870640Z</t>
+        </is>
+      </c>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-dota2-rae-z10-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>ea4069f9fa26716d37364f94a04d40c374520e264563d131060f068b82243fc0</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>ea4069f9fa26716d37364f94a04d40c374520e264563d131060f068b82243fc0</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T08:57:35.327439Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>7cb5f3f494e34949</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T12:04:11.833269Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>63062</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.563373</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>-0.036627</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:12:23.953583Z</t>
+        </is>
+      </c>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-ns-stray-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>1975149062e5ce6b992f64d64cd516228ceab5b0d4760dfd8a040fce4af22aeb</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>1975149062e5ce6b992f64d64cd516228ceab5b0d4760dfd8a040fce4af22aeb</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T12:04:07.127494Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>44ef28ae49fd401e</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T12:04:11.833269Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>62691</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.783842</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.42413</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:12:24.994663Z</t>
+        </is>
+      </c>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-dota2-agm-nemiga-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>1975149062e5ce6b992f64d64cd516228ceab5b0d4760dfd8a040fce4af22aeb</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>1975149062e5ce6b992f64d64cd516228ceab5b0d4760dfd8a040fce4af22aeb</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T12:04:07.620398Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>eaee9f9a4ebf4ab2</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T10:30:19.883158Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>63690</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Travoman Team</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.5938330000000001</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>-0.046455</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="n"/>
+      <c r="W19" s="26" t="n"/>
+      <c r="X19" s="26" t="n"/>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n"/>
+      <c r="AD19" s="24" t="n"/>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-dota2-stray-tt-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>Travoman Team</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Travoman Team</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Travoman Team</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>3bcd1fbb498942b21a2e085eda89faf5557d0f6661ee26a8410d8dba9769a397</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>3bcd1fbb498942b21a2e085eda89faf5557d0f6661ee26a8410d8dba9769a397</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T10:30:13.504721Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>f72326bdda87467a</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T10:30:19.883158Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>63691</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.574553</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>0.124103</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:00:59.768618Z</t>
+        </is>
+      </c>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lvlup-z10-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>3bcd1fbb498942b21a2e085eda89faf5557d0f6661ee26a8410d8dba9769a397</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>3bcd1fbb498942b21a2e085eda89faf5557d0f6661ee26a8410d8dba9769a397</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T10:30:13.979212Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>f7556a3a71ea4189</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T13:36:15.317500Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>63804</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Daxak Team</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.518561</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>-0.141303</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-dota2-avi-dxk-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Daxak Team</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Daxak Team</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Daxak Team</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>avice Team</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>84bbd26177707b184e5d7ceea063ce19a04245602c122da9675ab60a9329d7a7</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>84bbd26177707b184e5d7ceea063ce19a04245602c122da9675ab60a9329d7a7</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T13:36:10.465723Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>c869f43909794708</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.595951Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>64035</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.525766</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>-0.103864</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-agm-ill-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:06.029054Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>4565ff1335824b5e</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.595951Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>64671</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Midas Club</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.747717</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.127945</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-dota2-re-midas-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>Midas Club</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>Midas Club</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>Midas Club</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:06.676111Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>d932a8f01dfa4b63</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.595951Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>64672</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.598287</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>0.048737</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-dota2-yes-xctn-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:07.226095Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>ececb879756842aa</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.595951Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>64735</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.6120679999999999</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.021904</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-tr-pla-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:07.804702Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>4dfc6d70a14c4dd9</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.595951Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>64817</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>REKONIX</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>L1ga Team</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.501185</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>-0.088979</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-l1ga-rnx-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>REKONIX</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>REKONIX</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>REKONIX</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>L1ga Team</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>L1ga Team</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>L1ga Team</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:08.889542Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>8fc44093a67940f7</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.595951Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>64818</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Enjoy</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.605405</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>0.144576</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n"/>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-dota2-enjoy-glyph-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>Enjoy</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>Enjoy</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>Enjoy</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:09.456160Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>57bd098e4bdf4205</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.595951Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>64928</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.70634</v>
+      </c>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n">
+        <v>0.07671</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>58</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="n"/>
+      <c r="W28" s="26" t="n"/>
+      <c r="X28" s="26" t="n"/>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="28" t="n"/>
+      <c r="AC28" s="30" t="n"/>
+      <c r="AD28" s="24" t="n"/>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-xtreme-lgd-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.047707Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN28" s="28" t="n"/>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
+      <c r="BR28" s="28" t="n"/>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="n"/>
+      <c r="CD28" s="24" t="n"/>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="n"/>
+      <c r="CJ28" s="24" t="n"/>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>2852a9fcdec24231</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.595951Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>64929</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.611965</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>0.262315</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="n"/>
+      <c r="W29" s="26" t="n"/>
+      <c r="X29" s="26" t="n"/>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n"/>
+      <c r="AD29" s="24" t="n"/>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-dota2-yb-z10-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.594126Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="n"/>
+      <c r="CD29" s="24" t="n"/>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="n"/>
+      <c r="CJ29" s="24" t="n"/>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -6331,18 +6331,32 @@
       </c>
       <c r="U19" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y19" s="25" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n"/>
-      <c r="AD19" s="24" t="n"/>
+      <c r="AC19" s="30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:22:51.651166Z</t>
+        </is>
+      </c>
       <c r="AE19" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-dota2-stray-tt-2026-07-30).</t>
@@ -6355,7 +6369,7 @@
       </c>
       <c r="AG19" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH19" s="24" t="n"/>
@@ -7050,12 +7064,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>c869f43909794708</t>
+          <t>c3825b5d76f94d79</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.595951Z</t>
+          <t>2026-07-30T17:22:19.251723Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7100,20 +7114,20 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="O22" s="28" t="n">
         <v>0.525766</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>-0.103864</v>
+        <v>-0.114522</v>
       </c>
       <c r="R22" s="26" t="n">
         <v>0</v>
@@ -7142,7 +7156,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-agm-ill-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-dota2-agm-ill-2026-07-30).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7226,7 +7240,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7241,7 +7255,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7261,7 +7275,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:06.029054Z</t>
+          <t>2026-07-30T17:22:14.897922Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7271,13 +7285,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7311,12 +7325,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>4565ff1335824b5e</t>
+          <t>4e01a9028f884594</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.595951Z</t>
+          <t>2026-07-30T17:22:19.251723Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7487,7 +7501,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7502,7 +7516,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7522,7 +7536,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:06.676111Z</t>
+          <t>2026-07-30T17:22:15.485981Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7572,12 +7586,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>d932a8f01dfa4b63</t>
+          <t>18812a0c1f4c498d</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.595951Z</t>
+          <t>2026-07-30T17:22:19.251723Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -7748,7 +7762,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -7763,7 +7777,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -7783,7 +7797,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:07.226095Z</t>
+          <t>2026-07-30T17:22:16.072763Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -7833,12 +7847,12 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>ececb879756842aa</t>
+          <t>21a82b127de34c31</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.595951Z</t>
+          <t>2026-07-30T17:22:19.251723Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -8009,7 +8023,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8024,7 +8038,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8044,7 +8058,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:07.804702Z</t>
+          <t>2026-07-30T17:22:16.574192Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8094,12 +8108,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>4dfc6d70a14c4dd9</t>
+          <t>2290095e558242a3</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.595951Z</t>
+          <t>2026-07-30T17:22:19.251723Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8270,7 +8284,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8285,7 +8299,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8305,7 +8319,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:08.889542Z</t>
+          <t>2026-07-30T17:22:17.693210Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8355,12 +8369,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>8fc44093a67940f7</t>
+          <t>d583b8a52988474b</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.595951Z</t>
+          <t>2026-07-30T17:22:19.251723Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -8531,7 +8545,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8546,7 +8560,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8566,7 +8580,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:09.456160Z</t>
+          <t>2026-07-30T17:22:18.197240Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -8616,12 +8630,12 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>57bd098e4bdf4205</t>
+          <t>c823d327cc424fff</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.595951Z</t>
+          <t>2026-07-30T17:22:19.251723Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -8792,7 +8806,7 @@
       </c>
       <c r="BA28" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BB28" s="24" t="inlineStr">
@@ -8807,7 +8821,7 @@
       </c>
       <c r="BD28" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BE28" s="24" t="inlineStr">
@@ -8827,7 +8841,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.047707Z</t>
+          <t>2026-07-30T17:22:18.719201Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -8877,12 +8891,12 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>2852a9fcdec24231</t>
+          <t>84868dd7c9df4a50</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.595951Z</t>
+          <t>2026-07-30T17:22:19.251723Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -9053,7 +9067,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9068,7 +9082,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9088,7 +9102,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.594126Z</t>
+          <t>2026-07-30T17:22:19.250107Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -6350,7 +6350,7 @@
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
       <c r="AC19" s="30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
         <is>
@@ -7064,12 +7064,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>c3825b5d76f94d79</t>
+          <t>2b2794497c3a4977</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.251723Z</t>
+          <t>2026-07-30T17:39:56.381240Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7114,20 +7114,20 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>-178</v>
+        <v>-203</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.492611</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.669967</v>
       </c>
       <c r="O22" s="28" t="n">
         <v>0.525766</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>-0.114522</v>
+        <v>-0.144201</v>
       </c>
       <c r="R22" s="26" t="n">
         <v>0</v>
@@ -7156,7 +7156,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-dota2-agm-ill-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-agm-ill-2026-07-30).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:14.897922Z</t>
+          <t>2026-07-30T17:39:51.801402Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7285,13 +7285,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>-178</v>
+        <v>-203</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.492611</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.669967</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7325,12 +7325,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>4e01a9028f884594</t>
+          <t>3b298e369eba4fea</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.251723Z</t>
+          <t>2026-07-30T17:39:56.381240Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:15.485981Z</t>
+          <t>2026-07-30T17:39:52.434355Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7586,12 +7586,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>18812a0c1f4c498d</t>
+          <t>25e9bd707d764016</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.251723Z</t>
+          <t>2026-07-30T17:39:56.381240Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:16.072763Z</t>
+          <t>2026-07-30T17:39:52.965080Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -7847,12 +7847,12 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>21a82b127de34c31</t>
+          <t>5064bad801864474</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.251723Z</t>
+          <t>2026-07-30T17:39:56.381240Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:16.574192Z</t>
+          <t>2026-07-30T17:39:53.524510Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8108,12 +8108,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>2290095e558242a3</t>
+          <t>a49da12ebbb040ab</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.251723Z</t>
+          <t>2026-07-30T17:39:56.381240Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:17.693210Z</t>
+          <t>2026-07-30T17:39:54.685605Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8369,12 +8369,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>d583b8a52988474b</t>
+          <t>0246944d3a3f4a93</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.251723Z</t>
+          <t>2026-07-30T17:39:56.381240Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:18.197240Z</t>
+          <t>2026-07-30T17:39:55.261695Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -8630,12 +8630,12 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>c823d327cc424fff</t>
+          <t>c589d484f454480a</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.251723Z</t>
+          <t>2026-07-30T17:39:56.381240Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="BA28" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BB28" s="24" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="BD28" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BE28" s="24" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:18.719201Z</t>
+          <t>2026-07-30T17:39:55.839894Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -8891,12 +8891,12 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>84868dd7c9df4a50</t>
+          <t>d3c607e7406640ec</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.251723Z</t>
+          <t>2026-07-30T17:39:56.381240Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.250107Z</t>
+          <t>2026-07-30T17:39:56.380308Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO29" headerRowCount="1">
-  <autoFilter ref="A1:CO29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO15" headerRowCount="1">
+  <autoFilter ref="A1:CO15"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$29)</f>
+        <f>COUNTA('Picks'!$A$2:$A$15)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$29,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$29,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")/(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$29)/SUM('Picks'!$BX$2:$BX$29),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$29)</f>
+        <f>SUM('Picks'!$BY$2:$BY$15)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$29,"&lt;&gt;",'Picks'!$AB$2:$AB$29),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$29,'Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO29"/>
+  <dimension ref="A1:CO15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1578,22 +1578,22 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>873d2a5526b04b7d</t>
+          <t>7bb4334f68de4bcd</t>
         </is>
       </c>
       <c r="B2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T10:27:42.175744Z</t>
+          <t>2026-07-31T10:46:51.141594Z</t>
         </is>
       </c>
       <c r="C2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T12:00:00Z</t>
+          <t>2026-07-31T11:00:00Z</t>
         </is>
       </c>
       <c r="D2" s="24" t="inlineStr">
         <is>
-          <t>62511</t>
+          <t>64817</t>
         </is>
       </c>
       <c r="E2" s="24" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="F2" s="24" t="inlineStr">
         <is>
-          <t>Nemiga Gaming</t>
+          <t>REKONIX</t>
         </is>
       </c>
       <c r="G2" s="24" t="inlineStr">
         <is>
-          <t>Team Syntax</t>
+          <t>L1ga Team</t>
         </is>
       </c>
       <c r="H2" s="24" t="inlineStr">
@@ -1628,63 +1628,69 @@
         </is>
       </c>
       <c r="L2" s="26" t="n">
-        <v>-138</v>
+        <v>133</v>
       </c>
       <c r="M2" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.33</v>
       </c>
       <c r="N2" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.429185</v>
       </c>
       <c r="O2" s="28" t="n">
-        <v>0.521452</v>
+        <v>0.528355</v>
       </c>
       <c r="P2" s="28" t="n"/>
       <c r="Q2" s="28" t="n">
-        <v>-0.05838</v>
+        <v>0.09916999999999999</v>
       </c>
       <c r="R2" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="S2" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U2" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S2" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U2" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V2" s="24" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="W2" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" s="26" t="n">
-        <v>1</v>
-      </c>
       <c r="Y2" s="25" t="n"/>
-      <c r="Z2" s="26" t="n"/>
-      <c r="AA2" s="28" t="n"/>
-      <c r="AB2" s="28" t="n"/>
+      <c r="Z2" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="AA2" s="28" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AB2" s="28" t="n">
+        <v>0.000815</v>
+      </c>
       <c r="AC2" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T16:09:07.565768Z</t>
+          <t>2026-07-31T16:44:45.190822Z</t>
         </is>
       </c>
       <c r="AE2" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-stx-nemiga-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-dota2-l1ga-rnx-2026-07-31).</t>
         </is>
       </c>
       <c r="AF2" s="31" t="inlineStr">
@@ -1694,7 +1700,7 @@
       </c>
       <c r="AG2" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH2" s="24" t="n"/>
@@ -1720,37 +1726,37 @@
       </c>
       <c r="AO2" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP2" s="24" t="inlineStr">
         <is>
-          <t>Nemiga Gaming</t>
+          <t>REKONIX</t>
         </is>
       </c>
       <c r="AQ2" s="24" t="inlineStr">
         <is>
-          <t>Nemiga Gaming</t>
+          <t>REKONIX</t>
         </is>
       </c>
       <c r="AR2" s="24" t="inlineStr">
         <is>
-          <t>Nemiga Gaming</t>
+          <t>REKONIX</t>
         </is>
       </c>
       <c r="AS2" s="24" t="inlineStr">
         <is>
-          <t>Team Syntax</t>
+          <t>L1ga Team</t>
         </is>
       </c>
       <c r="AT2" s="24" t="inlineStr">
         <is>
-          <t>Team Syntax</t>
+          <t>L1ga Team</t>
         </is>
       </c>
       <c r="AU2" s="24" t="inlineStr">
         <is>
-          <t>Team Syntax</t>
+          <t>L1ga Team</t>
         </is>
       </c>
       <c r="AV2" s="24" t="n"/>
@@ -1768,7 +1774,7 @@
       </c>
       <c r="BA2" s="24" t="inlineStr">
         <is>
-          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
+          <t>def433bd75610fad2e6504afeb97fc726ca47b86cda4e8e2a0e49fa44868309d</t>
         </is>
       </c>
       <c r="BB2" s="24" t="inlineStr">
@@ -1778,12 +1784,12 @@
       </c>
       <c r="BC2" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD2" s="24" t="inlineStr">
         <is>
-          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
+          <t>def433bd75610fad2e6504afeb97fc726ca47b86cda4e8e2a0e49fa44868309d</t>
         </is>
       </c>
       <c r="BE2" s="24" t="inlineStr">
@@ -1798,12 +1804,12 @@
       </c>
       <c r="BG2" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T10:27:35.450448Z</t>
+          <t>2026-07-31T10:46:48.956138Z</t>
         </is>
       </c>
       <c r="BI2" s="24" t="inlineStr">
@@ -1813,19 +1819,23 @@
       </c>
       <c r="BJ2" s="25" t="n"/>
       <c r="BK2" s="26" t="n">
-        <v>-138</v>
+        <v>133</v>
       </c>
       <c r="BL2" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.33</v>
       </c>
       <c r="BM2" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.429185</v>
       </c>
       <c r="BN2" s="28" t="n"/>
       <c r="BO2" s="28" t="n"/>
       <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="27" t="n"/>
-      <c r="BR2" s="28" t="n"/>
+      <c r="BQ2" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BR2" s="28" t="n">
+        <v>0.43</v>
+      </c>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
       <c r="BU2" s="25" t="n"/>
@@ -1853,22 +1863,22 @@
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>796e62e9750d41fc</t>
+          <t>c26089390a3847c9</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T10:27:42.175744Z</t>
+          <t>2026-07-31T10:46:51.141594Z</t>
         </is>
       </c>
       <c r="C3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T12:00:00Z</t>
+          <t>2026-07-31T11:00:00Z</t>
         </is>
       </c>
       <c r="D3" s="24" t="inlineStr">
         <is>
-          <t>63054</t>
+          <t>64818</t>
         </is>
       </c>
       <c r="E3" s="24" t="inlineStr">
@@ -1878,12 +1888,12 @@
       </c>
       <c r="F3" s="24" t="inlineStr">
         <is>
-          <t>Daxak Team</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="G3" s="24" t="inlineStr">
         <is>
-          <t>YBN Team</t>
+          <t>Enjoy</t>
         </is>
       </c>
       <c r="H3" s="24" t="inlineStr">
@@ -1893,7 +1903,7 @@
       </c>
       <c r="I3" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J3" s="25" t="n"/>
@@ -1903,30 +1913,30 @@
         </is>
       </c>
       <c r="L3" s="26" t="n">
-        <v>-138</v>
+        <v>117</v>
       </c>
       <c r="M3" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.17</v>
       </c>
       <c r="N3" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.460829</v>
       </c>
       <c r="O3" s="28" t="n">
-        <v>0.521452</v>
+        <v>0.675115</v>
       </c>
       <c r="P3" s="28" t="n"/>
       <c r="Q3" s="28" t="n">
-        <v>-0.05838</v>
+        <v>0.214286</v>
       </c>
       <c r="R3" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S3" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T3" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U3" s="24" t="inlineStr">
@@ -1936,7 +1946,7 @@
       </c>
       <c r="V3" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W3" s="26" t="n">
@@ -1946,20 +1956,26 @@
         <v>0</v>
       </c>
       <c r="Y3" s="25" t="n"/>
-      <c r="Z3" s="26" t="n"/>
-      <c r="AA3" s="28" t="n"/>
-      <c r="AB3" s="28" t="n"/>
+      <c r="Z3" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="AA3" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB3" s="28" t="n">
+        <v>-0.000829</v>
+      </c>
       <c r="AC3" s="30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T16:09:08.721581Z</t>
+          <t>2026-07-31T16:44:46.440388Z</t>
         </is>
       </c>
       <c r="AE3" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-ybn-dxk-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-dota2-enjoy-glyph-2026-07-31).</t>
         </is>
       </c>
       <c r="AF3" s="31" t="inlineStr">
@@ -1969,7 +1985,7 @@
       </c>
       <c r="AG3" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH3" s="24" t="n"/>
@@ -1977,7 +1993,7 @@
       <c r="AJ3" s="31" t="n"/>
       <c r="AK3" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL3" s="26" t="n">
@@ -1985,47 +2001,47 @@
       </c>
       <c r="AM3" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN3" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO3" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP3" s="24" t="inlineStr">
         <is>
-          <t>Daxak Team</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="AQ3" s="24" t="inlineStr">
         <is>
-          <t>Daxak Team</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="AR3" s="24" t="inlineStr">
         <is>
-          <t>Daxak Team</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="AS3" s="24" t="inlineStr">
         <is>
-          <t>YBN Team</t>
+          <t>Enjoy</t>
         </is>
       </c>
       <c r="AT3" s="24" t="inlineStr">
         <is>
-          <t>YBN Team</t>
+          <t>Enjoy</t>
         </is>
       </c>
       <c r="AU3" s="24" t="inlineStr">
         <is>
-          <t>YBN Team</t>
+          <t>Enjoy</t>
         </is>
       </c>
       <c r="AV3" s="24" t="n"/>
@@ -2043,7 +2059,7 @@
       </c>
       <c r="BA3" s="24" t="inlineStr">
         <is>
-          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
+          <t>def433bd75610fad2e6504afeb97fc726ca47b86cda4e8e2a0e49fa44868309d</t>
         </is>
       </c>
       <c r="BB3" s="24" t="inlineStr">
@@ -2053,12 +2069,12 @@
       </c>
       <c r="BC3" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD3" s="24" t="inlineStr">
         <is>
-          <t>d08d23d003cdc05b1cc5be7d2e52d9f477153e66ad3c7ec5e0f446618fcfe82f</t>
+          <t>def433bd75610fad2e6504afeb97fc726ca47b86cda4e8e2a0e49fa44868309d</t>
         </is>
       </c>
       <c r="BE3" s="24" t="inlineStr">
@@ -2073,12 +2089,12 @@
       </c>
       <c r="BG3" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T10:27:35.968074Z</t>
+          <t>2026-07-31T10:46:49.443966Z</t>
         </is>
       </c>
       <c r="BI3" s="24" t="inlineStr">
@@ -2088,19 +2104,23 @@
       </c>
       <c r="BJ3" s="25" t="n"/>
       <c r="BK3" s="26" t="n">
-        <v>-138</v>
+        <v>117</v>
       </c>
       <c r="BL3" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.17</v>
       </c>
       <c r="BM3" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.460829</v>
       </c>
       <c r="BN3" s="28" t="n"/>
       <c r="BO3" s="28" t="n"/>
       <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n"/>
-      <c r="BR3" s="28" t="n"/>
+      <c r="BQ3" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BR3" s="28" t="n">
+        <v>0.46</v>
+      </c>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
       <c r="BU3" s="25" t="n"/>
@@ -2128,22 +2148,22 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>fcf7c3af1eca4efd</t>
+          <t>706d705e970c475e</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T13:32:02.513705Z</t>
+          <t>2026-07-31T11:11:38.723603Z</t>
         </is>
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T15:00:00Z</t>
+          <t>2026-07-31T12:00:00Z</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>63055</t>
+          <t>66989</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
@@ -2153,12 +2173,12 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>Rostik Team</t>
+          <t>VooDooSh Team</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Travoman Team</t>
         </is>
       </c>
       <c r="H4" s="24" t="inlineStr">
@@ -2178,30 +2198,30 @@
         </is>
       </c>
       <c r="L4" s="26" t="n">
-        <v>178</v>
+        <v>-170</v>
       </c>
       <c r="M4" s="27" t="n">
-        <v>2.78</v>
+        <v>1.588235</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.62963</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>0.523739</v>
+        <v>0.592068</v>
       </c>
       <c r="P4" s="28" t="n"/>
       <c r="Q4" s="28" t="n">
-        <v>0.164027</v>
+        <v>-0.037562</v>
       </c>
       <c r="R4" s="26" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="S4" s="29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U4" s="24" t="inlineStr">
@@ -2221,20 +2241,26 @@
         <v>1</v>
       </c>
       <c r="Y4" s="25" t="n"/>
-      <c r="Z4" s="26" t="n"/>
-      <c r="AA4" s="28" t="n"/>
-      <c r="AB4" s="28" t="n"/>
+      <c r="Z4" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA4" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB4" s="28" t="n">
+        <v>0.00037</v>
+      </c>
       <c r="AC4" s="30" t="n">
-        <v>0</v>
+        <v>0.7353</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T19:47:21.041247Z</t>
+          <t>2026-07-31T16:44:47.585797Z</t>
         </is>
       </c>
       <c r="AE4" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-dota2-ns-rt-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-tt-vds-2026-07-31).</t>
         </is>
       </c>
       <c r="AF4" s="31" t="inlineStr">
@@ -2270,37 +2296,37 @@
       </c>
       <c r="AO4" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP4" s="24" t="inlineStr">
         <is>
-          <t>Rostik Team</t>
+          <t>VooDooSh Team</t>
         </is>
       </c>
       <c r="AQ4" s="24" t="inlineStr">
         <is>
-          <t>Rostik Team</t>
+          <t>VooDooSh Team</t>
         </is>
       </c>
       <c r="AR4" s="24" t="inlineStr">
         <is>
-          <t>Rostik Team</t>
+          <t>VooDooSh Team</t>
         </is>
       </c>
       <c r="AS4" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Travoman Team</t>
         </is>
       </c>
       <c r="AT4" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Travoman Team</t>
         </is>
       </c>
       <c r="AU4" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Travoman Team</t>
         </is>
       </c>
       <c r="AV4" s="24" t="n"/>
@@ -2318,7 +2344,7 @@
       </c>
       <c r="BA4" s="24" t="inlineStr">
         <is>
-          <t>364cc42b22c3dca8b67013f8d5f39ea2a25268e5ee37712a8f8745913632a7c2</t>
+          <t>b23f7ad31351c726b3ccb9408d9601bd6e1b13a585cba9c6145c65f967bd5249</t>
         </is>
       </c>
       <c r="BB4" s="24" t="inlineStr">
@@ -2328,12 +2354,12 @@
       </c>
       <c r="BC4" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD4" s="24" t="inlineStr">
         <is>
-          <t>364cc42b22c3dca8b67013f8d5f39ea2a25268e5ee37712a8f8745913632a7c2</t>
+          <t>b23f7ad31351c726b3ccb9408d9601bd6e1b13a585cba9c6145c65f967bd5249</t>
         </is>
       </c>
       <c r="BE4" s="24" t="inlineStr">
@@ -2348,12 +2374,12 @@
       </c>
       <c r="BG4" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T13:31:56.327646Z</t>
+          <t>2026-07-31T11:11:37.653061Z</t>
         </is>
       </c>
       <c r="BI4" s="24" t="inlineStr">
@@ -2363,19 +2389,23 @@
       </c>
       <c r="BJ4" s="25" t="n"/>
       <c r="BK4" s="26" t="n">
-        <v>178</v>
+        <v>-170</v>
       </c>
       <c r="BL4" s="27" t="n">
-        <v>2.78</v>
+        <v>1.588235</v>
       </c>
       <c r="BM4" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.62963</v>
       </c>
       <c r="BN4" s="28" t="n"/>
       <c r="BO4" s="28" t="n"/>
       <c r="BP4" s="25" t="n"/>
-      <c r="BQ4" s="27" t="n"/>
-      <c r="BR4" s="28" t="n"/>
+      <c r="BQ4" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR4" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
       <c r="BU4" s="25" t="n"/>
@@ -2403,22 +2433,22 @@
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>a9b7e6562dec4458</t>
+          <t>5e5ddb150def4002</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T13:32:02.513705Z</t>
+          <t>2026-07-31T13:44:01.315844Z</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T15:00:00Z</t>
+          <t>2026-07-31T14:00:00Z</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>62512</t>
+          <t>64929</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -2428,12 +2458,12 @@
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>Ilbirs eSports</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
-          <t>Team Jenz</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="H5" s="24" t="inlineStr">
@@ -2443,7 +2473,7 @@
       </c>
       <c r="I5" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J5" s="25" t="n"/>
@@ -2453,59 +2483,69 @@
         </is>
       </c>
       <c r="L5" s="26" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="M5" s="27" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="N5" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.390625</v>
       </c>
       <c r="O5" s="28" t="n">
-        <v>0.523739</v>
+        <v>0.610359</v>
       </c>
       <c r="P5" s="28" t="n"/>
       <c r="Q5" s="28" t="n">
-        <v>0.103571</v>
+        <v>0.219734</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="S5" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T5" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U5" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U5" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V5" s="24" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="W5" s="26" t="n"/>
-      <c r="X5" s="26" t="n"/>
       <c r="Y5" s="25" t="n"/>
-      <c r="Z5" s="26" t="n"/>
-      <c r="AA5" s="28" t="n"/>
-      <c r="AB5" s="28" t="n"/>
+      <c r="Z5" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="AA5" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AB5" s="28" t="n">
+        <v>-0.000625</v>
+      </c>
       <c r="AC5" s="30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T23:36:55.745240Z</t>
+          <t>2026-07-31T19:51:09.070776Z</t>
         </is>
       </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-dota2-tje-ill-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-yb-z10-2026-07-31).</t>
         </is>
       </c>
       <c r="AF5" s="31" t="inlineStr">
@@ -2523,7 +2563,7 @@
       <c r="AJ5" s="31" t="n"/>
       <c r="AK5" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL5" s="26" t="n">
@@ -2531,47 +2571,47 @@
       </c>
       <c r="AM5" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN5" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO5" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP5" s="24" t="inlineStr">
         <is>
-          <t>Ilbirs eSports</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="AQ5" s="24" t="inlineStr">
         <is>
-          <t>Ilbirs eSports</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="AR5" s="24" t="inlineStr">
         <is>
-          <t>Ilbirs eSports</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="AS5" s="24" t="inlineStr">
         <is>
-          <t>Team Jenz</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AT5" s="24" t="inlineStr">
         <is>
-          <t>Team Jenz</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AU5" s="24" t="inlineStr">
         <is>
-          <t>Team Jenz</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AV5" s="24" t="n"/>
@@ -2589,7 +2629,7 @@
       </c>
       <c r="BA5" s="24" t="inlineStr">
         <is>
-          <t>364cc42b22c3dca8b67013f8d5f39ea2a25268e5ee37712a8f8745913632a7c2</t>
+          <t>b5798e8e2d651ab79c8db316f3ec8a564cab27653a02daab82555f6e9f330ac3</t>
         </is>
       </c>
       <c r="BB5" s="24" t="inlineStr">
@@ -2599,12 +2639,12 @@
       </c>
       <c r="BC5" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD5" s="24" t="inlineStr">
         <is>
-          <t>364cc42b22c3dca8b67013f8d5f39ea2a25268e5ee37712a8f8745913632a7c2</t>
+          <t>b5798e8e2d651ab79c8db316f3ec8a564cab27653a02daab82555f6e9f330ac3</t>
         </is>
       </c>
       <c r="BE5" s="24" t="inlineStr">
@@ -2619,12 +2659,12 @@
       </c>
       <c r="BG5" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T13:31:56.921798Z</t>
+          <t>2026-07-31T13:43:57.933952Z</t>
         </is>
       </c>
       <c r="BI5" s="24" t="inlineStr">
@@ -2634,28 +2674,28 @@
       </c>
       <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="BL5" s="27" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="BM5" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.390625</v>
       </c>
       <c r="BN5" s="28" t="n"/>
       <c r="BO5" s="28" t="n"/>
       <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n"/>
-      <c r="BR5" s="28" t="n"/>
+      <c r="BQ5" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BR5" s="28" t="n">
+        <v>0.39</v>
+      </c>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
       <c r="BU5" s="25" t="n"/>
       <c r="BV5" s="29" t="n"/>
-      <c r="BW5" s="24" t="inlineStr">
-        <is>
-          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
-        </is>
-      </c>
+      <c r="BW5" s="24" t="n"/>
       <c r="BX5" s="30" t="n"/>
       <c r="BY5" s="27" t="n"/>
       <c r="BZ5" s="24" t="n"/>
@@ -2678,22 +2718,22 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>584074ed11fa4131</t>
+          <t>a82473d0a2644fac</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T17:38:19.923501Z</t>
+          <t>2026-07-31T13:44:01.315844Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T18:00:00Z</t>
+          <t>2026-07-31T14:00:00Z</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>62513</t>
+          <t>64928</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -2703,12 +2743,12 @@
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">
@@ -2718,7 +2758,7 @@
       </c>
       <c r="I6" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J6" s="25" t="n"/>
@@ -2728,30 +2768,30 @@
         </is>
       </c>
       <c r="L6" s="26" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="M6" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.787402</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>0.643378</v>
+        <v>0.701925</v>
       </c>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
-        <v>0.09382799999999999</v>
+        <v>0.142454</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="S6" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T6" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U6" s="24" t="inlineStr">
@@ -2761,26 +2801,36 @@
       </c>
       <c r="V6" s="24" t="inlineStr">
         <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="W6" s="26" t="n"/>
-      <c r="X6" s="26" t="n"/>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y6" s="25" t="n"/>
-      <c r="Z6" s="26" t="n"/>
-      <c r="AA6" s="28" t="n"/>
-      <c r="AB6" s="28" t="n"/>
+      <c r="Z6" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA6" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB6" s="28" t="n">
+        <v>0.000529</v>
+      </c>
       <c r="AC6" s="30" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:57:07.091830Z</t>
+          <t>2026-07-31T23:28:36.259407Z</t>
         </is>
       </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-dota2-bald-kw-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-xtreme-lgd-2026-07-31).</t>
         </is>
       </c>
       <c r="AF6" s="31" t="inlineStr">
@@ -2790,7 +2840,7 @@
       </c>
       <c r="AG6" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH6" s="24" t="n"/>
@@ -2821,32 +2871,32 @@
       </c>
       <c r="AP6" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AQ6" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AR6" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AS6" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="AT6" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="AU6" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="AV6" s="24" t="n"/>
@@ -2864,7 +2914,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>713355eeac1c7f851a8fe35e939969377fe0747dd60b1ddb9f28fd4faae96635</t>
+          <t>b5798e8e2d651ab79c8db316f3ec8a564cab27653a02daab82555f6e9f330ac3</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2874,12 +2924,12 @@
       </c>
       <c r="BC6" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>713355eeac1c7f851a8fe35e939969377fe0747dd60b1ddb9f28fd4faae96635</t>
+          <t>b5798e8e2d651ab79c8db316f3ec8a564cab27653a02daab82555f6e9f330ac3</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2894,12 +2944,12 @@
       </c>
       <c r="BG6" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T17:38:14.567529Z</t>
+          <t>2026-07-31T13:43:58.701955Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">
@@ -2909,28 +2959,28 @@
       </c>
       <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="BL6" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.787402</v>
       </c>
       <c r="BM6" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN6" s="28" t="n"/>
       <c r="BO6" s="28" t="n"/>
       <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
-      <c r="BR6" s="28" t="n"/>
+      <c r="BQ6" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR6" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
       <c r="BU6" s="25" t="n"/>
       <c r="BV6" s="29" t="n"/>
-      <c r="BW6" s="24" t="inlineStr">
-        <is>
-          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
-        </is>
-      </c>
+      <c r="BW6" s="24" t="n"/>
       <c r="BX6" s="30" t="n"/>
       <c r="BY6" s="27" t="n"/>
       <c r="BZ6" s="24" t="n"/>
@@ -2953,22 +3003,22 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>87df2d01ec0145ee</t>
+          <t>df4dae03d7544b1a</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T17:38:19.923501Z</t>
+          <t>2026-08-01T03:02:50.460010Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T18:00:00Z</t>
+          <t>2026-08-01T05:00:00Z</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>63056</t>
+          <t>67524</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -2978,12 +3028,12 @@
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>avice Team</t>
+          <t>Amaru Gaming</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>VooDooSh Team</t>
+          <t>Execration</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
@@ -3003,63 +3053,63 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>-117</v>
+        <v>-138</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.724638</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.579832</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.537873</v>
+        <v>0.5986399999999999</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>-0.001298</v>
+        <v>0.018808</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="S7" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U7" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W7" s="26" t="n">
+      <c r="X7" s="26" t="n">
         <v>1</v>
-      </c>
-      <c r="X7" s="26" t="n">
-        <v>0</v>
       </c>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
       <c r="AC7" s="30" t="n">
-        <v>0</v>
+        <v>0.9058</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:57:08.268935Z</t>
+          <t>2026-08-01T10:15:49.684731Z</t>
         </is>
       </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-dota2-vds-avi-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-xctn-agm-2026-08-01).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3069,7 +3119,7 @@
       </c>
       <c r="AG7" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH7" s="24" t="n"/>
@@ -3095,37 +3145,37 @@
       </c>
       <c r="AO7" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP7" s="24" t="inlineStr">
         <is>
-          <t>avice Team</t>
+          <t>Amaru Gaming</t>
         </is>
       </c>
       <c r="AQ7" s="24" t="inlineStr">
         <is>
-          <t>avice Team</t>
+          <t>Amaru Gaming</t>
         </is>
       </c>
       <c r="AR7" s="24" t="inlineStr">
         <is>
-          <t>avice Team</t>
+          <t>Amaru Gaming</t>
         </is>
       </c>
       <c r="AS7" s="24" t="inlineStr">
         <is>
-          <t>VooDooSh Team</t>
+          <t>Execration</t>
         </is>
       </c>
       <c r="AT7" s="24" t="inlineStr">
         <is>
-          <t>VooDooSh Team</t>
+          <t>Execration</t>
         </is>
       </c>
       <c r="AU7" s="24" t="inlineStr">
         <is>
-          <t>VooDooSh Team</t>
+          <t>Execration</t>
         </is>
       </c>
       <c r="AV7" s="24" t="n"/>
@@ -3143,7 +3193,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>713355eeac1c7f851a8fe35e939969377fe0747dd60b1ddb9f28fd4faae96635</t>
+          <t>70c4a9b222a6dac9c1b0737621af569fa1e0e955085795442f7ac4d19191488f</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3153,12 +3203,12 @@
       </c>
       <c r="BC7" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>713355eeac1c7f851a8fe35e939969377fe0747dd60b1ddb9f28fd4faae96635</t>
+          <t>70c4a9b222a6dac9c1b0737621af569fa1e0e955085795442f7ac4d19191488f</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3173,12 +3223,12 @@
       </c>
       <c r="BG7" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T17:38:15.036899Z</t>
+          <t>2026-08-01T03:02:44.715510Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3188,13 +3238,13 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>-117</v>
+        <v>-138</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.724638</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.579832</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
@@ -3228,22 +3278,22 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>902b2feca020418f</t>
+          <t>c81acb3ece574db8</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T11:18:10.759539Z</t>
+          <t>2026-08-01T03:02:50.460010Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T12:00:00Z</t>
+          <t>2026-08-01T05:00:00Z</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>63057</t>
+          <t>67530</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -3253,12 +3303,12 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>Travoman Team</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Midas Club</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
@@ -3278,30 +3328,30 @@
         </is>
       </c>
       <c r="L8" s="26" t="n">
-        <v>-203</v>
+        <v>-150</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.666667</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.6</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>0.6704329999999999</v>
+        <v>0.630791</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.000466</v>
+        <v>0.030791</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="S8" s="29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T8" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U8" s="24" t="inlineStr">
@@ -3325,16 +3375,16 @@
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
       <c r="AC8" s="30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T14:58:59.922687Z</t>
+          <t>2026-08-01T10:15:50.858797Z</t>
         </is>
       </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-ns-tt-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-midas-tr-2026-08-01).</t>
         </is>
       </c>
       <c r="AF8" s="31" t="inlineStr">
@@ -3352,7 +3402,7 @@
       <c r="AJ8" s="31" t="n"/>
       <c r="AK8" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL8" s="26" t="n">
@@ -3360,47 +3410,47 @@
       </c>
       <c r="AM8" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN8" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO8" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP8" s="24" t="inlineStr">
         <is>
-          <t>Travoman Team</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AQ8" s="24" t="inlineStr">
         <is>
-          <t>Travoman Team</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AR8" s="24" t="inlineStr">
         <is>
-          <t>Travoman Team</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AS8" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Midas Club</t>
         </is>
       </c>
       <c r="AT8" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Midas Club</t>
         </is>
       </c>
       <c r="AU8" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Midas Club</t>
         </is>
       </c>
       <c r="AV8" s="24" t="n"/>
@@ -3418,7 +3468,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
+          <t>70c4a9b222a6dac9c1b0737621af569fa1e0e955085795442f7ac4d19191488f</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3428,12 +3478,12 @@
       </c>
       <c r="BC8" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
+          <t>70c4a9b222a6dac9c1b0737621af569fa1e0e955085795442f7ac4d19191488f</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3448,12 +3498,12 @@
       </c>
       <c r="BG8" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T11:18:04.086930Z</t>
+          <t>2026-08-01T03:02:45.273136Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3463,13 +3513,13 @@
       </c>
       <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
-        <v>-203</v>
+        <v>-150</v>
       </c>
       <c r="BL8" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.666667</v>
       </c>
       <c r="BM8" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.6</v>
       </c>
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
@@ -3503,22 +3553,22 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>d48ed423cea34f7b</t>
+          <t>dc64bf31375749af</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T11:18:10.759539Z</t>
+          <t>2026-08-01T06:42:17.908342Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T12:00:00Z</t>
+          <t>2026-08-01T08:00:00Z</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>62515</t>
+          <t>67531</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3528,12 +3578,12 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -3553,30 +3603,30 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>100</v>
+        <v>-178</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>2</v>
+        <v>1.561798</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.5</v>
+        <v>0.640288</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.523841</v>
+        <v>0.685333</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.023841</v>
+        <v>0.045045</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="S9" s="29" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="T9" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U9" s="24" t="inlineStr">
@@ -3586,26 +3636,36 @@
       </c>
       <c r="V9" s="24" t="inlineStr">
         <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
-      <c r="Z9" s="26" t="n"/>
-      <c r="AA9" s="28" t="n"/>
-      <c r="AB9" s="28" t="n"/>
+      <c r="Z9" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="AA9" s="28" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AB9" s="28" t="n">
+        <v>-0.000288</v>
+      </c>
       <c r="AC9" s="30" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T20:31:03.963365Z</t>
+          <t>2026-08-01T13:41:04.579614Z</t>
         </is>
       </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-dota2-bald-lvlup-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-dota2-re-pla-2026-08-01).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3615,7 +3675,7 @@
       </c>
       <c r="AG9" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH9" s="24" t="n"/>
@@ -3646,32 +3706,32 @@
       </c>
       <c r="AP9" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AQ9" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AR9" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AS9" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AT9" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AU9" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AV9" s="24" t="n"/>
@@ -3689,7 +3749,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
+          <t>752abd49fc5066bbf6c0b57bc44412069a390e80fbe7ec7ad0c39f984fb62854</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3699,12 +3759,12 @@
       </c>
       <c r="BC9" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
+          <t>752abd49fc5066bbf6c0b57bc44412069a390e80fbe7ec7ad0c39f984fb62854</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3719,12 +3779,12 @@
       </c>
       <c r="BG9" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T11:18:04.530689Z</t>
+          <t>2026-08-01T06:42:13.849047Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3734,28 +3794,28 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>100</v>
+        <v>-178</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>2</v>
+        <v>1.561798</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.5</v>
+        <v>0.640288</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
       <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
-      <c r="BR9" s="28" t="n"/>
+      <c r="BQ9" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BR9" s="28" t="n">
+        <v>0.64</v>
+      </c>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
       <c r="BU9" s="25" t="n"/>
       <c r="BV9" s="29" t="n"/>
-      <c r="BW9" s="24" t="inlineStr">
-        <is>
-          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
-        </is>
-      </c>
+      <c r="BW9" s="24" t="n"/>
       <c r="BX9" s="30" t="n"/>
       <c r="BY9" s="27" t="n"/>
       <c r="BZ9" s="24" t="n"/>
@@ -3778,22 +3838,22 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>f0ada500c4cb47c3</t>
+          <t>baa07510ef7e4401</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T11:18:10.759539Z</t>
+          <t>2026-08-01T06:42:17.908342Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T12:00:00Z</t>
+          <t>2026-08-01T09:00:00Z</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>63844</t>
+          <t>67990</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3803,12 +3863,12 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>PuckChamp</t>
+          <t>avice Team</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>No Hoodwink</t>
+          <t>Daxak Team</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -3818,7 +3878,7 @@
       </c>
       <c r="I10" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J10" s="25" t="n"/>
@@ -3828,63 +3888,69 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.787402</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.5611120000000001</v>
+        <v>0.517054</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>-0.009703</v>
+        <v>-0.042417</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S10" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="T10" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U10" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W10" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="26" t="n">
-        <v>1</v>
-      </c>
       <c r="Y10" s="25" t="n"/>
-      <c r="Z10" s="26" t="n"/>
-      <c r="AA10" s="28" t="n"/>
-      <c r="AB10" s="28" t="n"/>
+      <c r="Z10" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA10" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB10" s="28" t="n">
+        <v>0.000529</v>
+      </c>
       <c r="AC10" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T14:59:02.226867Z</t>
+          <t>2026-08-01T16:48:00.250076Z</t>
         </is>
       </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-nh-pckcp-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-dxk-avi-2026-08-01).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -3920,37 +3986,37 @@
       </c>
       <c r="AO10" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>PuckChamp</t>
+          <t>avice Team</t>
         </is>
       </c>
       <c r="AQ10" s="24" t="inlineStr">
         <is>
-          <t>PuckChamp</t>
+          <t>avice Team</t>
         </is>
       </c>
       <c r="AR10" s="24" t="inlineStr">
         <is>
-          <t>PuckChamp</t>
+          <t>avice Team</t>
         </is>
       </c>
       <c r="AS10" s="24" t="inlineStr">
         <is>
-          <t>No Hoodwink</t>
+          <t>Daxak Team</t>
         </is>
       </c>
       <c r="AT10" s="24" t="inlineStr">
         <is>
-          <t>No Hoodwink</t>
+          <t>Daxak Team</t>
         </is>
       </c>
       <c r="AU10" s="24" t="inlineStr">
         <is>
-          <t>No Hoodwink</t>
+          <t>Daxak Team</t>
         </is>
       </c>
       <c r="AV10" s="24" t="n"/>
@@ -3968,7 +4034,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
+          <t>752abd49fc5066bbf6c0b57bc44412069a390e80fbe7ec7ad0c39f984fb62854</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -3978,12 +4044,12 @@
       </c>
       <c r="BC10" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
+          <t>752abd49fc5066bbf6c0b57bc44412069a390e80fbe7ec7ad0c39f984fb62854</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -3998,12 +4064,12 @@
       </c>
       <c r="BG10" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T11:18:04.968998Z</t>
+          <t>2026-08-01T06:42:14.892061Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4013,19 +4079,23 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.787402</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
       <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
-      <c r="BR10" s="28" t="n"/>
+      <c r="BQ10" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR10" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
       <c r="BU10" s="25" t="n"/>
@@ -4053,22 +4123,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>f5c00befbba444f2</t>
+          <t>4b69058c47604a38</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T14:24:21.986372Z</t>
+          <t>2026-08-01T10:23:10.624442Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T15:00:00Z</t>
+          <t>2026-08-01T11:00:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>62516</t>
+          <t>67645</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4078,12 +4148,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>PuckChamp</t>
+          <t>Enjoy</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4093,7 +4163,7 @@
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J11" s="25" t="n"/>
@@ -4103,63 +4173,69 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>-186</v>
+        <v>138</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>1.537634</v>
+        <v>2.38</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.420168</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.549451</v>
+        <v>0.501304</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>-0.100899</v>
+        <v>0.081136</v>
       </c>
       <c r="R11" s="26" t="n">
+        <v>61</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U11" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="W11" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="26" t="n">
-        <v>1</v>
-      </c>
       <c r="Y11" s="25" t="n"/>
-      <c r="Z11" s="26" t="n"/>
-      <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n"/>
+      <c r="Z11" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="AA11" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB11" s="28" t="n">
+        <v>-0.000168</v>
+      </c>
       <c r="AC11" s="30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:24:45.971684Z</t>
+          <t>2026-08-01T16:48:01.379906Z</t>
         </is>
       </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-dota2-pckcp-kw-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-dota2-enjoy-yb-2026-08-01).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4200,32 +4276,32 @@
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>PuckChamp</t>
+          <t>Enjoy</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>PuckChamp</t>
+          <t>Enjoy</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>PuckChamp</t>
+          <t>Enjoy</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4243,7 +4319,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>cf077a212d603eddc5f2d2b29269bd9cb650529ae64fa38c21f4a7e24723110e</t>
+          <t>deda9eb37849d75abc167c468ca22f3b17af095f0b4080e2e6252b25fb3908be</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4253,12 +4329,12 @@
       </c>
       <c r="BC11" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>cf077a212d603eddc5f2d2b29269bd9cb650529ae64fa38c21f4a7e24723110e</t>
+          <t>deda9eb37849d75abc167c468ca22f3b17af095f0b4080e2e6252b25fb3908be</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4273,12 +4349,12 @@
       </c>
       <c r="BG11" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T14:24:16.158232Z</t>
+          <t>2026-08-01T10:23:08.624845Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4288,19 +4364,23 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>-186</v>
+        <v>138</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>1.537634</v>
+        <v>2.38</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.420168</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
       <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
-      <c r="BR11" s="28" t="n"/>
+      <c r="BQ11" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BR11" s="28" t="n">
+        <v>0.42</v>
+      </c>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
       <c r="BU11" s="25" t="n"/>
@@ -4328,22 +4408,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>a4f4a01d01a04a68</t>
+          <t>cc392b7a7e5d4e66</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T14:24:21.986372Z</t>
+          <t>2026-08-01T10:23:10.624442Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T15:00:00Z</t>
+          <t>2026-08-01T12:00:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>63059</t>
+          <t>67992</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4353,12 +4433,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Rostik Team</t>
+          <t>VooDooSh Team</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>Stray Team</t>
+          <t>NS Team</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4378,30 +4458,30 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-156</v>
+        <v>-138</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.724638</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.579832</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.625006</v>
+        <v>0.549255</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.015631</v>
+        <v>-0.030577</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U12" s="24" t="inlineStr">
@@ -4421,20 +4501,26 @@
         <v>1</v>
       </c>
       <c r="Y12" s="25" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n"/>
+      <c r="Z12" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="AA12" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB12" s="28" t="n">
+        <v>0.000168</v>
+      </c>
       <c r="AC12" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T20:31:05.130267Z</t>
+          <t>2026-08-01T18:35:23.071564Z</t>
         </is>
       </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-stray-rt-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-ns-vds-2026-08-01).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4475,32 +4561,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>Rostik Team</t>
+          <t>VooDooSh Team</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>Rostik Team</t>
+          <t>VooDooSh Team</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>Rostik Team</t>
+          <t>VooDooSh Team</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>Stray Team</t>
+          <t>NS Team</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>Stray Team</t>
+          <t>NS Team</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>Stray Team</t>
+          <t>NS Team</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4518,7 +4604,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>cf077a212d603eddc5f2d2b29269bd9cb650529ae64fa38c21f4a7e24723110e</t>
+          <t>deda9eb37849d75abc167c468ca22f3b17af095f0b4080e2e6252b25fb3908be</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4528,12 +4614,12 @@
       </c>
       <c r="BC12" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>cf077a212d603eddc5f2d2b29269bd9cb650529ae64fa38c21f4a7e24723110e</t>
+          <t>deda9eb37849d75abc167c468ca22f3b17af095f0b4080e2e6252b25fb3908be</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4548,12 +4634,12 @@
       </c>
       <c r="BG12" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T14:24:16.628016Z</t>
+          <t>2026-08-01T10:23:09.203539Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4563,19 +4649,23 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-156</v>
+        <v>-138</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.724638</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.579832</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
       <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
-      <c r="BR12" s="28" t="n"/>
+      <c r="BQ12" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BR12" s="28" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
       <c r="BU12" s="25" t="n"/>
@@ -4603,22 +4693,22 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>9c63058d7cac4902</t>
+          <t>c31b3778fa1d4a2a</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T14:24:21.986372Z</t>
+          <t>2026-08-01T13:46:48.325440Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T15:00:00Z</t>
+          <t>2026-08-01T14:00:00Z</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>63058</t>
+          <t>67647</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -4628,12 +4718,12 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>Daxak Team</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>VooDooSh Team</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -4653,63 +4743,69 @@
         </is>
       </c>
       <c r="L13" s="26" t="n">
-        <v>-144</v>
+        <v>-127</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.787402</v>
       </c>
       <c r="N13" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.537763</v>
+        <v>0.56954</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>-0.052401</v>
+        <v>0.010069</v>
       </c>
       <c r="R13" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U13" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W13" s="26" t="n">
+      <c r="X13" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="X13" s="26" t="n">
-        <v>0</v>
-      </c>
       <c r="Y13" s="25" t="n"/>
-      <c r="Z13" s="26" t="n"/>
-      <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n"/>
+      <c r="Z13" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA13" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB13" s="28" t="n">
+        <v>0.000529</v>
+      </c>
       <c r="AC13" s="30" t="n">
-        <v>0</v>
+        <v>0.9843</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T20:31:06.213379Z</t>
+          <t>2026-08-01T18:35:24.307034Z</t>
         </is>
       </c>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-vds-dxk-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-glyph-z10-2026-08-01).</t>
         </is>
       </c>
       <c r="AF13" s="31" t="inlineStr">
@@ -4719,7 +4815,7 @@
       </c>
       <c r="AG13" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH13" s="24" t="n"/>
@@ -4745,37 +4841,37 @@
       </c>
       <c r="AO13" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP13" s="24" t="inlineStr">
         <is>
-          <t>Daxak Team</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="AQ13" s="24" t="inlineStr">
         <is>
-          <t>Daxak Team</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="AR13" s="24" t="inlineStr">
         <is>
-          <t>Daxak Team</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="AS13" s="24" t="inlineStr">
         <is>
-          <t>VooDooSh Team</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="AT13" s="24" t="inlineStr">
         <is>
-          <t>VooDooSh Team</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="AU13" s="24" t="inlineStr">
         <is>
-          <t>VooDooSh Team</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="AV13" s="24" t="n"/>
@@ -4793,7 +4889,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>cf077a212d603eddc5f2d2b29269bd9cb650529ae64fa38c21f4a7e24723110e</t>
+          <t>e9c5ed6e71791ea5be7f930d81f2276296bd4d18a6bc053f0b2a93d60ab25a74</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4803,12 +4899,12 @@
       </c>
       <c r="BC13" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>cf077a212d603eddc5f2d2b29269bd9cb650529ae64fa38c21f4a7e24723110e</t>
+          <t>e9c5ed6e71791ea5be7f930d81f2276296bd4d18a6bc053f0b2a93d60ab25a74</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4823,12 +4919,12 @@
       </c>
       <c r="BG13" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T14:24:17.095198Z</t>
+          <t>2026-08-01T13:46:47.801537Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4838,19 +4934,23 @@
       </c>
       <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
-        <v>-144</v>
+        <v>-127</v>
       </c>
       <c r="BL13" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.787402</v>
       </c>
       <c r="BM13" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
       <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
-      <c r="BR13" s="28" t="n"/>
+      <c r="BQ13" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR13" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
       <c r="BU13" s="25" t="n"/>
@@ -4878,22 +4978,22 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>3f0a8c05ed684ff2</t>
+          <t>b90b9623c89246cc</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:30:23.509787Z</t>
+          <t>2026-08-01T13:46:48.325440Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T18:00:00Z</t>
+          <t>2026-08-01T15:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>63060</t>
+          <t>67941</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -4903,12 +5003,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>avice Team</t>
+          <t>Travoman Team</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>YBN Team</t>
+          <t>Stray Team</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -4918,7 +5018,7 @@
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J14" s="25" t="n"/>
@@ -4928,30 +5028,30 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>163</v>
+        <v>-156</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>2.63</v>
+        <v>1.641026</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.609375</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.68116</v>
+        <v>0.546939</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.300932</v>
+        <v>-0.062436</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U14" s="24" t="inlineStr">
@@ -4961,7 +5061,7 @@
       </c>
       <c r="V14" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W14" s="26" t="n">
@@ -4971,20 +5071,26 @@
         <v>0</v>
       </c>
       <c r="Y14" s="25" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="28" t="n"/>
-      <c r="AB14" s="28" t="n"/>
+      <c r="Z14" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AA14" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB14" s="28" t="n">
+        <v>0.000625</v>
+      </c>
       <c r="AC14" s="30" t="n">
-        <v>0</v>
+        <v>0.641</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T23:36:56.948442Z</t>
+          <t>2026-08-01T21:25:24.126155Z</t>
         </is>
       </c>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-dota2-ybn-avi-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-stray-tt-2026-08-01).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -4994,7 +5100,7 @@
       </c>
       <c r="AG14" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH14" s="24" t="n"/>
@@ -5020,37 +5126,37 @@
       </c>
       <c r="AO14" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>avice Team</t>
+          <t>Travoman Team</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>avice Team</t>
+          <t>Travoman Team</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>avice Team</t>
+          <t>Travoman Team</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>YBN Team</t>
+          <t>Stray Team</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>YBN Team</t>
+          <t>Stray Team</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>YBN Team</t>
+          <t>Stray Team</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5068,7 +5174,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>d5654d4f52e87448d68cdf73205dec099fa0dc5a5637072a26a63fb8afd8476d</t>
+          <t>e9c5ed6e71791ea5be7f930d81f2276296bd4d18a6bc053f0b2a93d60ab25a74</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5078,12 +5184,12 @@
       </c>
       <c r="BC14" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>d5654d4f52e87448d68cdf73205dec099fa0dc5a5637072a26a63fb8afd8476d</t>
+          <t>e9c5ed6e71791ea5be7f930d81f2276296bd4d18a6bc053f0b2a93d60ab25a74</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5098,12 +5204,12 @@
       </c>
       <c r="BG14" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:30:19.228024Z</t>
+          <t>2026-08-01T13:46:48.324209Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5113,19 +5219,23 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>163</v>
+        <v>-156</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>2.63</v>
+        <v>1.641026</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.609375</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
       <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
-      <c r="BR14" s="28" t="n"/>
+      <c r="BQ14" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BR14" s="28" t="n">
+        <v>0.61</v>
+      </c>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
       <c r="BU14" s="25" t="n"/>
@@ -5153,22 +5263,22 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>9f728f10d58d400a</t>
+          <t>561c588bbefe48c3</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:30:23.509787Z</t>
+          <t>2026-08-01T21:24:30.033213Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T18:00:00Z</t>
+          <t>2026-08-02T08:00:00Z</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>62517</t>
+          <t>68446</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -5178,12 +5288,12 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>Team Jenz</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>Amaru Gaming</t>
+          <t>Yellow Submarine</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5203,59 +5313,49 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>-113</v>
+        <v>-104</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.961538</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.509804</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.639298</v>
+        <v>0.576057</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.108782</v>
+        <v>0.06625300000000001</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="S15" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T15" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U15" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
       <c r="W15" s="26" t="n"/>
       <c r="X15" s="26" t="n"/>
       <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-29T17:34:22.760087Z</t>
-        </is>
-      </c>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-agm-tje-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-dota2-yes-tr-2026-08-02).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5296,32 +5396,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>Team Jenz</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>Team Jenz</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>Team Jenz</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>Amaru Gaming</t>
+          <t>Yellow Submarine</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>Amaru Gaming</t>
+          <t>Yellow Submarine</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>Amaru Gaming</t>
+          <t>Yellow Submarine</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5339,7 +5439,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>d5654d4f52e87448d68cdf73205dec099fa0dc5a5637072a26a63fb8afd8476d</t>
+          <t>65b8f79741d3dcd1d060bb1f14ea0523262331890046cd8c8cccbede889da72c</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5349,12 +5449,12 @@
       </c>
       <c r="BC15" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>d5654d4f52e87448d68cdf73205dec099fa0dc5a5637072a26a63fb8afd8476d</t>
+          <t>65b8f79741d3dcd1d060bb1f14ea0523262331890046cd8c8cccbede889da72c</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5369,12 +5469,12 @@
       </c>
       <c r="BG15" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:30:19.772763Z</t>
+          <t>2026-08-01T21:24:29.070923Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5384,13 +5484,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>-113</v>
+        <v>-104</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.961538</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.509804</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5401,11 +5501,7 @@
       <c r="BT15" s="28" t="n"/>
       <c r="BU15" s="25" t="n"/>
       <c r="BV15" s="29" t="n"/>
-      <c r="BW15" s="24" t="inlineStr">
-        <is>
-          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
-        </is>
-      </c>
+      <c r="BW15" s="24" t="n"/>
       <c r="BX15" s="30" t="n"/>
       <c r="BY15" s="27" t="n"/>
       <c r="BZ15" s="24" t="n"/>
@@ -5425,3730 +5521,6 @@
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>900bc27a5bc54481</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-29T08:57:41.131320Z</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-29T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>62625</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>RE.Arise</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L16" s="26" t="n">
-        <v>-104</v>
-      </c>
-      <c r="M16" s="27" t="n">
-        <v>1.961538</v>
-      </c>
-      <c r="N16" s="28" t="n">
-        <v>0.509804</v>
-      </c>
-      <c r="O16" s="28" t="n">
-        <v>0.545326</v>
-      </c>
-      <c r="P16" s="28" t="n"/>
-      <c r="Q16" s="28" t="n">
-        <v>0.035522</v>
-      </c>
-      <c r="R16" s="26" t="n">
-        <v>38</v>
-      </c>
-      <c r="S16" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U16" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W16" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD16" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-29T15:04:45.870640Z</t>
-        </is>
-      </c>
-      <c r="AE16" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-dota2-rae-z10-2026-07-29).</t>
-        </is>
-      </c>
-      <c r="AF16" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG16" s="24" t="inlineStr">
-        <is>
-          <t>review_required</t>
-        </is>
-      </c>
-      <c r="AH16" s="24" t="n"/>
-      <c r="AI16" s="31" t="n"/>
-      <c r="AJ16" s="31" t="n"/>
-      <c r="AK16" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL16" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM16" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN16" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO16" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP16" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AQ16" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AR16" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AS16" s="24" t="inlineStr">
-        <is>
-          <t>RE.Arise</t>
-        </is>
-      </c>
-      <c r="AT16" s="24" t="inlineStr">
-        <is>
-          <t>RE.Arise</t>
-        </is>
-      </c>
-      <c r="AU16" s="24" t="inlineStr">
-        <is>
-          <t>RE.Arise</t>
-        </is>
-      </c>
-      <c r="AV16" s="24" t="n"/>
-      <c r="AW16" s="24" t="n"/>
-      <c r="AX16" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY16" s="24" t="n"/>
-      <c r="AZ16" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA16" s="24" t="inlineStr">
-        <is>
-          <t>ea4069f9fa26716d37364f94a04d40c374520e264563d131060f068b82243fc0</t>
-        </is>
-      </c>
-      <c r="BB16" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC16" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD16" s="24" t="inlineStr">
-        <is>
-          <t>ea4069f9fa26716d37364f94a04d40c374520e264563d131060f068b82243fc0</t>
-        </is>
-      </c>
-      <c r="BE16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG16" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH16" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-29T08:57:35.327439Z</t>
-        </is>
-      </c>
-      <c r="BI16" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ16" s="25" t="n"/>
-      <c r="BK16" s="26" t="n">
-        <v>-104</v>
-      </c>
-      <c r="BL16" s="27" t="n">
-        <v>1.961538</v>
-      </c>
-      <c r="BM16" s="28" t="n">
-        <v>0.509804</v>
-      </c>
-      <c r="BN16" s="28" t="n"/>
-      <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
-      <c r="BS16" s="28" t="n"/>
-      <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
-      <c r="BV16" s="29" t="n"/>
-      <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n"/>
-      <c r="BY16" s="27" t="n"/>
-      <c r="BZ16" s="24" t="n"/>
-      <c r="CA16" s="31" t="n"/>
-      <c r="CB16" s="24" t="n"/>
-      <c r="CC16" s="24" t="n"/>
-      <c r="CD16" s="24" t="n"/>
-      <c r="CE16" s="24" t="n"/>
-      <c r="CF16" s="24" t="n"/>
-      <c r="CG16" s="24" t="n"/>
-      <c r="CH16" s="24" t="n"/>
-      <c r="CI16" s="24" t="n"/>
-      <c r="CJ16" s="24" t="n"/>
-      <c r="CK16" s="24" t="n"/>
-      <c r="CL16" s="24" t="n"/>
-      <c r="CM16" s="24" t="n"/>
-      <c r="CN16" s="24" t="n"/>
-      <c r="CO16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>7cb5f3f494e34949</t>
-        </is>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-29T12:04:11.833269Z</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-29T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>63062</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F17" s="24" t="inlineStr">
-        <is>
-          <t>Stray Team</t>
-        </is>
-      </c>
-      <c r="G17" s="24" t="inlineStr">
-        <is>
-          <t>NS Team</t>
-        </is>
-      </c>
-      <c r="H17" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L17" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="M17" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="N17" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O17" s="28" t="n">
-        <v>0.563373</v>
-      </c>
-      <c r="P17" s="28" t="n"/>
-      <c r="Q17" s="28" t="n">
-        <v>-0.036627</v>
-      </c>
-      <c r="R17" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U17" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="W17" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T04:12:23.953583Z</t>
-        </is>
-      </c>
-      <c r="AE17" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-ns-stray-2026-07-29).</t>
-        </is>
-      </c>
-      <c r="AF17" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG17" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH17" s="24" t="n"/>
-      <c r="AI17" s="31" t="n"/>
-      <c r="AJ17" s="31" t="n"/>
-      <c r="AK17" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL17" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM17" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN17" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO17" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP17" s="24" t="inlineStr">
-        <is>
-          <t>Stray Team</t>
-        </is>
-      </c>
-      <c r="AQ17" s="24" t="inlineStr">
-        <is>
-          <t>Stray Team</t>
-        </is>
-      </c>
-      <c r="AR17" s="24" t="inlineStr">
-        <is>
-          <t>Stray Team</t>
-        </is>
-      </c>
-      <c r="AS17" s="24" t="inlineStr">
-        <is>
-          <t>NS Team</t>
-        </is>
-      </c>
-      <c r="AT17" s="24" t="inlineStr">
-        <is>
-          <t>NS Team</t>
-        </is>
-      </c>
-      <c r="AU17" s="24" t="inlineStr">
-        <is>
-          <t>NS Team</t>
-        </is>
-      </c>
-      <c r="AV17" s="24" t="n"/>
-      <c r="AW17" s="24" t="n"/>
-      <c r="AX17" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY17" s="24" t="n"/>
-      <c r="AZ17" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA17" s="24" t="inlineStr">
-        <is>
-          <t>1975149062e5ce6b992f64d64cd516228ceab5b0d4760dfd8a040fce4af22aeb</t>
-        </is>
-      </c>
-      <c r="BB17" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC17" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD17" s="24" t="inlineStr">
-        <is>
-          <t>1975149062e5ce6b992f64d64cd516228ceab5b0d4760dfd8a040fce4af22aeb</t>
-        </is>
-      </c>
-      <c r="BE17" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF17" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG17" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH17" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-29T12:04:07.127494Z</t>
-        </is>
-      </c>
-      <c r="BI17" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ17" s="25" t="n"/>
-      <c r="BK17" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="BL17" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="BM17" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN17" s="28" t="n"/>
-      <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
-      <c r="BR17" s="28" t="n"/>
-      <c r="BS17" s="28" t="n"/>
-      <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="25" t="n"/>
-      <c r="BV17" s="29" t="n"/>
-      <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n"/>
-      <c r="BY17" s="27" t="n"/>
-      <c r="BZ17" s="24" t="n"/>
-      <c r="CA17" s="31" t="n"/>
-      <c r="CB17" s="24" t="n"/>
-      <c r="CC17" s="24" t="n"/>
-      <c r="CD17" s="24" t="n"/>
-      <c r="CE17" s="24" t="n"/>
-      <c r="CF17" s="24" t="n"/>
-      <c r="CG17" s="24" t="n"/>
-      <c r="CH17" s="24" t="n"/>
-      <c r="CI17" s="24" t="n"/>
-      <c r="CJ17" s="24" t="n"/>
-      <c r="CK17" s="24" t="n"/>
-      <c r="CL17" s="24" t="n"/>
-      <c r="CM17" s="24" t="n"/>
-      <c r="CN17" s="24" t="n"/>
-      <c r="CO17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>44ef28ae49fd401e</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-29T12:04:11.833269Z</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-29T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>62691</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
-        <is>
-          <t>Nemiga Gaming</t>
-        </is>
-      </c>
-      <c r="G18" s="24" t="inlineStr">
-        <is>
-          <t>Amaru Gaming</t>
-        </is>
-      </c>
-      <c r="H18" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="n"/>
-      <c r="K18" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L18" s="26" t="n">
-        <v>178</v>
-      </c>
-      <c r="M18" s="27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="N18" s="28" t="n">
-        <v>0.359712</v>
-      </c>
-      <c r="O18" s="28" t="n">
-        <v>0.783842</v>
-      </c>
-      <c r="P18" s="28" t="n"/>
-      <c r="Q18" s="28" t="n">
-        <v>0.42413</v>
-      </c>
-      <c r="R18" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S18" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U18" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W18" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="25" t="n"/>
-      <c r="Z18" s="26" t="n"/>
-      <c r="AA18" s="28" t="n"/>
-      <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AD18" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T04:12:24.994663Z</t>
-        </is>
-      </c>
-      <c r="AE18" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-dota2-agm-nemiga-2026-07-29).</t>
-        </is>
-      </c>
-      <c r="AF18" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG18" s="24" t="inlineStr">
-        <is>
-          <t>review_required</t>
-        </is>
-      </c>
-      <c r="AH18" s="24" t="n"/>
-      <c r="AI18" s="31" t="n"/>
-      <c r="AJ18" s="31" t="n"/>
-      <c r="AK18" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL18" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM18" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN18" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO18" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP18" s="24" t="inlineStr">
-        <is>
-          <t>Nemiga Gaming</t>
-        </is>
-      </c>
-      <c r="AQ18" s="24" t="inlineStr">
-        <is>
-          <t>Nemiga Gaming</t>
-        </is>
-      </c>
-      <c r="AR18" s="24" t="inlineStr">
-        <is>
-          <t>Nemiga Gaming</t>
-        </is>
-      </c>
-      <c r="AS18" s="24" t="inlineStr">
-        <is>
-          <t>Amaru Gaming</t>
-        </is>
-      </c>
-      <c r="AT18" s="24" t="inlineStr">
-        <is>
-          <t>Amaru Gaming</t>
-        </is>
-      </c>
-      <c r="AU18" s="24" t="inlineStr">
-        <is>
-          <t>Amaru Gaming</t>
-        </is>
-      </c>
-      <c r="AV18" s="24" t="n"/>
-      <c r="AW18" s="24" t="n"/>
-      <c r="AX18" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY18" s="24" t="n"/>
-      <c r="AZ18" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA18" s="24" t="inlineStr">
-        <is>
-          <t>1975149062e5ce6b992f64d64cd516228ceab5b0d4760dfd8a040fce4af22aeb</t>
-        </is>
-      </c>
-      <c r="BB18" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC18" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD18" s="24" t="inlineStr">
-        <is>
-          <t>1975149062e5ce6b992f64d64cd516228ceab5b0d4760dfd8a040fce4af22aeb</t>
-        </is>
-      </c>
-      <c r="BE18" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF18" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG18" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH18" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-29T12:04:07.620398Z</t>
-        </is>
-      </c>
-      <c r="BI18" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ18" s="25" t="n"/>
-      <c r="BK18" s="26" t="n">
-        <v>178</v>
-      </c>
-      <c r="BL18" s="27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BM18" s="28" t="n">
-        <v>0.359712</v>
-      </c>
-      <c r="BN18" s="28" t="n"/>
-      <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
-      <c r="BR18" s="28" t="n"/>
-      <c r="BS18" s="28" t="n"/>
-      <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="25" t="n"/>
-      <c r="BV18" s="29" t="n"/>
-      <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n"/>
-      <c r="BY18" s="27" t="n"/>
-      <c r="BZ18" s="24" t="n"/>
-      <c r="CA18" s="31" t="n"/>
-      <c r="CB18" s="24" t="n"/>
-      <c r="CC18" s="24" t="n"/>
-      <c r="CD18" s="24" t="n"/>
-      <c r="CE18" s="24" t="n"/>
-      <c r="CF18" s="24" t="n"/>
-      <c r="CG18" s="24" t="n"/>
-      <c r="CH18" s="24" t="n"/>
-      <c r="CI18" s="24" t="n"/>
-      <c r="CJ18" s="24" t="n"/>
-      <c r="CK18" s="24" t="n"/>
-      <c r="CL18" s="24" t="n"/>
-      <c r="CM18" s="24" t="n"/>
-      <c r="CN18" s="24" t="n"/>
-      <c r="CO18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>eaee9f9a4ebf4ab2</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T10:30:19.883158Z</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>63690</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
-        <is>
-          <t>Travoman Team</t>
-        </is>
-      </c>
-      <c r="G19" s="24" t="inlineStr">
-        <is>
-          <t>Stray Team</t>
-        </is>
-      </c>
-      <c r="H19" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="n"/>
-      <c r="K19" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L19" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M19" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N19" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O19" s="28" t="n">
-        <v>0.5938330000000001</v>
-      </c>
-      <c r="P19" s="28" t="n"/>
-      <c r="Q19" s="28" t="n">
-        <v>-0.046455</v>
-      </c>
-      <c r="R19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U19" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="25" t="n"/>
-      <c r="Z19" s="26" t="n"/>
-      <c r="AA19" s="28" t="n"/>
-      <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:22:51.651166Z</t>
-        </is>
-      </c>
-      <c r="AE19" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-dota2-stray-tt-2026-07-30).</t>
-        </is>
-      </c>
-      <c r="AF19" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG19" s="24" t="inlineStr">
-        <is>
-          <t>review_required</t>
-        </is>
-      </c>
-      <c r="AH19" s="24" t="n"/>
-      <c r="AI19" s="31" t="n"/>
-      <c r="AJ19" s="31" t="n"/>
-      <c r="AK19" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL19" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM19" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN19" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO19" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP19" s="24" t="inlineStr">
-        <is>
-          <t>Travoman Team</t>
-        </is>
-      </c>
-      <c r="AQ19" s="24" t="inlineStr">
-        <is>
-          <t>Travoman Team</t>
-        </is>
-      </c>
-      <c r="AR19" s="24" t="inlineStr">
-        <is>
-          <t>Travoman Team</t>
-        </is>
-      </c>
-      <c r="AS19" s="24" t="inlineStr">
-        <is>
-          <t>Stray Team</t>
-        </is>
-      </c>
-      <c r="AT19" s="24" t="inlineStr">
-        <is>
-          <t>Stray Team</t>
-        </is>
-      </c>
-      <c r="AU19" s="24" t="inlineStr">
-        <is>
-          <t>Stray Team</t>
-        </is>
-      </c>
-      <c r="AV19" s="24" t="n"/>
-      <c r="AW19" s="24" t="n"/>
-      <c r="AX19" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY19" s="24" t="n"/>
-      <c r="AZ19" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA19" s="24" t="inlineStr">
-        <is>
-          <t>3bcd1fbb498942b21a2e085eda89faf5557d0f6661ee26a8410d8dba9769a397</t>
-        </is>
-      </c>
-      <c r="BB19" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC19" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD19" s="24" t="inlineStr">
-        <is>
-          <t>3bcd1fbb498942b21a2e085eda89faf5557d0f6661ee26a8410d8dba9769a397</t>
-        </is>
-      </c>
-      <c r="BE19" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF19" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG19" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH19" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T10:30:13.504721Z</t>
-        </is>
-      </c>
-      <c r="BI19" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ19" s="25" t="n"/>
-      <c r="BK19" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL19" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM19" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN19" s="28" t="n"/>
-      <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
-      <c r="BR19" s="28" t="n"/>
-      <c r="BS19" s="28" t="n"/>
-      <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="25" t="n"/>
-      <c r="BV19" s="29" t="n"/>
-      <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="30" t="n"/>
-      <c r="BY19" s="27" t="n"/>
-      <c r="BZ19" s="24" t="n"/>
-      <c r="CA19" s="31" t="n"/>
-      <c r="CB19" s="24" t="n"/>
-      <c r="CC19" s="24" t="n"/>
-      <c r="CD19" s="24" t="n"/>
-      <c r="CE19" s="24" t="n"/>
-      <c r="CF19" s="24" t="n"/>
-      <c r="CG19" s="24" t="n"/>
-      <c r="CH19" s="24" t="n"/>
-      <c r="CI19" s="24" t="n"/>
-      <c r="CJ19" s="24" t="n"/>
-      <c r="CK19" s="24" t="n"/>
-      <c r="CL19" s="24" t="n"/>
-      <c r="CM19" s="24" t="n"/>
-      <c r="CN19" s="24" t="n"/>
-      <c r="CO19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>f72326bdda87467a</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T10:30:19.883158Z</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>63691</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F20" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="G20" s="24" t="inlineStr">
-        <is>
-          <t>Level UP</t>
-        </is>
-      </c>
-      <c r="H20" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n"/>
-      <c r="K20" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L20" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="M20" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="N20" s="28" t="n">
-        <v>0.45045</v>
-      </c>
-      <c r="O20" s="28" t="n">
-        <v>0.574553</v>
-      </c>
-      <c r="P20" s="28" t="n"/>
-      <c r="Q20" s="28" t="n">
-        <v>0.124103</v>
-      </c>
-      <c r="R20" s="26" t="n">
-        <v>82</v>
-      </c>
-      <c r="S20" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T20" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U20" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V20" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W20" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="25" t="n"/>
-      <c r="Z20" s="26" t="n"/>
-      <c r="AA20" s="28" t="n"/>
-      <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AD20" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T16:00:59.768618Z</t>
-        </is>
-      </c>
-      <c r="AE20" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lvlup-z10-2026-07-30).</t>
-        </is>
-      </c>
-      <c r="AF20" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG20" s="24" t="inlineStr">
-        <is>
-          <t>review_required</t>
-        </is>
-      </c>
-      <c r="AH20" s="24" t="n"/>
-      <c r="AI20" s="31" t="n"/>
-      <c r="AJ20" s="31" t="n"/>
-      <c r="AK20" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL20" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM20" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN20" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO20" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP20" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AQ20" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AR20" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AS20" s="24" t="inlineStr">
-        <is>
-          <t>Level UP</t>
-        </is>
-      </c>
-      <c r="AT20" s="24" t="inlineStr">
-        <is>
-          <t>Level UP</t>
-        </is>
-      </c>
-      <c r="AU20" s="24" t="inlineStr">
-        <is>
-          <t>Level UP</t>
-        </is>
-      </c>
-      <c r="AV20" s="24" t="n"/>
-      <c r="AW20" s="24" t="n"/>
-      <c r="AX20" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY20" s="24" t="n"/>
-      <c r="AZ20" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA20" s="24" t="inlineStr">
-        <is>
-          <t>3bcd1fbb498942b21a2e085eda89faf5557d0f6661ee26a8410d8dba9769a397</t>
-        </is>
-      </c>
-      <c r="BB20" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC20" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD20" s="24" t="inlineStr">
-        <is>
-          <t>3bcd1fbb498942b21a2e085eda89faf5557d0f6661ee26a8410d8dba9769a397</t>
-        </is>
-      </c>
-      <c r="BE20" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF20" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG20" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH20" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T10:30:13.979212Z</t>
-        </is>
-      </c>
-      <c r="BI20" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ20" s="25" t="n"/>
-      <c r="BK20" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="BL20" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BM20" s="28" t="n">
-        <v>0.45045</v>
-      </c>
-      <c r="BN20" s="28" t="n"/>
-      <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
-      <c r="BR20" s="28" t="n"/>
-      <c r="BS20" s="28" t="n"/>
-      <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="25" t="n"/>
-      <c r="BV20" s="29" t="n"/>
-      <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="30" t="n"/>
-      <c r="BY20" s="27" t="n"/>
-      <c r="BZ20" s="24" t="n"/>
-      <c r="CA20" s="31" t="n"/>
-      <c r="CB20" s="24" t="n"/>
-      <c r="CC20" s="24" t="n"/>
-      <c r="CD20" s="24" t="n"/>
-      <c r="CE20" s="24" t="n"/>
-      <c r="CF20" s="24" t="n"/>
-      <c r="CG20" s="24" t="n"/>
-      <c r="CH20" s="24" t="n"/>
-      <c r="CI20" s="24" t="n"/>
-      <c r="CJ20" s="24" t="n"/>
-      <c r="CK20" s="24" t="n"/>
-      <c r="CL20" s="24" t="n"/>
-      <c r="CM20" s="24" t="n"/>
-      <c r="CN20" s="24" t="n"/>
-      <c r="CO20" s="24" t="n"/>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>f7556a3a71ea4189</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T13:36:15.317500Z</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>63804</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F21" s="24" t="inlineStr">
-        <is>
-          <t>Daxak Team</t>
-        </is>
-      </c>
-      <c r="G21" s="24" t="inlineStr">
-        <is>
-          <t>avice Team</t>
-        </is>
-      </c>
-      <c r="H21" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I21" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J21" s="25" t="n"/>
-      <c r="K21" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L21" s="26" t="n">
-        <v>-194</v>
-      </c>
-      <c r="M21" s="27" t="n">
-        <v>1.515464</v>
-      </c>
-      <c r="N21" s="28" t="n">
-        <v>0.659864</v>
-      </c>
-      <c r="O21" s="28" t="n">
-        <v>0.518561</v>
-      </c>
-      <c r="P21" s="28" t="n"/>
-      <c r="Q21" s="28" t="n">
-        <v>-0.141303</v>
-      </c>
-      <c r="R21" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U21" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
-      <c r="Y21" s="25" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="28" t="n"/>
-      <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n"/>
-      <c r="AD21" s="24" t="n"/>
-      <c r="AE21" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-dota2-avi-dxk-2026-07-30).</t>
-        </is>
-      </c>
-      <c r="AF21" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG21" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH21" s="24" t="n"/>
-      <c r="AI21" s="31" t="n"/>
-      <c r="AJ21" s="31" t="n"/>
-      <c r="AK21" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL21" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM21" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN21" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO21" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP21" s="24" t="inlineStr">
-        <is>
-          <t>Daxak Team</t>
-        </is>
-      </c>
-      <c r="AQ21" s="24" t="inlineStr">
-        <is>
-          <t>Daxak Team</t>
-        </is>
-      </c>
-      <c r="AR21" s="24" t="inlineStr">
-        <is>
-          <t>Daxak Team</t>
-        </is>
-      </c>
-      <c r="AS21" s="24" t="inlineStr">
-        <is>
-          <t>avice Team</t>
-        </is>
-      </c>
-      <c r="AT21" s="24" t="inlineStr">
-        <is>
-          <t>avice Team</t>
-        </is>
-      </c>
-      <c r="AU21" s="24" t="inlineStr">
-        <is>
-          <t>avice Team</t>
-        </is>
-      </c>
-      <c r="AV21" s="24" t="n"/>
-      <c r="AW21" s="24" t="n"/>
-      <c r="AX21" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY21" s="24" t="n"/>
-      <c r="AZ21" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA21" s="24" t="inlineStr">
-        <is>
-          <t>84bbd26177707b184e5d7ceea063ce19a04245602c122da9675ab60a9329d7a7</t>
-        </is>
-      </c>
-      <c r="BB21" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC21" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD21" s="24" t="inlineStr">
-        <is>
-          <t>84bbd26177707b184e5d7ceea063ce19a04245602c122da9675ab60a9329d7a7</t>
-        </is>
-      </c>
-      <c r="BE21" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF21" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG21" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH21" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T13:36:10.465723Z</t>
-        </is>
-      </c>
-      <c r="BI21" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ21" s="25" t="n"/>
-      <c r="BK21" s="26" t="n">
-        <v>-194</v>
-      </c>
-      <c r="BL21" s="27" t="n">
-        <v>1.515464</v>
-      </c>
-      <c r="BM21" s="28" t="n">
-        <v>0.659864</v>
-      </c>
-      <c r="BN21" s="28" t="n"/>
-      <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
-      <c r="BR21" s="28" t="n"/>
-      <c r="BS21" s="28" t="n"/>
-      <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
-      <c r="BV21" s="29" t="n"/>
-      <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
-      <c r="BZ21" s="24" t="n"/>
-      <c r="CA21" s="31" t="n"/>
-      <c r="CB21" s="24" t="n"/>
-      <c r="CC21" s="24" t="n"/>
-      <c r="CD21" s="24" t="n"/>
-      <c r="CE21" s="24" t="n"/>
-      <c r="CF21" s="24" t="n"/>
-      <c r="CG21" s="24" t="n"/>
-      <c r="CH21" s="24" t="n"/>
-      <c r="CI21" s="24" t="n"/>
-      <c r="CJ21" s="24" t="n"/>
-      <c r="CK21" s="24" t="n"/>
-      <c r="CL21" s="24" t="n"/>
-      <c r="CM21" s="24" t="n"/>
-      <c r="CN21" s="24" t="n"/>
-      <c r="CO21" s="24" t="n"/>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>2b2794497c3a4977</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.381240Z</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>64035</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
-        <is>
-          <t>Ilbirs eSports</t>
-        </is>
-      </c>
-      <c r="G22" s="24" t="inlineStr">
-        <is>
-          <t>Amaru Gaming</t>
-        </is>
-      </c>
-      <c r="H22" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I22" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L22" s="26" t="n">
-        <v>-203</v>
-      </c>
-      <c r="M22" s="27" t="n">
-        <v>1.492611</v>
-      </c>
-      <c r="N22" s="28" t="n">
-        <v>0.669967</v>
-      </c>
-      <c r="O22" s="28" t="n">
-        <v>0.525766</v>
-      </c>
-      <c r="P22" s="28" t="n"/>
-      <c r="Q22" s="28" t="n">
-        <v>-0.144201</v>
-      </c>
-      <c r="R22" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U22" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V22" s="24" t="n"/>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
-      <c r="Y22" s="25" t="n"/>
-      <c r="Z22" s="26" t="n"/>
-      <c r="AA22" s="28" t="n"/>
-      <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n"/>
-      <c r="AD22" s="24" t="n"/>
-      <c r="AE22" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-agm-ill-2026-07-30).</t>
-        </is>
-      </c>
-      <c r="AF22" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG22" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH22" s="24" t="n"/>
-      <c r="AI22" s="31" t="n"/>
-      <c r="AJ22" s="31" t="n"/>
-      <c r="AK22" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL22" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM22" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN22" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO22" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP22" s="24" t="inlineStr">
-        <is>
-          <t>Ilbirs eSports</t>
-        </is>
-      </c>
-      <c r="AQ22" s="24" t="inlineStr">
-        <is>
-          <t>Ilbirs eSports</t>
-        </is>
-      </c>
-      <c r="AR22" s="24" t="inlineStr">
-        <is>
-          <t>Ilbirs eSports</t>
-        </is>
-      </c>
-      <c r="AS22" s="24" t="inlineStr">
-        <is>
-          <t>Amaru Gaming</t>
-        </is>
-      </c>
-      <c r="AT22" s="24" t="inlineStr">
-        <is>
-          <t>Amaru Gaming</t>
-        </is>
-      </c>
-      <c r="AU22" s="24" t="inlineStr">
-        <is>
-          <t>Amaru Gaming</t>
-        </is>
-      </c>
-      <c r="AV22" s="24" t="n"/>
-      <c r="AW22" s="24" t="n"/>
-      <c r="AX22" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY22" s="24" t="n"/>
-      <c r="AZ22" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA22" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BB22" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC22" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD22" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BE22" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF22" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG22" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH22" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:51.801402Z</t>
-        </is>
-      </c>
-      <c r="BI22" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ22" s="25" t="n"/>
-      <c r="BK22" s="26" t="n">
-        <v>-203</v>
-      </c>
-      <c r="BL22" s="27" t="n">
-        <v>1.492611</v>
-      </c>
-      <c r="BM22" s="28" t="n">
-        <v>0.669967</v>
-      </c>
-      <c r="BN22" s="28" t="n"/>
-      <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
-      <c r="BR22" s="28" t="n"/>
-      <c r="BS22" s="28" t="n"/>
-      <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
-      <c r="BV22" s="29" t="n"/>
-      <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
-      <c r="BZ22" s="24" t="n"/>
-      <c r="CA22" s="31" t="n"/>
-      <c r="CB22" s="24" t="n"/>
-      <c r="CC22" s="24" t="n"/>
-      <c r="CD22" s="24" t="n"/>
-      <c r="CE22" s="24" t="n"/>
-      <c r="CF22" s="24" t="n"/>
-      <c r="CG22" s="24" t="n"/>
-      <c r="CH22" s="24" t="n"/>
-      <c r="CI22" s="24" t="n"/>
-      <c r="CJ22" s="24" t="n"/>
-      <c r="CK22" s="24" t="n"/>
-      <c r="CL22" s="24" t="n"/>
-      <c r="CM22" s="24" t="n"/>
-      <c r="CN22" s="24" t="n"/>
-      <c r="CO22" s="24" t="n"/>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>3b298e369eba4fea</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.381240Z</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>64671</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
-        <is>
-          <t>Midas Club</t>
-        </is>
-      </c>
-      <c r="G23" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="H23" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I23" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L23" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="M23" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="N23" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="O23" s="28" t="n">
-        <v>0.747717</v>
-      </c>
-      <c r="P23" s="28" t="n"/>
-      <c r="Q23" s="28" t="n">
-        <v>0.127945</v>
-      </c>
-      <c r="R23" s="26" t="n">
-        <v>84</v>
-      </c>
-      <c r="S23" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U23" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V23" s="24" t="n"/>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
-      <c r="Y23" s="25" t="n"/>
-      <c r="Z23" s="26" t="n"/>
-      <c r="AA23" s="28" t="n"/>
-      <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n"/>
-      <c r="AD23" s="24" t="n"/>
-      <c r="AE23" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-dota2-re-midas-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF23" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG23" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH23" s="24" t="n"/>
-      <c r="AI23" s="31" t="n"/>
-      <c r="AJ23" s="31" t="n"/>
-      <c r="AK23" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL23" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM23" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN23" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO23" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP23" s="24" t="inlineStr">
-        <is>
-          <t>Midas Club</t>
-        </is>
-      </c>
-      <c r="AQ23" s="24" t="inlineStr">
-        <is>
-          <t>Midas Club</t>
-        </is>
-      </c>
-      <c r="AR23" s="24" t="inlineStr">
-        <is>
-          <t>Midas Club</t>
-        </is>
-      </c>
-      <c r="AS23" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AT23" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AU23" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AV23" s="24" t="n"/>
-      <c r="AW23" s="24" t="n"/>
-      <c r="AX23" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY23" s="24" t="n"/>
-      <c r="AZ23" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA23" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BB23" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC23" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD23" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BE23" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF23" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG23" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH23" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:52.434355Z</t>
-        </is>
-      </c>
-      <c r="BI23" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ23" s="25" t="n"/>
-      <c r="BK23" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="BL23" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="BM23" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="BN23" s="28" t="n"/>
-      <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
-      <c r="BR23" s="28" t="n"/>
-      <c r="BS23" s="28" t="n"/>
-      <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="25" t="n"/>
-      <c r="BV23" s="29" t="n"/>
-      <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n"/>
-      <c r="BY23" s="27" t="n"/>
-      <c r="BZ23" s="24" t="n"/>
-      <c r="CA23" s="31" t="n"/>
-      <c r="CB23" s="24" t="n"/>
-      <c r="CC23" s="24" t="n"/>
-      <c r="CD23" s="24" t="n"/>
-      <c r="CE23" s="24" t="n"/>
-      <c r="CF23" s="24" t="n"/>
-      <c r="CG23" s="24" t="n"/>
-      <c r="CH23" s="24" t="n"/>
-      <c r="CI23" s="24" t="n"/>
-      <c r="CJ23" s="24" t="n"/>
-      <c r="CK23" s="24" t="n"/>
-      <c r="CL23" s="24" t="n"/>
-      <c r="CM23" s="24" t="n"/>
-      <c r="CN23" s="24" t="n"/>
-      <c r="CO23" s="24" t="n"/>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>25e9bd707d764016</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.381240Z</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr">
-        <is>
-          <t>64672</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F24" s="24" t="inlineStr">
-        <is>
-          <t>Execration</t>
-        </is>
-      </c>
-      <c r="G24" s="24" t="inlineStr">
-        <is>
-          <t>Yellow Submarine</t>
-        </is>
-      </c>
-      <c r="H24" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I24" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J24" s="25" t="n"/>
-      <c r="K24" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L24" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="M24" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="N24" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="O24" s="28" t="n">
-        <v>0.598287</v>
-      </c>
-      <c r="P24" s="28" t="n"/>
-      <c r="Q24" s="28" t="n">
-        <v>0.048737</v>
-      </c>
-      <c r="R24" s="26" t="n">
-        <v>44</v>
-      </c>
-      <c r="S24" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T24" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U24" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
-      <c r="Y24" s="25" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="28" t="n"/>
-      <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="24" t="n"/>
-      <c r="AE24" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-dota2-yes-xctn-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF24" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG24" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH24" s="24" t="n"/>
-      <c r="AI24" s="31" t="n"/>
-      <c r="AJ24" s="31" t="n"/>
-      <c r="AK24" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL24" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM24" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN24" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO24" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP24" s="24" t="inlineStr">
-        <is>
-          <t>Execration</t>
-        </is>
-      </c>
-      <c r="AQ24" s="24" t="inlineStr">
-        <is>
-          <t>Execration</t>
-        </is>
-      </c>
-      <c r="AR24" s="24" t="inlineStr">
-        <is>
-          <t>Execration</t>
-        </is>
-      </c>
-      <c r="AS24" s="24" t="inlineStr">
-        <is>
-          <t>Yellow Submarine</t>
-        </is>
-      </c>
-      <c r="AT24" s="24" t="inlineStr">
-        <is>
-          <t>Yellow Submarine</t>
-        </is>
-      </c>
-      <c r="AU24" s="24" t="inlineStr">
-        <is>
-          <t>Yellow Submarine</t>
-        </is>
-      </c>
-      <c r="AV24" s="24" t="n"/>
-      <c r="AW24" s="24" t="n"/>
-      <c r="AX24" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY24" s="24" t="n"/>
-      <c r="AZ24" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA24" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BB24" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC24" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD24" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BE24" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF24" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG24" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH24" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:52.965080Z</t>
-        </is>
-      </c>
-      <c r="BI24" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ24" s="25" t="n"/>
-      <c r="BK24" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="BL24" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="BM24" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="BN24" s="28" t="n"/>
-      <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
-      <c r="BR24" s="28" t="n"/>
-      <c r="BS24" s="28" t="n"/>
-      <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="25" t="n"/>
-      <c r="BV24" s="29" t="n"/>
-      <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="30" t="n"/>
-      <c r="BY24" s="27" t="n"/>
-      <c r="BZ24" s="24" t="n"/>
-      <c r="CA24" s="31" t="n"/>
-      <c r="CB24" s="24" t="n"/>
-      <c r="CC24" s="24" t="n"/>
-      <c r="CD24" s="24" t="n"/>
-      <c r="CE24" s="24" t="n"/>
-      <c r="CF24" s="24" t="n"/>
-      <c r="CG24" s="24" t="n"/>
-      <c r="CH24" s="24" t="n"/>
-      <c r="CI24" s="24" t="n"/>
-      <c r="CJ24" s="24" t="n"/>
-      <c r="CK24" s="24" t="n"/>
-      <c r="CL24" s="24" t="n"/>
-      <c r="CM24" s="24" t="n"/>
-      <c r="CN24" s="24" t="n"/>
-      <c r="CO24" s="24" t="n"/>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>5064bad801864474</t>
-        </is>
-      </c>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.381240Z</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>64735</t>
-        </is>
-      </c>
-      <c r="E25" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F25" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="G25" s="24" t="inlineStr">
-        <is>
-          <t>Team Resilience</t>
-        </is>
-      </c>
-      <c r="H25" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I25" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J25" s="25" t="n"/>
-      <c r="K25" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L25" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M25" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N25" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O25" s="28" t="n">
-        <v>0.6120679999999999</v>
-      </c>
-      <c r="P25" s="28" t="n"/>
-      <c r="Q25" s="28" t="n">
-        <v>0.021904</v>
-      </c>
-      <c r="R25" s="26" t="n">
-        <v>31</v>
-      </c>
-      <c r="S25" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T25" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U25" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
-      <c r="Y25" s="25" t="n"/>
-      <c r="Z25" s="26" t="n"/>
-      <c r="AA25" s="28" t="n"/>
-      <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n"/>
-      <c r="AD25" s="24" t="n"/>
-      <c r="AE25" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-tr-pla-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF25" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG25" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH25" s="24" t="n"/>
-      <c r="AI25" s="31" t="n"/>
-      <c r="AJ25" s="31" t="n"/>
-      <c r="AK25" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL25" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM25" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN25" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO25" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP25" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AQ25" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AR25" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AS25" s="24" t="inlineStr">
-        <is>
-          <t>Team Resilience</t>
-        </is>
-      </c>
-      <c r="AT25" s="24" t="inlineStr">
-        <is>
-          <t>Team Resilience</t>
-        </is>
-      </c>
-      <c r="AU25" s="24" t="inlineStr">
-        <is>
-          <t>Team Resilience</t>
-        </is>
-      </c>
-      <c r="AV25" s="24" t="n"/>
-      <c r="AW25" s="24" t="n"/>
-      <c r="AX25" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY25" s="24" t="n"/>
-      <c r="AZ25" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA25" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BB25" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC25" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD25" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BE25" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF25" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG25" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH25" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:53.524510Z</t>
-        </is>
-      </c>
-      <c r="BI25" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ25" s="25" t="n"/>
-      <c r="BK25" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL25" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM25" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN25" s="28" t="n"/>
-      <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
-      <c r="BR25" s="28" t="n"/>
-      <c r="BS25" s="28" t="n"/>
-      <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="25" t="n"/>
-      <c r="BV25" s="29" t="n"/>
-      <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="30" t="n"/>
-      <c r="BY25" s="27" t="n"/>
-      <c r="BZ25" s="24" t="n"/>
-      <c r="CA25" s="31" t="n"/>
-      <c r="CB25" s="24" t="n"/>
-      <c r="CC25" s="24" t="n"/>
-      <c r="CD25" s="24" t="n"/>
-      <c r="CE25" s="24" t="n"/>
-      <c r="CF25" s="24" t="n"/>
-      <c r="CG25" s="24" t="n"/>
-      <c r="CH25" s="24" t="n"/>
-      <c r="CI25" s="24" t="n"/>
-      <c r="CJ25" s="24" t="n"/>
-      <c r="CK25" s="24" t="n"/>
-      <c r="CL25" s="24" t="n"/>
-      <c r="CM25" s="24" t="n"/>
-      <c r="CN25" s="24" t="n"/>
-      <c r="CO25" s="24" t="n"/>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>a49da12ebbb040ab</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.381240Z</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>64817</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
-        <is>
-          <t>REKONIX</t>
-        </is>
-      </c>
-      <c r="G26" s="24" t="inlineStr">
-        <is>
-          <t>L1ga Team</t>
-        </is>
-      </c>
-      <c r="H26" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I26" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J26" s="25" t="n"/>
-      <c r="K26" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L26" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M26" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N26" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O26" s="28" t="n">
-        <v>0.501185</v>
-      </c>
-      <c r="P26" s="28" t="n"/>
-      <c r="Q26" s="28" t="n">
-        <v>-0.088979</v>
-      </c>
-      <c r="R26" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U26" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
-      <c r="Y26" s="25" t="n"/>
-      <c r="Z26" s="26" t="n"/>
-      <c r="AA26" s="28" t="n"/>
-      <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
-      <c r="AE26" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-l1ga-rnx-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF26" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG26" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH26" s="24" t="n"/>
-      <c r="AI26" s="31" t="n"/>
-      <c r="AJ26" s="31" t="n"/>
-      <c r="AK26" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL26" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM26" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN26" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO26" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP26" s="24" t="inlineStr">
-        <is>
-          <t>REKONIX</t>
-        </is>
-      </c>
-      <c r="AQ26" s="24" t="inlineStr">
-        <is>
-          <t>REKONIX</t>
-        </is>
-      </c>
-      <c r="AR26" s="24" t="inlineStr">
-        <is>
-          <t>REKONIX</t>
-        </is>
-      </c>
-      <c r="AS26" s="24" t="inlineStr">
-        <is>
-          <t>L1ga Team</t>
-        </is>
-      </c>
-      <c r="AT26" s="24" t="inlineStr">
-        <is>
-          <t>L1ga Team</t>
-        </is>
-      </c>
-      <c r="AU26" s="24" t="inlineStr">
-        <is>
-          <t>L1ga Team</t>
-        </is>
-      </c>
-      <c r="AV26" s="24" t="n"/>
-      <c r="AW26" s="24" t="n"/>
-      <c r="AX26" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY26" s="24" t="n"/>
-      <c r="AZ26" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA26" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BB26" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC26" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD26" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BE26" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF26" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG26" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH26" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:54.685605Z</t>
-        </is>
-      </c>
-      <c r="BI26" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ26" s="25" t="n"/>
-      <c r="BK26" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL26" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM26" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN26" s="28" t="n"/>
-      <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
-      <c r="BR26" s="28" t="n"/>
-      <c r="BS26" s="28" t="n"/>
-      <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="25" t="n"/>
-      <c r="BV26" s="29" t="n"/>
-      <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="30" t="n"/>
-      <c r="BY26" s="27" t="n"/>
-      <c r="BZ26" s="24" t="n"/>
-      <c r="CA26" s="31" t="n"/>
-      <c r="CB26" s="24" t="n"/>
-      <c r="CC26" s="24" t="n"/>
-      <c r="CD26" s="24" t="n"/>
-      <c r="CE26" s="24" t="n"/>
-      <c r="CF26" s="24" t="n"/>
-      <c r="CG26" s="24" t="n"/>
-      <c r="CH26" s="24" t="n"/>
-      <c r="CI26" s="24" t="n"/>
-      <c r="CJ26" s="24" t="n"/>
-      <c r="CK26" s="24" t="n"/>
-      <c r="CL26" s="24" t="n"/>
-      <c r="CM26" s="24" t="n"/>
-      <c r="CN26" s="24" t="n"/>
-      <c r="CO26" s="24" t="n"/>
-    </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>0246944d3a3f4a93</t>
-        </is>
-      </c>
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.381240Z</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>64818</t>
-        </is>
-      </c>
-      <c r="E27" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="G27" s="24" t="inlineStr">
-        <is>
-          <t>Enjoy</t>
-        </is>
-      </c>
-      <c r="H27" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I27" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J27" s="25" t="n"/>
-      <c r="K27" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L27" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="M27" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="N27" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="O27" s="28" t="n">
-        <v>0.605405</v>
-      </c>
-      <c r="P27" s="28" t="n"/>
-      <c r="Q27" s="28" t="n">
-        <v>0.144576</v>
-      </c>
-      <c r="R27" s="26" t="n">
-        <v>92</v>
-      </c>
-      <c r="S27" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T27" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U27" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
-      <c r="Y27" s="25" t="n"/>
-      <c r="Z27" s="26" t="n"/>
-      <c r="AA27" s="28" t="n"/>
-      <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
-      <c r="AE27" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-dota2-enjoy-glyph-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF27" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG27" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH27" s="24" t="n"/>
-      <c r="AI27" s="31" t="n"/>
-      <c r="AJ27" s="31" t="n"/>
-      <c r="AK27" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL27" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM27" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN27" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO27" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP27" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AQ27" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AR27" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AS27" s="24" t="inlineStr">
-        <is>
-          <t>Enjoy</t>
-        </is>
-      </c>
-      <c r="AT27" s="24" t="inlineStr">
-        <is>
-          <t>Enjoy</t>
-        </is>
-      </c>
-      <c r="AU27" s="24" t="inlineStr">
-        <is>
-          <t>Enjoy</t>
-        </is>
-      </c>
-      <c r="AV27" s="24" t="n"/>
-      <c r="AW27" s="24" t="n"/>
-      <c r="AX27" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY27" s="24" t="n"/>
-      <c r="AZ27" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA27" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BB27" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC27" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD27" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BE27" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF27" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG27" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH27" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:55.261695Z</t>
-        </is>
-      </c>
-      <c r="BI27" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ27" s="25" t="n"/>
-      <c r="BK27" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="BL27" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM27" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="BN27" s="28" t="n"/>
-      <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
-      <c r="BR27" s="28" t="n"/>
-      <c r="BS27" s="28" t="n"/>
-      <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="25" t="n"/>
-      <c r="BV27" s="29" t="n"/>
-      <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="30" t="n"/>
-      <c r="BY27" s="27" t="n"/>
-      <c r="BZ27" s="24" t="n"/>
-      <c r="CA27" s="31" t="n"/>
-      <c r="CB27" s="24" t="n"/>
-      <c r="CC27" s="24" t="n"/>
-      <c r="CD27" s="24" t="n"/>
-      <c r="CE27" s="24" t="n"/>
-      <c r="CF27" s="24" t="n"/>
-      <c r="CG27" s="24" t="n"/>
-      <c r="CH27" s="24" t="n"/>
-      <c r="CI27" s="24" t="n"/>
-      <c r="CJ27" s="24" t="n"/>
-      <c r="CK27" s="24" t="n"/>
-      <c r="CL27" s="24" t="n"/>
-      <c r="CM27" s="24" t="n"/>
-      <c r="CN27" s="24" t="n"/>
-      <c r="CO27" s="24" t="n"/>
-    </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
-        <is>
-          <t>c589d484f454480a</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.381240Z</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="inlineStr">
-        <is>
-          <t>64928</t>
-        </is>
-      </c>
-      <c r="E28" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F28" s="24" t="inlineStr">
-        <is>
-          <t>LGD Gaming</t>
-        </is>
-      </c>
-      <c r="G28" s="24" t="inlineStr">
-        <is>
-          <t>Xtreme Gaming</t>
-        </is>
-      </c>
-      <c r="H28" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I28" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J28" s="25" t="n"/>
-      <c r="K28" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L28" s="26" t="n">
-        <v>-170</v>
-      </c>
-      <c r="M28" s="27" t="n">
-        <v>1.588235</v>
-      </c>
-      <c r="N28" s="28" t="n">
-        <v>0.62963</v>
-      </c>
-      <c r="O28" s="28" t="n">
-        <v>0.70634</v>
-      </c>
-      <c r="P28" s="28" t="n"/>
-      <c r="Q28" s="28" t="n">
-        <v>0.07671</v>
-      </c>
-      <c r="R28" s="26" t="n">
-        <v>58</v>
-      </c>
-      <c r="S28" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U28" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V28" s="24" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
-      <c r="Y28" s="25" t="n"/>
-      <c r="Z28" s="26" t="n"/>
-      <c r="AA28" s="28" t="n"/>
-      <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n"/>
-      <c r="AD28" s="24" t="n"/>
-      <c r="AE28" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-xtreme-lgd-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF28" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG28" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH28" s="24" t="n"/>
-      <c r="AI28" s="31" t="n"/>
-      <c r="AJ28" s="31" t="n"/>
-      <c r="AK28" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL28" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM28" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN28" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO28" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP28" s="24" t="inlineStr">
-        <is>
-          <t>LGD Gaming</t>
-        </is>
-      </c>
-      <c r="AQ28" s="24" t="inlineStr">
-        <is>
-          <t>LGD Gaming</t>
-        </is>
-      </c>
-      <c r="AR28" s="24" t="inlineStr">
-        <is>
-          <t>LGD Gaming</t>
-        </is>
-      </c>
-      <c r="AS28" s="24" t="inlineStr">
-        <is>
-          <t>Xtreme Gaming</t>
-        </is>
-      </c>
-      <c r="AT28" s="24" t="inlineStr">
-        <is>
-          <t>Xtreme Gaming</t>
-        </is>
-      </c>
-      <c r="AU28" s="24" t="inlineStr">
-        <is>
-          <t>Xtreme Gaming</t>
-        </is>
-      </c>
-      <c r="AV28" s="24" t="n"/>
-      <c r="AW28" s="24" t="n"/>
-      <c r="AX28" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY28" s="24" t="n"/>
-      <c r="AZ28" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA28" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BB28" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC28" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD28" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BE28" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF28" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG28" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH28" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:55.839894Z</t>
-        </is>
-      </c>
-      <c r="BI28" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ28" s="25" t="n"/>
-      <c r="BK28" s="26" t="n">
-        <v>-170</v>
-      </c>
-      <c r="BL28" s="27" t="n">
-        <v>1.588235</v>
-      </c>
-      <c r="BM28" s="28" t="n">
-        <v>0.62963</v>
-      </c>
-      <c r="BN28" s="28" t="n"/>
-      <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="25" t="n"/>
-      <c r="BQ28" s="27" t="n"/>
-      <c r="BR28" s="28" t="n"/>
-      <c r="BS28" s="28" t="n"/>
-      <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="25" t="n"/>
-      <c r="BV28" s="29" t="n"/>
-      <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="30" t="n"/>
-      <c r="BY28" s="27" t="n"/>
-      <c r="BZ28" s="24" t="n"/>
-      <c r="CA28" s="31" t="n"/>
-      <c r="CB28" s="24" t="n"/>
-      <c r="CC28" s="24" t="n"/>
-      <c r="CD28" s="24" t="n"/>
-      <c r="CE28" s="24" t="n"/>
-      <c r="CF28" s="24" t="n"/>
-      <c r="CG28" s="24" t="n"/>
-      <c r="CH28" s="24" t="n"/>
-      <c r="CI28" s="24" t="n"/>
-      <c r="CJ28" s="24" t="n"/>
-      <c r="CK28" s="24" t="n"/>
-      <c r="CL28" s="24" t="n"/>
-      <c r="CM28" s="24" t="n"/>
-      <c r="CN28" s="24" t="n"/>
-      <c r="CO28" s="24" t="n"/>
-    </row>
-    <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
-        <is>
-          <t>d3c607e7406640ec</t>
-        </is>
-      </c>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.381240Z</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="inlineStr">
-        <is>
-          <t>64929</t>
-        </is>
-      </c>
-      <c r="E29" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F29" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="G29" s="24" t="inlineStr">
-        <is>
-          <t>Yakult Brothers</t>
-        </is>
-      </c>
-      <c r="H29" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I29" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J29" s="25" t="n"/>
-      <c r="K29" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L29" s="26" t="n">
-        <v>186</v>
-      </c>
-      <c r="M29" s="27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="N29" s="28" t="n">
-        <v>0.34965</v>
-      </c>
-      <c r="O29" s="28" t="n">
-        <v>0.611965</v>
-      </c>
-      <c r="P29" s="28" t="n"/>
-      <c r="Q29" s="28" t="n">
-        <v>0.262315</v>
-      </c>
-      <c r="R29" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S29" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T29" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U29" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V29" s="24" t="n"/>
-      <c r="W29" s="26" t="n"/>
-      <c r="X29" s="26" t="n"/>
-      <c r="Y29" s="25" t="n"/>
-      <c r="Z29" s="26" t="n"/>
-      <c r="AA29" s="28" t="n"/>
-      <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n"/>
-      <c r="AD29" s="24" t="n"/>
-      <c r="AE29" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-dota2-yb-z10-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF29" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG29" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH29" s="24" t="n"/>
-      <c r="AI29" s="31" t="n"/>
-      <c r="AJ29" s="31" t="n"/>
-      <c r="AK29" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL29" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM29" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN29" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO29" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP29" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AQ29" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AR29" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AS29" s="24" t="inlineStr">
-        <is>
-          <t>Yakult Brothers</t>
-        </is>
-      </c>
-      <c r="AT29" s="24" t="inlineStr">
-        <is>
-          <t>Yakult Brothers</t>
-        </is>
-      </c>
-      <c r="AU29" s="24" t="inlineStr">
-        <is>
-          <t>Yakult Brothers</t>
-        </is>
-      </c>
-      <c r="AV29" s="24" t="n"/>
-      <c r="AW29" s="24" t="n"/>
-      <c r="AX29" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY29" s="24" t="n"/>
-      <c r="AZ29" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA29" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BB29" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC29" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD29" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BE29" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF29" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG29" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH29" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.380308Z</t>
-        </is>
-      </c>
-      <c r="BI29" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ29" s="25" t="n"/>
-      <c r="BK29" s="26" t="n">
-        <v>186</v>
-      </c>
-      <c r="BL29" s="27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BM29" s="28" t="n">
-        <v>0.34965</v>
-      </c>
-      <c r="BN29" s="28" t="n"/>
-      <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="25" t="n"/>
-      <c r="BQ29" s="27" t="n"/>
-      <c r="BR29" s="28" t="n"/>
-      <c r="BS29" s="28" t="n"/>
-      <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="25" t="n"/>
-      <c r="BV29" s="29" t="n"/>
-      <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="30" t="n"/>
-      <c r="BY29" s="27" t="n"/>
-      <c r="BZ29" s="24" t="n"/>
-      <c r="CA29" s="31" t="n"/>
-      <c r="CB29" s="24" t="n"/>
-      <c r="CC29" s="24" t="n"/>
-      <c r="CD29" s="24" t="n"/>
-      <c r="CE29" s="24" t="n"/>
-      <c r="CF29" s="24" t="n"/>
-      <c r="CG29" s="24" t="n"/>
-      <c r="CH29" s="24" t="n"/>
-      <c r="CI29" s="24" t="n"/>
-      <c r="CJ29" s="24" t="n"/>
-      <c r="CK29" s="24" t="n"/>
-      <c r="CL29" s="24" t="n"/>
-      <c r="CM29" s="24" t="n"/>
-      <c r="CN29" s="24" t="n"/>
-      <c r="CO29" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO15" headerRowCount="1">
-  <autoFilter ref="A1:CO15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO17" headerRowCount="1">
+  <autoFilter ref="A1:CO17"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$15)</f>
+        <f>COUNTA('Picks'!$A$2:$A$17)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$17,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$17,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")/(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$17)/SUM('Picks'!$BX$2:$BX$17),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$15)</f>
+        <f>SUM('Picks'!$BY$2:$BY$17)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$17,"&lt;&gt;",'Picks'!$AB$2:$AB$17),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$17,'Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO15"/>
+  <dimension ref="A1:CO17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5263,12 +5263,12 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>561c588bbefe48c3</t>
+          <t>961c76b983e44d0f</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:30.033213Z</t>
+          <t>2026-08-02T07:16:32.312595Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -5313,23 +5313,23 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>-104</v>
+        <v>127</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>1.961538</v>
+        <v>2.27</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.440529</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.576057</v>
+        <v>0.576085</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.06625300000000001</v>
+        <v>0.135556</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="S15" s="29" t="n">
         <v>1.25</v>
@@ -5355,7 +5355,7 @@
       <c r="AD15" s="24" t="n"/>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-dota2-yes-tr-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-dota2-yes-tr-2026-08-02).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>65b8f79741d3dcd1d060bb1f14ea0523262331890046cd8c8cccbede889da72c</t>
+          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>65b8f79741d3dcd1d060bb1f14ea0523262331890046cd8c8cccbede889da72c</t>
+          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:29.070923Z</t>
+          <t>2026-08-02T07:16:30.813424Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5484,13 +5484,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>-104</v>
+        <v>127</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>1.961538</v>
+        <v>2.27</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.440529</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5521,6 +5521,528 @@
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
     </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>07d0365ef8b4453f</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:32.312595Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>69232</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>REKONIX</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.702765</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.212569</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-dota2-rnx-yb-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>REKONIX</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>REKONIX</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>REKONIX</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:31.369505Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>5988c54f87f4472f</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:32.312595Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>69337</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.594749</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>0.004585</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="n"/>
+      <c r="W17" s="26" t="n"/>
+      <c r="X17" s="26" t="n"/>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n"/>
+      <c r="AD17" s="24" t="n"/>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-stray-ns-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>NS Team</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>Stray Team</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:31.843066Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -5524,12 +5524,12 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>07d0365ef8b4453f</t>
+          <t>d3452e106eed4a11</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:32.312595Z</t>
+          <t>2026-08-02T08:19:44.224670Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
+          <t>ba371790eb45b92bbd2fbfe5a33bbaab7ea5a0f07509006df65e77e32545f142</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
+          <t>ba371790eb45b92bbd2fbfe5a33bbaab7ea5a0f07509006df65e77e32545f142</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:31.369505Z</t>
+          <t>2026-08-02T08:19:43.195542Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5785,12 +5785,12 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>5988c54f87f4472f</t>
+          <t>2e76a6befe484819</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:32.312595Z</t>
+          <t>2026-08-02T08:19:44.224670Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -5835,23 +5835,23 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-144</v>
+        <v>-156</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.641026</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.609375</v>
       </c>
       <c r="O17" s="28" t="n">
         <v>0.594749</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>0.004585</v>
+        <v>-0.014626</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="S17" s="29" t="n">
         <v>1.25</v>
@@ -5877,7 +5877,7 @@
       <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-stray-ns-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-stray-ns-2026-08-02).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
+          <t>ba371790eb45b92bbd2fbfe5a33bbaab7ea5a0f07509006df65e77e32545f142</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
+          <t>ba371790eb45b92bbd2fbfe5a33bbaab7ea5a0f07509006df65e77e32545f142</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:31.843066Z</t>
+          <t>2026-08-02T08:19:43.755030Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6006,13 +6006,13 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-144</v>
+        <v>-156</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.641026</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.609375</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -5524,12 +5524,12 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>d3452e106eed4a11</t>
+          <t>a66a28305cd640a1</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:44.224670Z</t>
+          <t>2026-08-02T10:00:11.648885Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>69232</t>
+          <t>69337</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>NS Team</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>REKONIX</t>
+          <t>Stray Team</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -5574,26 +5574,26 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>104</v>
+        <v>-156</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>2.04</v>
+        <v>1.641026</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.609375</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.702765</v>
+        <v>0.594749</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.212569</v>
+        <v>-0.014626</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T16" s="24" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
       <c r="AD16" s="24" t="n"/>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-dota2-rnx-yb-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-stray-ns-2026-08-02).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5634,7 +5634,7 @@
       <c r="AJ16" s="31" t="n"/>
       <c r="AK16" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL16" s="26" t="n">
@@ -5642,47 +5642,47 @@
       </c>
       <c r="AM16" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN16" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO16" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP16" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>NS Team</t>
         </is>
       </c>
       <c r="AQ16" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>NS Team</t>
         </is>
       </c>
       <c r="AR16" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>NS Team</t>
         </is>
       </c>
       <c r="AS16" s="24" t="inlineStr">
         <is>
-          <t>REKONIX</t>
+          <t>Stray Team</t>
         </is>
       </c>
       <c r="AT16" s="24" t="inlineStr">
         <is>
-          <t>REKONIX</t>
+          <t>Stray Team</t>
         </is>
       </c>
       <c r="AU16" s="24" t="inlineStr">
         <is>
-          <t>REKONIX</t>
+          <t>Stray Team</t>
         </is>
       </c>
       <c r="AV16" s="24" t="n"/>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>ba371790eb45b92bbd2fbfe5a33bbaab7ea5a0f07509006df65e77e32545f142</t>
+          <t>d60687e602976b4a2779a4ff6a5f8f825a178fa4df1e53dc8ee5e3eeffcc3d8b</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>ba371790eb45b92bbd2fbfe5a33bbaab7ea5a0f07509006df65e77e32545f142</t>
+          <t>d60687e602976b4a2779a4ff6a5f8f825a178fa4df1e53dc8ee5e3eeffcc3d8b</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:43.195542Z</t>
+          <t>2026-08-02T10:00:10.104239Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5745,13 +5745,13 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>104</v>
+        <v>-156</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>2.04</v>
+        <v>1.641026</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.609375</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
@@ -5785,12 +5785,12 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>2e76a6befe484819</t>
+          <t>32020a9dad6e4660</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:44.224670Z</t>
+          <t>2026-08-02T10:00:11.648885Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>69337</t>
+          <t>69232</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>Stray Team</t>
+          <t>REKONIX</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -5835,26 +5835,26 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-156</v>
+        <v>104</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.641026</v>
+        <v>2.04</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.490196</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.594749</v>
+        <v>0.702765</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>-0.014626</v>
+        <v>0.212569</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
       <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-stray-ns-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-dota2-rnx-yb-2026-08-02).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -5895,7 +5895,7 @@
       <c r="AJ17" s="31" t="n"/>
       <c r="AK17" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL17" s="26" t="n">
@@ -5903,47 +5903,47 @@
       </c>
       <c r="AM17" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN17" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO17" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP17" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AQ17" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AR17" s="24" t="inlineStr">
         <is>
-          <t>NS Team</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AS17" s="24" t="inlineStr">
         <is>
-          <t>Stray Team</t>
+          <t>REKONIX</t>
         </is>
       </c>
       <c r="AT17" s="24" t="inlineStr">
         <is>
-          <t>Stray Team</t>
+          <t>REKONIX</t>
         </is>
       </c>
       <c r="AU17" s="24" t="inlineStr">
         <is>
-          <t>Stray Team</t>
+          <t>REKONIX</t>
         </is>
       </c>
       <c r="AV17" s="24" t="n"/>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>ba371790eb45b92bbd2fbfe5a33bbaab7ea5a0f07509006df65e77e32545f142</t>
+          <t>d60687e602976b4a2779a4ff6a5f8f825a178fa4df1e53dc8ee5e3eeffcc3d8b</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>ba371790eb45b92bbd2fbfe5a33bbaab7ea5a0f07509006df65e77e32545f142</t>
+          <t>d60687e602976b4a2779a4ff6a5f8f825a178fa4df1e53dc8ee5e3eeffcc3d8b</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:43.755030Z</t>
+          <t>2026-08-02T10:00:10.645047Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6006,13 +6006,13 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-156</v>
+        <v>104</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.641026</v>
+        <v>2.04</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.490196</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO17" headerRowCount="1">
-  <autoFilter ref="A1:CO17"/>
-  <tableColumns count="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP18" headerRowCount="1">
+  <autoFilter ref="A1:CP18"/>
+  <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,6 +396,7 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
+    <tableColumn id="94" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -752,19 +753,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$17)</f>
+        <f>COUNTA('Picks'!$A$2:$A$18)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$17,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$18,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +793,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$17,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$18,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")/(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")/(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$17)/SUM('Picks'!$BX$2:$BX$17),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$18)/SUM('Picks'!$BX$2:$BX$18),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +833,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$17)</f>
+        <f>SUM('Picks'!$BY$2:$BY$18)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$17,"&lt;&gt;",'Picks'!$AB$2:$AB$17),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$18,"&lt;&gt;",'Picks'!$AB$2:$AB$18),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$17,'Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$18,'Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +900,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +916,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +931,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +947,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +962,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +978,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO17"/>
+  <dimension ref="A1:CP18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1107,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1572,6 +1574,11 @@
       <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
+        </is>
+      </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
         </is>
       </c>
     </row>
@@ -1859,6 +1866,7 @@
       <c r="CM2" s="24" t="n"/>
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2144,6 +2152,7 @@
       <c r="CM3" s="24" t="n"/>
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2429,6 +2438,7 @@
       <c r="CM4" s="24" t="n"/>
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
+      <c r="CP4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2714,6 +2724,7 @@
       <c r="CM5" s="24" t="n"/>
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
+      <c r="CP5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -2999,6 +3010,7 @@
       <c r="CM6" s="24" t="n"/>
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3274,6 +3286,7 @@
       <c r="CM7" s="24" t="n"/>
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
+      <c r="CP7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3549,6 +3562,7 @@
       <c r="CM8" s="24" t="n"/>
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3834,6 +3848,7 @@
       <c r="CM9" s="24" t="n"/>
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4119,6 +4134,7 @@
       <c r="CM10" s="24" t="n"/>
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4404,6 +4420,7 @@
       <c r="CM11" s="24" t="n"/>
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4689,6 +4706,7 @@
       <c r="CM12" s="24" t="n"/>
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -4974,6 +4992,7 @@
       <c r="CM13" s="24" t="n"/>
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5259,6 +5278,7 @@
       <c r="CM14" s="24" t="n"/>
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5520,6 +5540,7 @@
       <c r="CM15" s="24" t="n"/>
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5781,6 +5802,7 @@
       <c r="CM16" s="24" t="n"/>
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6042,6 +6064,269 @@
       <c r="CM17" s="24" t="n"/>
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>f9f0806ef44b4f94</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:07:54.976833Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.688017</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.108185</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="n"/>
+      <c r="W18" s="26" t="n"/>
+      <c r="X18" s="26" t="n"/>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n"/>
+      <c r="AD18" s="24" t="n"/>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>8b942fbb736985bcb2d3060c95145f67db9c15bdfbfc2955dc5cb5d8a411ff0a</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>8b942fbb736985bcb2d3060c95145f67db9c15bdfbfc2955dc5cb5d8a411ff0a</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:07:54.975627Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -5361,18 +5361,38 @@
       </c>
       <c r="U15" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
+      <c r="Z15" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="AA15" s="28" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AB15" s="28" t="n">
+        <v>-0.000529</v>
+      </c>
+      <c r="AC15" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:52:54.937176Z</t>
+        </is>
+      </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-dota2-yes-tr-2026-08-02).</t>
@@ -5385,7 +5405,7 @@
       </c>
       <c r="AG15" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH15" s="24" t="n"/>
@@ -5515,8 +5535,12 @@
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
       <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
+      <c r="BQ15" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BR15" s="28" t="n">
+        <v>0.44</v>
+      </c>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
       <c r="BU15" s="25" t="n"/>
@@ -5623,18 +5647,38 @@
       </c>
       <c r="U16" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
+      <c r="Z16" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AA16" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB16" s="28" t="n">
+        <v>0.000625</v>
+      </c>
+      <c r="AC16" s="30" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:52:56.184837Z</t>
+        </is>
+      </c>
       <c r="AE16" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-stray-ns-2026-08-02).</t>
@@ -5777,8 +5821,12 @@
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
       <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
+      <c r="BQ16" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BR16" s="28" t="n">
+        <v>0.61</v>
+      </c>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
       <c r="BU16" s="25" t="n"/>
@@ -6069,12 +6117,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>f9f0806ef44b4f94</t>
+          <t>c37f424aa4bb4d87</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:54.976833Z</t>
+          <t>2026-08-02T15:51:47.398301Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6119,23 +6167,23 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>-138</v>
+        <v>-127</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.787402</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.688017</v>
+        <v>0.68794</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.108185</v>
+        <v>0.128469</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S18" s="29" t="n">
         <v>2</v>
@@ -6161,7 +6209,7 @@
       <c r="AD18" s="24" t="n"/>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6245,7 +6293,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>8b942fbb736985bcb2d3060c95145f67db9c15bdfbfc2955dc5cb5d8a411ff0a</t>
+          <t>f0fcbc1453d1a656a25d9f456c501ac849c71b8ef6259b2f4e05c512bd7040ac</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6260,7 +6308,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>8b942fbb736985bcb2d3060c95145f67db9c15bdfbfc2955dc5cb5d8a411ff0a</t>
+          <t>f0fcbc1453d1a656a25d9f456c501ac849c71b8ef6259b2f4e05c512bd7040ac</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6280,7 +6328,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:54.975627Z</t>
+          <t>2026-08-02T15:51:46.912541Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6290,13 +6338,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>-138</v>
+        <v>-127</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.787402</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
@@ -6326,7 +6374,11 @@
       <c r="CM18" s="24" t="n"/>
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
-      <c r="CP18" s="24" t="n"/>
+      <c r="CP18" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP18" headerRowCount="1">
-  <autoFilter ref="A1:CP18"/>
-  <tableColumns count="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ18" headerRowCount="1">
+  <autoFilter ref="A1:CQ18"/>
+  <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,7 +396,8 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="trade_candidate"/>
+    <tableColumn id="94" name="market_residual_probability"/>
+    <tableColumn id="95" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1011,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP18"/>
+  <dimension ref="A1:CQ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1108,8 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="17" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="17" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1577,6 +1579,11 @@
         </is>
       </c>
       <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>market_residual_probability</t>
+        </is>
+      </c>
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1867,6 +1874,7 @@
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2153,6 +2161,7 @@
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2439,6 +2448,7 @@
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
+      <c r="CQ4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2725,6 +2735,7 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
+      <c r="CQ5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3011,6 +3022,7 @@
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
+      <c r="CQ6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3287,6 +3299,7 @@
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
+      <c r="CQ7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3563,6 +3576,7 @@
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
+      <c r="CQ8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3849,6 +3863,7 @@
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4135,6 +4150,7 @@
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4421,6 +4437,7 @@
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4707,6 +4724,7 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -4993,6 +5011,7 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5279,6 +5298,7 @@
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5565,6 +5585,7 @@
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5851,6 +5872,7 @@
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6113,16 +6135,17 @@
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>c37f424aa4bb4d87</t>
+          <t>84f8f619cc534833</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:47.398301Z</t>
+          <t>2026-08-02T16:15:20.632773Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6176,11 +6199,11 @@
         <v>0.5594710000000001</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.68794</v>
+        <v>0.687866</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.128469</v>
+        <v>0.128395</v>
       </c>
       <c r="R18" s="26" t="n">
         <v>84</v>
@@ -6293,7 +6316,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>f0fcbc1453d1a656a25d9f456c501ac849c71b8ef6259b2f4e05c512bd7040ac</t>
+          <t>dd15133f8ac3980e0e8f9507ceb080d57ad35a633e2d504e0df7fc9cdc098a3f</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6308,7 +6331,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>f0fcbc1453d1a656a25d9f456c501ac849c71b8ef6259b2f4e05c512bd7040ac</t>
+          <t>dd15133f8ac3980e0e8f9507ceb080d57ad35a633e2d504e0df7fc9cdc098a3f</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6328,7 +6351,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:46.912541Z</t>
+          <t>2026-08-02T16:15:20.152893Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6374,7 +6397,8 @@
       <c r="CM18" s="24" t="n"/>
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
-      <c r="CP18" s="24" t="inlineStr">
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -6140,12 +6140,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>84f8f619cc534833</t>
+          <t>8514e21bbc704abd</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:20.632773Z</t>
+          <t>2026-08-02T16:53:39.730207Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>dd15133f8ac3980e0e8f9507ceb080d57ad35a633e2d504e0df7fc9cdc098a3f</t>
+          <t>3b481b72458f95998f81ca892704b4ac7dca0dff8b1583067f4c8fae4d84ff0d</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>dd15133f8ac3980e0e8f9507ceb080d57ad35a633e2d504e0df7fc9cdc098a3f</t>
+          <t>3b481b72458f95998f81ca892704b4ac7dca0dff8b1583067f4c8fae4d84ff0d</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:20.152893Z</t>
+          <t>2026-08-02T16:53:39.258654Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ18" headerRowCount="1">
-  <autoFilter ref="A1:CQ18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ17" headerRowCount="1">
+  <autoFilter ref="A1:CQ17"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$18)</f>
+        <f>COUNTA('Picks'!$A$2:$A$17)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$18,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$17,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$18,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$17,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")/(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")/(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$18)/SUM('Picks'!$BX$2:$BX$18),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$17)/SUM('Picks'!$BX$2:$BX$17),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$18)</f>
+        <f>SUM('Picks'!$BY$2:$BY$17)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$18,"&lt;&gt;",'Picks'!$AB$2:$AB$18),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$17,"&lt;&gt;",'Picks'!$AB$2:$AB$17),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$18,'Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$17,'Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ18"/>
+  <dimension ref="A1:CQ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6137,273 +6137,6 @@
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>8514e21bbc704abd</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:39.730207Z</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>69530</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="G18" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="H18" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="n"/>
-      <c r="K18" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L18" s="26" t="n">
-        <v>-127</v>
-      </c>
-      <c r="M18" s="27" t="n">
-        <v>1.787402</v>
-      </c>
-      <c r="N18" s="28" t="n">
-        <v>0.5594710000000001</v>
-      </c>
-      <c r="O18" s="28" t="n">
-        <v>0.687866</v>
-      </c>
-      <c r="P18" s="28" t="n"/>
-      <c r="Q18" s="28" t="n">
-        <v>0.128395</v>
-      </c>
-      <c r="R18" s="26" t="n">
-        <v>84</v>
-      </c>
-      <c r="S18" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U18" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
-      <c r="Y18" s="25" t="n"/>
-      <c r="Z18" s="26" t="n"/>
-      <c r="AA18" s="28" t="n"/>
-      <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n"/>
-      <c r="AD18" s="24" t="n"/>
-      <c r="AE18" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF18" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG18" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH18" s="24" t="n"/>
-      <c r="AI18" s="31" t="n"/>
-      <c r="AJ18" s="31" t="n"/>
-      <c r="AK18" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL18" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM18" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN18" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO18" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP18" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AQ18" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AR18" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AS18" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AT18" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AU18" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AV18" s="24" t="n"/>
-      <c r="AW18" s="24" t="n"/>
-      <c r="AX18" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY18" s="24" t="n"/>
-      <c r="AZ18" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA18" s="24" t="inlineStr">
-        <is>
-          <t>3b481b72458f95998f81ca892704b4ac7dca0dff8b1583067f4c8fae4d84ff0d</t>
-        </is>
-      </c>
-      <c r="BB18" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC18" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD18" s="24" t="inlineStr">
-        <is>
-          <t>3b481b72458f95998f81ca892704b4ac7dca0dff8b1583067f4c8fae4d84ff0d</t>
-        </is>
-      </c>
-      <c r="BE18" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF18" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG18" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH18" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:39.258654Z</t>
-        </is>
-      </c>
-      <c r="BI18" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ18" s="25" t="n"/>
-      <c r="BK18" s="26" t="n">
-        <v>-127</v>
-      </c>
-      <c r="BL18" s="27" t="n">
-        <v>1.787402</v>
-      </c>
-      <c r="BM18" s="28" t="n">
-        <v>0.5594710000000001</v>
-      </c>
-      <c r="BN18" s="28" t="n"/>
-      <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
-      <c r="BR18" s="28" t="n"/>
-      <c r="BS18" s="28" t="n"/>
-      <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="25" t="n"/>
-      <c r="BV18" s="29" t="n"/>
-      <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n"/>
-      <c r="BY18" s="27" t="n"/>
-      <c r="BZ18" s="24" t="n"/>
-      <c r="CA18" s="31" t="n"/>
-      <c r="CB18" s="24" t="n"/>
-      <c r="CC18" s="24" t="n"/>
-      <c r="CD18" s="24" t="n"/>
-      <c r="CE18" s="24" t="n"/>
-      <c r="CF18" s="24" t="n"/>
-      <c r="CG18" s="24" t="n"/>
-      <c r="CH18" s="24" t="n"/>
-      <c r="CI18" s="24" t="n"/>
-      <c r="CJ18" s="24" t="n"/>
-      <c r="CK18" s="24" t="n"/>
-      <c r="CL18" s="24" t="n"/>
-      <c r="CM18" s="24" t="n"/>
-      <c r="CN18" s="24" t="n"/>
-      <c r="CO18" s="24" t="n"/>
-      <c r="CP18" s="24" t="n"/>
-      <c r="CQ18" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ17" headerRowCount="1">
-  <autoFilter ref="A1:CQ17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ18" headerRowCount="1">
+  <autoFilter ref="A1:CQ18"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$17)</f>
+        <f>COUNTA('Picks'!$A$2:$A$18)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$17,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$18,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$17,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$18,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")/(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")/(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$17)/SUM('Picks'!$BX$2:$BX$17),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$18)/SUM('Picks'!$BX$2:$BX$18),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$17)</f>
+        <f>SUM('Picks'!$BY$2:$BY$18)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$17,"&lt;&gt;",'Picks'!$AB$2:$AB$17),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$18,"&lt;&gt;",'Picks'!$AB$2:$AB$18),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$17,'Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$18,'Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ17"/>
+  <dimension ref="A1:CQ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6137,6 +6137,273 @@
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
     </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>20650966b2554f10</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:47.353360Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.687866</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.128395</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="n"/>
+      <c r="W18" s="26" t="n"/>
+      <c r="X18" s="26" t="n"/>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n"/>
+      <c r="AD18" s="24" t="n"/>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>bcd7d4bdd1e2218dd22c32e053e9e1e56eeed1afdf8b775edd90e5369a90ae7e</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>bcd7d4bdd1e2218dd22c32e053e9e1e56eeed1afdf8b775edd90e5369a90ae7e</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:46.828865Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -6140,12 +6140,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>20650966b2554f10</t>
+          <t>9a4bcd61115b4a5e</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:47.353360Z</t>
+          <t>2026-08-02T18:09:15.539608Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>bcd7d4bdd1e2218dd22c32e053e9e1e56eeed1afdf8b775edd90e5369a90ae7e</t>
+          <t>8e17bc625b6f663721d0cd0b27f30cf8017a2cbaa61c81881824fbb2600f16d7</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>bcd7d4bdd1e2218dd22c32e053e9e1e56eeed1afdf8b775edd90e5369a90ae7e</t>
+          <t>8e17bc625b6f663721d0cd0b27f30cf8017a2cbaa61c81881824fbb2600f16d7</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:46.828865Z</t>
+          <t>2026-08-02T18:09:15.062801Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ18" headerRowCount="1">
-  <autoFilter ref="A1:CQ18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ17" headerRowCount="1">
+  <autoFilter ref="A1:CQ17"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$18)</f>
+        <f>COUNTA('Picks'!$A$2:$A$17)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$18,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$17,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$18,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$17,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")/(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")/(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$18)/SUM('Picks'!$BX$2:$BX$18),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$17)/SUM('Picks'!$BX$2:$BX$17),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$18)</f>
+        <f>SUM('Picks'!$BY$2:$BY$17)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$18,"&lt;&gt;",'Picks'!$AB$2:$AB$18),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$17,"&lt;&gt;",'Picks'!$AB$2:$AB$17),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$18,'Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$17,'Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ18"/>
+  <dimension ref="A1:CQ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6137,273 +6137,6 @@
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>9a4bcd61115b4a5e</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:15.539608Z</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>69530</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="G18" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="H18" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="n"/>
-      <c r="K18" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L18" s="26" t="n">
-        <v>-127</v>
-      </c>
-      <c r="M18" s="27" t="n">
-        <v>1.787402</v>
-      </c>
-      <c r="N18" s="28" t="n">
-        <v>0.5594710000000001</v>
-      </c>
-      <c r="O18" s="28" t="n">
-        <v>0.687866</v>
-      </c>
-      <c r="P18" s="28" t="n"/>
-      <c r="Q18" s="28" t="n">
-        <v>0.128395</v>
-      </c>
-      <c r="R18" s="26" t="n">
-        <v>84</v>
-      </c>
-      <c r="S18" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U18" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
-      <c r="Y18" s="25" t="n"/>
-      <c r="Z18" s="26" t="n"/>
-      <c r="AA18" s="28" t="n"/>
-      <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n"/>
-      <c r="AD18" s="24" t="n"/>
-      <c r="AE18" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF18" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG18" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH18" s="24" t="n"/>
-      <c r="AI18" s="31" t="n"/>
-      <c r="AJ18" s="31" t="n"/>
-      <c r="AK18" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL18" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM18" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN18" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO18" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP18" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AQ18" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AR18" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AS18" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AT18" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AU18" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AV18" s="24" t="n"/>
-      <c r="AW18" s="24" t="n"/>
-      <c r="AX18" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY18" s="24" t="n"/>
-      <c r="AZ18" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA18" s="24" t="inlineStr">
-        <is>
-          <t>8e17bc625b6f663721d0cd0b27f30cf8017a2cbaa61c81881824fbb2600f16d7</t>
-        </is>
-      </c>
-      <c r="BB18" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC18" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD18" s="24" t="inlineStr">
-        <is>
-          <t>8e17bc625b6f663721d0cd0b27f30cf8017a2cbaa61c81881824fbb2600f16d7</t>
-        </is>
-      </c>
-      <c r="BE18" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF18" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG18" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH18" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:15.062801Z</t>
-        </is>
-      </c>
-      <c r="BI18" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ18" s="25" t="n"/>
-      <c r="BK18" s="26" t="n">
-        <v>-127</v>
-      </c>
-      <c r="BL18" s="27" t="n">
-        <v>1.787402</v>
-      </c>
-      <c r="BM18" s="28" t="n">
-        <v>0.5594710000000001</v>
-      </c>
-      <c r="BN18" s="28" t="n"/>
-      <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
-      <c r="BR18" s="28" t="n"/>
-      <c r="BS18" s="28" t="n"/>
-      <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="25" t="n"/>
-      <c r="BV18" s="29" t="n"/>
-      <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n"/>
-      <c r="BY18" s="27" t="n"/>
-      <c r="BZ18" s="24" t="n"/>
-      <c r="CA18" s="31" t="n"/>
-      <c r="CB18" s="24" t="n"/>
-      <c r="CC18" s="24" t="n"/>
-      <c r="CD18" s="24" t="n"/>
-      <c r="CE18" s="24" t="n"/>
-      <c r="CF18" s="24" t="n"/>
-      <c r="CG18" s="24" t="n"/>
-      <c r="CH18" s="24" t="n"/>
-      <c r="CI18" s="24" t="n"/>
-      <c r="CJ18" s="24" t="n"/>
-      <c r="CK18" s="24" t="n"/>
-      <c r="CL18" s="24" t="n"/>
-      <c r="CM18" s="24" t="n"/>
-      <c r="CN18" s="24" t="n"/>
-      <c r="CO18" s="24" t="n"/>
-      <c r="CP18" s="24" t="n"/>
-      <c r="CQ18" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ17" headerRowCount="1">
-  <autoFilter ref="A1:CQ17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ18" headerRowCount="1">
+  <autoFilter ref="A1:CQ18"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$17)</f>
+        <f>COUNTA('Picks'!$A$2:$A$18)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$17,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$18,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$17,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$18,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")/(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")/(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$17)/SUM('Picks'!$BX$2:$BX$17),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$18)/SUM('Picks'!$BX$2:$BX$18),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$17)</f>
+        <f>SUM('Picks'!$BY$2:$BY$18)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$17,"&lt;&gt;",'Picks'!$AB$2:$AB$17),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$18,"&lt;&gt;",'Picks'!$AB$2:$AB$18),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$17,'Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$18,'Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ17"/>
+  <dimension ref="A1:CQ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6137,6 +6137,273 @@
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
     </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>d71c6211bef842ad</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:04.078583Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.687866</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.128395</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="n"/>
+      <c r="W18" s="26" t="n"/>
+      <c r="X18" s="26" t="n"/>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n"/>
+      <c r="AD18" s="24" t="n"/>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>cb2508545871cd245c79cd37a7ddf28f5f869bf875eba85e1d6069b628af9a62</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>cb2508545871cd245c79cd37a7ddf28f5f869bf875eba85e1d6069b628af9a62</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:03.516712Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ18" headerRowCount="1">
-  <autoFilter ref="A1:CQ18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ27" headerRowCount="1">
+  <autoFilter ref="A1:CQ27"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$18)</f>
+        <f>COUNTA('Picks'!$A$2:$A$27)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$18,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$27,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$18,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$27,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")/(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")/(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$18)/SUM('Picks'!$BX$2:$BX$18),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$27)/SUM('Picks'!$BX$2:$BX$27),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$18)</f>
+        <f>SUM('Picks'!$BY$2:$BY$27)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$18,"&lt;&gt;",'Picks'!$AB$2:$AB$18),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$27,"&lt;&gt;",'Picks'!$AB$2:$AB$27),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$18,'Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$27,'Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ18"/>
+  <dimension ref="A1:CQ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5955,18 +5955,38 @@
       </c>
       <c r="U17" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n"/>
-      <c r="AD17" s="24" t="n"/>
+      <c r="Z17" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="AA17" s="28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB17" s="28" t="n">
+        <v>-0.000196</v>
+      </c>
+      <c r="AC17" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:26:45.633634Z</t>
+        </is>
+      </c>
       <c r="AE17" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-dota2-rnx-yb-2026-08-02).</t>
@@ -5979,7 +5999,7 @@
       </c>
       <c r="AG17" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH17" s="24" t="n"/>
@@ -6109,8 +6129,12 @@
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
       <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
-      <c r="BR17" s="28" t="n"/>
+      <c r="BQ17" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BR17" s="28" t="n">
+        <v>0.49</v>
+      </c>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
       <c r="BU17" s="25" t="n"/>
@@ -6140,12 +6164,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>d71c6211bef842ad</t>
+          <t>3fd99efe9c6243da</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:04.078583Z</t>
+          <t>2026-08-03T04:20:25.162543Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6190,23 +6214,23 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>-127</v>
+        <v>-170</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.588235</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.62963</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.687866</v>
+        <v>0.688438</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.128395</v>
+        <v>0.058808</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="S18" s="29" t="n">
         <v>2</v>
@@ -6218,21 +6242,41 @@
       </c>
       <c r="U18" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y18" s="25" t="n"/>
-      <c r="Z18" s="26" t="n"/>
-      <c r="AA18" s="28" t="n"/>
-      <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n"/>
-      <c r="AD18" s="24" t="n"/>
+      <c r="Z18" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA18" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB18" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC18" s="30" t="n">
+        <v>1.1765</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:06:42.804391Z</t>
+        </is>
+      </c>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6316,7 +6360,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>cb2508545871cd245c79cd37a7ddf28f5f869bf875eba85e1d6069b628af9a62</t>
+          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6331,7 +6375,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>cb2508545871cd245c79cd37a7ddf28f5f869bf875eba85e1d6069b628af9a62</t>
+          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6351,7 +6395,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:03.516712Z</t>
+          <t>2026-08-03T04:20:21.088131Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6361,19 +6405,23 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>-127</v>
+        <v>-170</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.588235</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.62963</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
       <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
-      <c r="BR18" s="28" t="n"/>
+      <c r="BQ18" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR18" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
       <c r="BU18" s="25" t="n"/>
@@ -6404,6 +6452,2505 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>6530d53c06454f44</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:32:33.049242Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>70303</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.622594</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>0.231969</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="AA19" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AB19" s="28" t="n">
+        <v>-0.000625</v>
+      </c>
+      <c r="AC19" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:55:54.261507Z</t>
+        </is>
+      </c>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-lgd-1win-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>533fea08f6899886856a22c8b82fe2bc1d4c49576971024283434d4b7315bbc9</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>533fea08f6899886856a22c8b82fe2bc1d4c49576971024283434d4b7315bbc9</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:32:30.412423Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BR19" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>8e9037eabbdc48e1</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:43.802206Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>GamerLegion</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.557781</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>-0.032383</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="AA20" s="28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AB20" s="28" t="n">
+        <v>-0.000164</v>
+      </c>
+      <c r="AC20" s="30" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:52:24.784101Z</t>
+        </is>
+      </c>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-og-gl-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>GamerLegion</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>GamerLegion</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>GamerLegion</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>528639205c5899c0cdf1bae7bf1adfb5d019bc11e79b9bc778f8eb3bb742ae6e</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>528639205c5899c0cdf1bae7bf1adfb5d019bc11e79b9bc778f8eb3bb742ae6e</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:42.011106Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BR20" s="28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>e4bdc99ea0824c30</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:35.070004Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.75532</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>0.05562</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="AA21" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB21" s="28" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="AC21" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:55:33.101548Z</t>
+        </is>
+      </c>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-re-lgd-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:33.121525Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BR21" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>23f48a1e758d46b2</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:35.070004Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.571416</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA22" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB22" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC22" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:52:00.620621Z</t>
+        </is>
+      </c>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-flc-bb-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:33.684542Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR22" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>8928b112b45a4512</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.678151Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>70891</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.720685</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.020985</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-og-bb-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:39.542403Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>b4f71ce0de934c17</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.678151Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>70684</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.701803</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>0.092428</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>66</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-pla-tr-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:40.034960Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>b683afa2c0064707</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.678151Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>71393</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Vici Gaming</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.535922</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>-0.134045</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-1win-vg-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>Vici Gaming</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Vici Gaming</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Vici Gaming</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:40.568093Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>edb82e4e4f5144d5</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.678151Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>71323</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.63019</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>0.050358</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-yb-re-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.112906Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>2dee7668363d48ea</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.678151Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>71394</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Team Liquid</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.599177</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>-0.051173</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n"/>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-dota2-flc-liquid-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>Team Liquid</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>Team Liquid</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>Team Liquid</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.677954Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ27" headerRowCount="1">
-  <autoFilter ref="A1:CQ27"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR26" headerRowCount="1">
+  <autoFilter ref="A1:CR26"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$27)</f>
+        <f>COUNTA('Picks'!$A$2:$A$26)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$27,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$26,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$27,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$26,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")/(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")/(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$27)/SUM('Picks'!$BX$2:$BX$27),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$26)/SUM('Picks'!$BX$2:$BX$26),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$27)</f>
+        <f>SUM('Picks'!$BY$2:$BY$26)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$27,"&lt;&gt;",'Picks'!$AB$2:$AB$27),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$26,"&lt;&gt;",'Picks'!$AB$2:$AB$26),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$27,'Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$26,'Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ27"/>
+  <dimension ref="A1:CR26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1875,6 +1882,7 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2162,6 +2170,7 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2449,6 +2458,7 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2736,6 +2746,7 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3023,6 +3034,7 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3300,6 +3312,7 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3577,6 +3590,7 @@
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3864,6 +3878,7 @@
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4151,6 +4166,7 @@
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4438,6 +4454,7 @@
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4725,6 +4742,7 @@
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -5012,6 +5030,7 @@
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5299,6 +5318,7 @@
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5586,6 +5606,7 @@
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5873,6 +5894,7 @@
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6160,6 +6182,7 @@
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6446,7 +6469,8 @@
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
-      <c r="CQ18" s="24" t="inlineStr">
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6737,7 +6761,8 @@
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
-      <c r="CQ19" s="24" t="inlineStr">
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7028,7 +7053,8 @@
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
-      <c r="CQ20" s="24" t="inlineStr">
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7319,7 +7345,8 @@
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
-      <c r="CQ21" s="24" t="inlineStr">
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7610,7 +7637,8 @@
       <c r="CN22" s="24" t="n"/>
       <c r="CO22" s="24" t="n"/>
       <c r="CP22" s="24" t="n"/>
-      <c r="CQ22" s="24" t="inlineStr">
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7619,22 +7647,22 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>8928b112b45a4512</t>
+          <t>7f141fd9db27496a</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:41.678151Z</t>
+          <t>2026-08-04T08:56:24.176296Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T09:00:00Z</t>
+          <t>2026-08-04T11:00:00Z</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>70891</t>
+          <t>70684</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -7644,12 +7672,12 @@
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>OG</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -7659,7 +7687,7 @@
       </c>
       <c r="I23" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J23" s="25" t="n"/>
@@ -7669,23 +7697,23 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>-233</v>
+        <v>-138</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.724638</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.579832</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.720685</v>
+        <v>0.701803</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>0.020985</v>
+        <v>0.121971</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="S23" s="29" t="n">
         <v>2</v>
@@ -7711,7 +7739,7 @@
       <c r="AD23" s="24" t="n"/>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-og-bb-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-pla-tr-2026-08-04).</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7752,32 +7780,32 @@
       </c>
       <c r="AP23" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AQ23" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AR23" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AS23" s="24" t="inlineStr">
         <is>
-          <t>OG</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AT23" s="24" t="inlineStr">
         <is>
-          <t>OG</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AU23" s="24" t="inlineStr">
         <is>
-          <t>OG</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AV23" s="24" t="n"/>
@@ -7795,7 +7823,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7810,7 +7838,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7830,7 +7858,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:39.542403Z</t>
+          <t>2026-08-04T08:56:22.344795Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7840,13 +7868,13 @@
       </c>
       <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
-        <v>-233</v>
+        <v>-138</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.724638</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.579832</v>
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
@@ -7877,7 +7905,8 @@
       <c r="CN23" s="24" t="n"/>
       <c r="CO23" s="24" t="n"/>
       <c r="CP23" s="24" t="n"/>
-      <c r="CQ23" s="24" t="inlineStr">
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7886,22 +7915,22 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>b4f71ce0de934c17</t>
+          <t>dc4a35f1660a4298</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:41.678151Z</t>
+          <t>2026-08-04T08:56:24.176296Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T11:00:00Z</t>
+          <t>2026-08-04T12:00:00Z</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>70684</t>
+          <t>71393</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -7911,12 +7940,12 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Vici Gaming</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>1win</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -7936,26 +7965,26 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-156</v>
+        <v>-203</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.492611</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.669967</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.701803</v>
+        <v>0.535922</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>0.092428</v>
+        <v>-0.134045</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="S24" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T24" s="24" t="inlineStr">
         <is>
@@ -7978,7 +8007,7 @@
       <c r="AD24" s="24" t="n"/>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-pla-tr-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-1win-vg-2026-08-04).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -7996,7 +8025,7 @@
       <c r="AJ24" s="31" t="n"/>
       <c r="AK24" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL24" s="26" t="n">
@@ -8004,47 +8033,47 @@
       </c>
       <c r="AM24" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN24" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO24" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP24" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Vici Gaming</t>
         </is>
       </c>
       <c r="AQ24" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Vici Gaming</t>
         </is>
       </c>
       <c r="AR24" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Vici Gaming</t>
         </is>
       </c>
       <c r="AS24" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>1win</t>
         </is>
       </c>
       <c r="AT24" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>1win</t>
         </is>
       </c>
       <c r="AU24" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>1win</t>
         </is>
       </c>
       <c r="AV24" s="24" t="n"/>
@@ -8062,7 +8091,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -8077,7 +8106,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -8097,7 +8126,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:40.034960Z</t>
+          <t>2026-08-04T08:56:22.969840Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8107,13 +8136,13 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>-156</v>
+        <v>-203</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.492611</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.669967</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
@@ -8144,31 +8173,32 @@
       <c r="CN24" s="24" t="n"/>
       <c r="CO24" s="24" t="n"/>
       <c r="CP24" s="24" t="n"/>
-      <c r="CQ24" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>b683afa2c0064707</t>
+          <t>070a4150052a47df</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:41.678151Z</t>
+          <t>2026-08-04T08:56:24.176296Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T12:00:00Z</t>
+          <t>2026-08-04T14:00:00Z</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>71393</t>
+          <t>71323</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -8178,12 +8208,12 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>Vici Gaming</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -8193,7 +8223,7 @@
       </c>
       <c r="I25" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J25" s="25" t="n"/>
@@ -8203,26 +8233,26 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>-203</v>
+        <v>-150</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.666667</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.6</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.535922</v>
+        <v>0.63019</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>-0.134045</v>
+        <v>0.03019</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
@@ -8245,7 +8275,7 @@
       <c r="AD25" s="24" t="n"/>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-1win-vg-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-yb-re-2026-08-04).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8263,7 +8293,7 @@
       <c r="AJ25" s="31" t="n"/>
       <c r="AK25" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL25" s="26" t="n">
@@ -8271,47 +8301,47 @@
       </c>
       <c r="AM25" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN25" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO25" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP25" s="24" t="inlineStr">
         <is>
-          <t>Vici Gaming</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AQ25" s="24" t="inlineStr">
         <is>
-          <t>Vici Gaming</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AR25" s="24" t="inlineStr">
         <is>
-          <t>Vici Gaming</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AS25" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AT25" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AU25" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AV25" s="24" t="n"/>
@@ -8329,7 +8359,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8344,7 +8374,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8364,7 +8394,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:40.568093Z</t>
+          <t>2026-08-04T08:56:23.442743Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8374,13 +8404,13 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>-203</v>
+        <v>-150</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.666667</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.6</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
@@ -8411,31 +8441,32 @@
       <c r="CN25" s="24" t="n"/>
       <c r="CO25" s="24" t="n"/>
       <c r="CP25" s="24" t="n"/>
-      <c r="CQ25" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>edb82e4e4f5144d5</t>
+          <t>6718700cecee4421</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:41.678151Z</t>
+          <t>2026-08-04T08:56:24.176296Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:00:00Z</t>
+          <t>2026-08-04T15:00:00Z</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>71323</t>
+          <t>71394</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -8445,12 +8476,12 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Falcons</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -8460,7 +8491,7 @@
       </c>
       <c r="I26" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J26" s="25" t="n"/>
@@ -8470,26 +8501,26 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>-138</v>
+        <v>-186</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.537634</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.65035</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.63019</v>
+        <v>0.599177</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>0.050358</v>
+        <v>-0.051173</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="S26" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
@@ -8512,7 +8543,7 @@
       <c r="AD26" s="24" t="n"/>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-yb-re-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-dota2-flc-liquid-2026-08-04).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8530,7 +8561,7 @@
       <c r="AJ26" s="31" t="n"/>
       <c r="AK26" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL26" s="26" t="n">
@@ -8538,47 +8569,47 @@
       </c>
       <c r="AM26" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN26" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO26" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP26" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AQ26" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AR26" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AS26" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Falcons</t>
         </is>
       </c>
       <c r="AT26" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Falcons</t>
         </is>
       </c>
       <c r="AU26" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Falcons</t>
         </is>
       </c>
       <c r="AV26" s="24" t="n"/>
@@ -8596,7 +8627,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8611,7 +8642,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8631,7 +8662,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:41.112906Z</t>
+          <t>2026-08-04T08:56:24.176088Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8641,13 +8672,13 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>-138</v>
+        <v>-186</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.537634</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.65035</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
@@ -8678,274 +8709,8 @@
       <c r="CN26" s="24" t="n"/>
       <c r="CO26" s="24" t="n"/>
       <c r="CP26" s="24" t="n"/>
-      <c r="CQ26" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>2dee7668363d48ea</t>
-        </is>
-      </c>
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T02:00:41.678151Z</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>71394</t>
-        </is>
-      </c>
-      <c r="E27" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
-        <is>
-          <t>Team Liquid</t>
-        </is>
-      </c>
-      <c r="G27" s="24" t="inlineStr">
-        <is>
-          <t>Team Falcons</t>
-        </is>
-      </c>
-      <c r="H27" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I27" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J27" s="25" t="n"/>
-      <c r="K27" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L27" s="26" t="n">
-        <v>-186</v>
-      </c>
-      <c r="M27" s="27" t="n">
-        <v>1.537634</v>
-      </c>
-      <c r="N27" s="28" t="n">
-        <v>0.65035</v>
-      </c>
-      <c r="O27" s="28" t="n">
-        <v>0.599177</v>
-      </c>
-      <c r="P27" s="28" t="n"/>
-      <c r="Q27" s="28" t="n">
-        <v>-0.051173</v>
-      </c>
-      <c r="R27" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T27" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U27" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
-      <c r="Y27" s="25" t="n"/>
-      <c r="Z27" s="26" t="n"/>
-      <c r="AA27" s="28" t="n"/>
-      <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
-      <c r="AE27" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-dota2-flc-liquid-2026-08-04).</t>
-        </is>
-      </c>
-      <c r="AF27" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG27" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH27" s="24" t="n"/>
-      <c r="AI27" s="31" t="n"/>
-      <c r="AJ27" s="31" t="n"/>
-      <c r="AK27" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL27" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM27" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN27" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO27" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP27" s="24" t="inlineStr">
-        <is>
-          <t>Team Liquid</t>
-        </is>
-      </c>
-      <c r="AQ27" s="24" t="inlineStr">
-        <is>
-          <t>Team Liquid</t>
-        </is>
-      </c>
-      <c r="AR27" s="24" t="inlineStr">
-        <is>
-          <t>Team Liquid</t>
-        </is>
-      </c>
-      <c r="AS27" s="24" t="inlineStr">
-        <is>
-          <t>Team Falcons</t>
-        </is>
-      </c>
-      <c r="AT27" s="24" t="inlineStr">
-        <is>
-          <t>Team Falcons</t>
-        </is>
-      </c>
-      <c r="AU27" s="24" t="inlineStr">
-        <is>
-          <t>Team Falcons</t>
-        </is>
-      </c>
-      <c r="AV27" s="24" t="n"/>
-      <c r="AW27" s="24" t="n"/>
-      <c r="AX27" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY27" s="24" t="n"/>
-      <c r="AZ27" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA27" s="24" t="inlineStr">
-        <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
-        </is>
-      </c>
-      <c r="BB27" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC27" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD27" s="24" t="inlineStr">
-        <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
-        </is>
-      </c>
-      <c r="BE27" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF27" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG27" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH27" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T02:00:41.677954Z</t>
-        </is>
-      </c>
-      <c r="BI27" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ27" s="25" t="n"/>
-      <c r="BK27" s="26" t="n">
-        <v>-186</v>
-      </c>
-      <c r="BL27" s="27" t="n">
-        <v>1.537634</v>
-      </c>
-      <c r="BM27" s="28" t="n">
-        <v>0.65035</v>
-      </c>
-      <c r="BN27" s="28" t="n"/>
-      <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
-      <c r="BR27" s="28" t="n"/>
-      <c r="BS27" s="28" t="n"/>
-      <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="25" t="n"/>
-      <c r="BV27" s="29" t="n"/>
-      <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="30" t="n"/>
-      <c r="BY27" s="27" t="n"/>
-      <c r="BZ27" s="24" t="n"/>
-      <c r="CA27" s="31" t="n"/>
-      <c r="CB27" s="24" t="n"/>
-      <c r="CC27" s="24" t="n"/>
-      <c r="CD27" s="24" t="n"/>
-      <c r="CE27" s="24" t="n"/>
-      <c r="CF27" s="24" t="n"/>
-      <c r="CG27" s="24" t="n"/>
-      <c r="CH27" s="24" t="n"/>
-      <c r="CI27" s="24" t="n"/>
-      <c r="CJ27" s="24" t="n"/>
-      <c r="CK27" s="24" t="n"/>
-      <c r="CL27" s="24" t="n"/>
-      <c r="CM27" s="24" t="n"/>
-      <c r="CN27" s="24" t="n"/>
-      <c r="CO27" s="24" t="n"/>
-      <c r="CP27" s="24" t="n"/>
-      <c r="CQ27" s="24" t="inlineStr">
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR26" headerRowCount="1">
-  <autoFilter ref="A1:CR26"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS25" headerRowCount="1">
+  <autoFilter ref="A1:CS25"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -755,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$26)</f>
+        <f>COUNTA('Picks'!$A$2:$A$25)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$26,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$25,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -795,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$26,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$25,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")/(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")/(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$26)/SUM('Picks'!$BX$2:$BX$26),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$25)/SUM('Picks'!$BX$2:$BX$25),0)</f>
         <v/>
       </c>
     </row>
@@ -835,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$26)</f>
+        <f>SUM('Picks'!$BY$2:$BY$25)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$26,"&lt;&gt;",'Picks'!$AB$2:$AB$26),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$25,"&lt;&gt;",'Picks'!$AB$2:$AB$25),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$26,'Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$25,'Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -902,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -918,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -933,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -949,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -964,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -980,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR26"/>
+  <dimension ref="A1:CS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1883,6 +1890,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2171,6 +2179,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2459,6 +2468,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2747,6 +2757,7 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3035,6 +3046,7 @@
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
       <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3313,6 +3325,7 @@
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
       <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3591,6 +3604,7 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
       <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3879,6 +3893,7 @@
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
       <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4167,6 +4182,7 @@
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
       <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4455,6 +4471,7 @@
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
       <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4743,6 +4760,7 @@
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
       <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -5031,6 +5049,7 @@
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
       <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5319,6 +5338,7 @@
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
       <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5607,6 +5627,7 @@
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
       <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5895,6 +5916,7 @@
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
       <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6183,6 +6205,7 @@
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
       <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6470,7 +6493,8 @@
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
       <c r="CQ18" s="24" t="n"/>
-      <c r="CR18" s="24" t="inlineStr">
+      <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6762,7 +6786,8 @@
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
       <c r="CQ19" s="24" t="n"/>
-      <c r="CR19" s="24" t="inlineStr">
+      <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7054,7 +7079,8 @@
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
       <c r="CQ20" s="24" t="n"/>
-      <c r="CR20" s="24" t="inlineStr">
+      <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7346,7 +7372,8 @@
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
       <c r="CQ21" s="24" t="n"/>
-      <c r="CR21" s="24" t="inlineStr">
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7638,7 +7665,8 @@
       <c r="CO22" s="24" t="n"/>
       <c r="CP22" s="24" t="n"/>
       <c r="CQ22" s="24" t="n"/>
-      <c r="CR22" s="24" t="inlineStr">
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7725,18 +7753,38 @@
       </c>
       <c r="U23" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V23" s="24" t="n"/>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y23" s="25" t="n"/>
-      <c r="Z23" s="26" t="n"/>
-      <c r="AA23" s="28" t="n"/>
-      <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n"/>
-      <c r="AD23" s="24" t="n"/>
+      <c r="Z23" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="AA23" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB23" s="28" t="n">
+        <v>0.000168</v>
+      </c>
+      <c r="AC23" s="30" t="n">
+        <v>1.4493</v>
+      </c>
+      <c r="AD23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:19.328085Z</t>
+        </is>
+      </c>
       <c r="AE23" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-pla-tr-2026-08-04).</t>
@@ -7879,8 +7927,12 @@
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
       <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
-      <c r="BR23" s="28" t="n"/>
+      <c r="BQ23" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BR23" s="28" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
       <c r="BU23" s="25" t="n"/>
@@ -7906,7 +7958,8 @@
       <c r="CO23" s="24" t="n"/>
       <c r="CP23" s="24" t="n"/>
       <c r="CQ23" s="24" t="n"/>
-      <c r="CR23" s="24" t="inlineStr">
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7915,22 +7968,22 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>dc4a35f1660a4298</t>
+          <t>3bfb89d3bcc646f4</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:24.176296Z</t>
+          <t>2026-08-04T12:01:37.365629Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T12:00:00Z</t>
+          <t>2026-08-04T14:00:00Z</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>71393</t>
+          <t>71323</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -7940,12 +7993,12 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>Vici Gaming</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -7955,7 +8008,7 @@
       </c>
       <c r="I24" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J24" s="25" t="n"/>
@@ -7965,26 +8018,26 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-203</v>
+        <v>-150</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.666667</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.6</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.535922</v>
+        <v>0.63019</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>-0.134045</v>
+        <v>0.03019</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="S24" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T24" s="24" t="inlineStr">
         <is>
@@ -8007,7 +8060,7 @@
       <c r="AD24" s="24" t="n"/>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-1win-vg-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-yb-re-2026-08-04).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -8025,7 +8078,7 @@
       <c r="AJ24" s="31" t="n"/>
       <c r="AK24" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL24" s="26" t="n">
@@ -8033,47 +8086,47 @@
       </c>
       <c r="AM24" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN24" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO24" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP24" s="24" t="inlineStr">
         <is>
-          <t>Vici Gaming</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AQ24" s="24" t="inlineStr">
         <is>
-          <t>Vici Gaming</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AR24" s="24" t="inlineStr">
         <is>
-          <t>Vici Gaming</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AS24" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AT24" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AU24" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AV24" s="24" t="n"/>
@@ -8091,7 +8144,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
+          <t>a6c9607e653da0963c1aedbfdf02df93d0e81f5e712085073f323442476b541d</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -8106,7 +8159,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
+          <t>a6c9607e653da0963c1aedbfdf02df93d0e81f5e712085073f323442476b541d</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -8126,7 +8179,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:22.969840Z</t>
+          <t>2026-08-04T12:01:36.421980Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8136,13 +8189,13 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>-203</v>
+        <v>-150</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.666667</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.6</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
@@ -8174,31 +8227,32 @@
       <c r="CO24" s="24" t="n"/>
       <c r="CP24" s="24" t="n"/>
       <c r="CQ24" s="24" t="n"/>
-      <c r="CR24" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>070a4150052a47df</t>
+          <t>191a66f39af04c24</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:24.176296Z</t>
+          <t>2026-08-04T14:26:39.396561Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:00:00Z</t>
+          <t>2026-08-04T15:00:00Z</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>71323</t>
+          <t>71394</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -8208,12 +8262,12 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Falcons</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -8223,7 +8277,7 @@
       </c>
       <c r="I25" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J25" s="25" t="n"/>
@@ -8233,26 +8287,26 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>-150</v>
+        <v>-186</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.537634</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.6</v>
+        <v>0.65035</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.63019</v>
+        <v>0.599247</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>0.03019</v>
+        <v>-0.051103</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
@@ -8275,7 +8329,7 @@
       <c r="AD25" s="24" t="n"/>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-yb-re-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-dota2-flc-liquid-2026-08-04).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8293,7 +8347,7 @@
       <c r="AJ25" s="31" t="n"/>
       <c r="AK25" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL25" s="26" t="n">
@@ -8301,47 +8355,47 @@
       </c>
       <c r="AM25" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN25" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO25" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP25" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AQ25" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AR25" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AS25" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Falcons</t>
         </is>
       </c>
       <c r="AT25" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Falcons</t>
         </is>
       </c>
       <c r="AU25" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Falcons</t>
         </is>
       </c>
       <c r="AV25" s="24" t="n"/>
@@ -8359,7 +8413,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
+          <t>b921081c94f350d1171b92b678f9b1518a4a8603443c3731dc34195c91e09a2e</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8374,7 +8428,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
+          <t>b921081c94f350d1171b92b678f9b1518a4a8603443c3731dc34195c91e09a2e</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8394,7 +8448,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:23.442743Z</t>
+          <t>2026-08-04T14:26:39.396089Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8404,13 +8458,13 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>-150</v>
+        <v>-186</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.537634</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.6</v>
+        <v>0.65035</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
@@ -8442,275 +8496,8 @@
       <c r="CO25" s="24" t="n"/>
       <c r="CP25" s="24" t="n"/>
       <c r="CQ25" s="24" t="n"/>
-      <c r="CR25" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>6718700cecee4421</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T08:56:24.176296Z</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>71394</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
-        <is>
-          <t>Team Liquid</t>
-        </is>
-      </c>
-      <c r="G26" s="24" t="inlineStr">
-        <is>
-          <t>Team Falcons</t>
-        </is>
-      </c>
-      <c r="H26" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I26" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J26" s="25" t="n"/>
-      <c r="K26" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L26" s="26" t="n">
-        <v>-186</v>
-      </c>
-      <c r="M26" s="27" t="n">
-        <v>1.537634</v>
-      </c>
-      <c r="N26" s="28" t="n">
-        <v>0.65035</v>
-      </c>
-      <c r="O26" s="28" t="n">
-        <v>0.599177</v>
-      </c>
-      <c r="P26" s="28" t="n"/>
-      <c r="Q26" s="28" t="n">
-        <v>-0.051173</v>
-      </c>
-      <c r="R26" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T26" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U26" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
-      <c r="Y26" s="25" t="n"/>
-      <c r="Z26" s="26" t="n"/>
-      <c r="AA26" s="28" t="n"/>
-      <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
-      <c r="AE26" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-dota2-flc-liquid-2026-08-04).</t>
-        </is>
-      </c>
-      <c r="AF26" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG26" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH26" s="24" t="n"/>
-      <c r="AI26" s="31" t="n"/>
-      <c r="AJ26" s="31" t="n"/>
-      <c r="AK26" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL26" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM26" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN26" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO26" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP26" s="24" t="inlineStr">
-        <is>
-          <t>Team Liquid</t>
-        </is>
-      </c>
-      <c r="AQ26" s="24" t="inlineStr">
-        <is>
-          <t>Team Liquid</t>
-        </is>
-      </c>
-      <c r="AR26" s="24" t="inlineStr">
-        <is>
-          <t>Team Liquid</t>
-        </is>
-      </c>
-      <c r="AS26" s="24" t="inlineStr">
-        <is>
-          <t>Team Falcons</t>
-        </is>
-      </c>
-      <c r="AT26" s="24" t="inlineStr">
-        <is>
-          <t>Team Falcons</t>
-        </is>
-      </c>
-      <c r="AU26" s="24" t="inlineStr">
-        <is>
-          <t>Team Falcons</t>
-        </is>
-      </c>
-      <c r="AV26" s="24" t="n"/>
-      <c r="AW26" s="24" t="n"/>
-      <c r="AX26" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY26" s="24" t="n"/>
-      <c r="AZ26" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA26" s="24" t="inlineStr">
-        <is>
-          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
-        </is>
-      </c>
-      <c r="BB26" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC26" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD26" s="24" t="inlineStr">
-        <is>
-          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
-        </is>
-      </c>
-      <c r="BE26" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF26" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG26" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH26" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T08:56:24.176088Z</t>
-        </is>
-      </c>
-      <c r="BI26" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ26" s="25" t="n"/>
-      <c r="BK26" s="26" t="n">
-        <v>-186</v>
-      </c>
-      <c r="BL26" s="27" t="n">
-        <v>1.537634</v>
-      </c>
-      <c r="BM26" s="28" t="n">
-        <v>0.65035</v>
-      </c>
-      <c r="BN26" s="28" t="n"/>
-      <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
-      <c r="BR26" s="28" t="n"/>
-      <c r="BS26" s="28" t="n"/>
-      <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="25" t="n"/>
-      <c r="BV26" s="29" t="n"/>
-      <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="30" t="n"/>
-      <c r="BY26" s="27" t="n"/>
-      <c r="BZ26" s="24" t="n"/>
-      <c r="CA26" s="31" t="n"/>
-      <c r="CB26" s="24" t="n"/>
-      <c r="CC26" s="24" t="n"/>
-      <c r="CD26" s="24" t="n"/>
-      <c r="CE26" s="24" t="n"/>
-      <c r="CF26" s="24" t="n"/>
-      <c r="CG26" s="24" t="n"/>
-      <c r="CH26" s="24" t="n"/>
-      <c r="CI26" s="24" t="n"/>
-      <c r="CJ26" s="24" t="n"/>
-      <c r="CK26" s="24" t="n"/>
-      <c r="CL26" s="24" t="n"/>
-      <c r="CM26" s="24" t="n"/>
-      <c r="CN26" s="24" t="n"/>
-      <c r="CO26" s="24" t="n"/>
-      <c r="CP26" s="24" t="n"/>
-      <c r="CQ26" s="24" t="n"/>
-      <c r="CR26" s="24" t="inlineStr">
+      <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS25" headerRowCount="1">
-  <autoFilter ref="A1:CS25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS31" headerRowCount="1">
+  <autoFilter ref="A1:CS31"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$25)</f>
+        <f>COUNTA('Picks'!$A$2:$A$31)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$25,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$31,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")+COUNTIFS('Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$25,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$31,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")/(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")/(COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")+COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$25)/SUM('Picks'!$BX$2:$BX$25),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$31)/SUM('Picks'!$BX$2:$BX$31),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$25)</f>
+        <f>SUM('Picks'!$BY$2:$BY$31)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$25,"&lt;&gt;",'Picks'!$AB$2:$AB$25),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$31,"&lt;&gt;",'Picks'!$AB$2:$AB$31),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$31,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$25,'Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$31,'Picks'!$AM$2:$AM$31,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS25"/>
+  <dimension ref="A1:CS31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8046,18 +8046,38 @@
       </c>
       <c r="U24" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y24" s="25" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="28" t="n"/>
-      <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="24" t="n"/>
+      <c r="Z24" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="AA24" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB24" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:02.952248Z</t>
+        </is>
+      </c>
       <c r="AE24" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-yb-re-2026-08-04).</t>
@@ -8070,7 +8090,7 @@
       </c>
       <c r="AG24" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH24" s="24" t="n"/>
@@ -8200,8 +8220,12 @@
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
       <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
-      <c r="BR24" s="28" t="n"/>
+      <c r="BQ24" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BR24" s="28" t="n">
+        <v>0.6</v>
+      </c>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
       <c r="BU24" s="25" t="n"/>
@@ -8315,18 +8339,38 @@
       </c>
       <c r="U25" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y25" s="25" t="n"/>
-      <c r="Z25" s="26" t="n"/>
-      <c r="AA25" s="28" t="n"/>
-      <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n"/>
-      <c r="AD25" s="24" t="n"/>
+      <c r="Z25" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="AA25" s="28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AB25" s="28" t="n">
+        <v>-0.00035</v>
+      </c>
+      <c r="AC25" s="30" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:05.209291Z</t>
+        </is>
+      </c>
       <c r="AE25" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-dota2-flc-liquid-2026-08-04).</t>
@@ -8469,8 +8513,12 @@
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
       <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
-      <c r="BR25" s="28" t="n"/>
+      <c r="BQ25" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BR25" s="28" t="n">
+        <v>0.65</v>
+      </c>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
       <c r="BU25" s="25" t="n"/>
@@ -8503,6 +8551,1620 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>8804b09f2e484069</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>72079</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.500216</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>0.049766</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-tr-re-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:08.611098Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>38b2b0d956f84f99</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>71970</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.658681</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>0.128165</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n"/>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-1win-bb-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:09.196950Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>fe56aa0725d34209</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>72080</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.806217</v>
+      </c>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n">
+        <v>0.115815</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="n"/>
+      <c r="W28" s="26" t="n"/>
+      <c r="X28" s="26" t="n"/>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="28" t="n"/>
+      <c r="AC28" s="30" t="n"/>
+      <c r="AD28" s="24" t="n"/>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-dota2-pla-yb-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:09.769926Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN28" s="28" t="n"/>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
+      <c r="BR28" s="28" t="n"/>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="n"/>
+      <c r="CD28" s="24" t="n"/>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="n"/>
+      <c r="CJ28" s="24" t="n"/>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>5079924cff64404a</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>70575</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.528647</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>0.078197</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="n"/>
+      <c r="W29" s="26" t="n"/>
+      <c r="X29" s="26" t="n"/>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n"/>
+      <c r="AD29" s="24" t="n"/>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lvlup-rae-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:10.316562Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="n"/>
+      <c r="CD29" s="24" t="n"/>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="n"/>
+      <c r="CJ29" s="24" t="n"/>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>e2ad8578f6c04c90</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>70648</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.611725</v>
+      </c>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n">
+        <v>0.211725</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="n"/>
+      <c r="W30" s="26" t="n"/>
+      <c r="X30" s="26" t="n"/>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n"/>
+      <c r="AD30" s="24" t="n"/>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-rae-nh-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:10.870839Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN30" s="28" t="n"/>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n"/>
+      <c r="BY30" s="27" t="n"/>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="n"/>
+      <c r="CD30" s="24" t="n"/>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="n"/>
+      <c r="CJ30" s="24" t="n"/>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>bf6757ae2e2e4ffd</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.558677</v>
+      </c>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n">
+        <v>-0.000794</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="n"/>
+      <c r="W31" s="26" t="n"/>
+      <c r="X31" s="26" t="n"/>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="28" t="n"/>
+      <c r="AC31" s="30" t="n"/>
+      <c r="AD31" s="24" t="n"/>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-nh-lvlup-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:11.700160Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN31" s="28" t="n"/>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n"/>
+      <c r="BY31" s="27" t="n"/>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="n"/>
+      <c r="CD31" s="24" t="n"/>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="n"/>
+      <c r="CJ31" s="24" t="n"/>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -8632,18 +8632,38 @@
       </c>
       <c r="U26" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y26" s="25" t="n"/>
-      <c r="Z26" s="26" t="n"/>
-      <c r="AA26" s="28" t="n"/>
-      <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
+      <c r="Z26" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA26" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB26" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC26" s="30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:17:02.060126Z</t>
+        </is>
+      </c>
       <c r="AE26" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-tr-re-2026-08-05).</t>
@@ -8786,8 +8806,12 @@
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
       <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
-      <c r="BR26" s="28" t="n"/>
+      <c r="BQ26" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR26" s="28" t="n">
+        <v>0.45</v>
+      </c>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
       <c r="BU26" s="25" t="n"/>
@@ -8901,18 +8925,38 @@
       </c>
       <c r="U27" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y27" s="25" t="n"/>
-      <c r="Z27" s="26" t="n"/>
-      <c r="AA27" s="28" t="n"/>
-      <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
+      <c r="Z27" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA27" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB27" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC27" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:50:43.202468Z</t>
+        </is>
+      </c>
       <c r="AE27" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-1win-bb-2026-08-05).</t>
@@ -8925,7 +8969,7 @@
       </c>
       <c r="AG27" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH27" s="24" t="n"/>
@@ -9055,8 +9099,12 @@
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
       <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
-      <c r="BR27" s="28" t="n"/>
+      <c r="BQ27" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR27" s="28" t="n">
+        <v>0.53</v>
+      </c>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
       <c r="BU27" s="25" t="n"/>
@@ -9092,12 +9140,12 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>fe56aa0725d34209</t>
+          <t>8300edfe97dd4fab</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:12.341207Z</t>
+          <t>2026-08-05T10:46:31.198892Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -9142,23 +9190,23 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>-223</v>
+        <v>-203</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.492611</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.669967</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>0.806217</v>
+        <v>0.805779</v>
       </c>
       <c r="P28" s="28" t="n"/>
       <c r="Q28" s="28" t="n">
-        <v>0.115815</v>
+        <v>0.135812</v>
       </c>
       <c r="R28" s="26" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="S28" s="29" t="n">
         <v>2</v>
@@ -9184,7 +9232,7 @@
       <c r="AD28" s="24" t="n"/>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-dota2-pla-yb-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-pla-yb-2026-08-05).</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -9268,7 +9316,7 @@
       </c>
       <c r="BA28" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
         </is>
       </c>
       <c r="BB28" s="24" t="inlineStr">
@@ -9283,7 +9331,7 @@
       </c>
       <c r="BD28" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
         </is>
       </c>
       <c r="BE28" s="24" t="inlineStr">
@@ -9303,7 +9351,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:09.769926Z</t>
+          <t>2026-08-05T10:46:27.725458Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -9313,13 +9361,13 @@
       </c>
       <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
-        <v>-223</v>
+        <v>-203</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.492611</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.669967</v>
       </c>
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
@@ -9361,12 +9409,12 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>5079924cff64404a</t>
+          <t>b56d715e272c4466</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:12.341207Z</t>
+          <t>2026-08-05T13:56:09.744515Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -9411,23 +9459,23 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.429185</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.528647</v>
+        <v>0.528031</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>0.078197</v>
+        <v>0.098846</v>
       </c>
       <c r="R29" s="26" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="S29" s="29" t="n">
         <v>1</v>
@@ -9453,7 +9501,7 @@
       <c r="AD29" s="24" t="n"/>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lvlup-rae-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-dota2-lvlup-rae-2026-08-06).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9537,7 +9585,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9552,7 +9600,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9572,7 +9620,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:10.316562Z</t>
+          <t>2026-08-05T13:56:07.743708Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9582,13 +9630,13 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.429185</v>
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
@@ -9630,12 +9678,12 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>e2ad8578f6c04c90</t>
+          <t>bb4e032c2ca34ea7</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:12.341207Z</t>
+          <t>2026-08-05T13:56:09.744515Z</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -9689,11 +9737,11 @@
         <v>0.4</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>0.611725</v>
+        <v>0.611634</v>
       </c>
       <c r="P30" s="28" t="n"/>
       <c r="Q30" s="28" t="n">
-        <v>0.211725</v>
+        <v>0.211634</v>
       </c>
       <c r="R30" s="26" t="n">
         <v>100</v>
@@ -9806,7 +9854,7 @@
       </c>
       <c r="BA30" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
         </is>
       </c>
       <c r="BB30" s="24" t="inlineStr">
@@ -9821,7 +9869,7 @@
       </c>
       <c r="BD30" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
         </is>
       </c>
       <c r="BE30" s="24" t="inlineStr">
@@ -9841,7 +9889,7 @@
       </c>
       <c r="BH30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:10.870839Z</t>
+          <t>2026-08-05T13:56:08.266131Z</t>
         </is>
       </c>
       <c r="BI30" s="24" t="inlineStr">
@@ -9899,12 +9947,12 @@
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>bf6757ae2e2e4ffd</t>
+          <t>1aefac3d3c024cbd</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:12.341207Z</t>
+          <t>2026-08-05T13:56:09.744515Z</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
@@ -9949,23 +9997,23 @@
         </is>
       </c>
       <c r="L31" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="O31" s="28" t="n">
-        <v>0.558677</v>
+        <v>0.557963</v>
       </c>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="28" t="n">
-        <v>-0.000794</v>
+        <v>-0.012852</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="S31" s="29" t="n">
         <v>1</v>
@@ -9991,7 +10039,7 @@
       <c r="AD31" s="24" t="n"/>
       <c r="AE31" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-nh-lvlup-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-nh-lvlup-2026-08-06).</t>
         </is>
       </c>
       <c r="AF31" s="31" t="inlineStr">
@@ -10075,7 +10123,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -10090,7 +10138,7 @@
       </c>
       <c r="BD31" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
         </is>
       </c>
       <c r="BE31" s="24" t="inlineStr">
@@ -10110,7 +10158,7 @@
       </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:11.700160Z</t>
+          <t>2026-08-05T13:56:08.986800Z</t>
         </is>
       </c>
       <c r="BI31" s="24" t="inlineStr">
@@ -10120,13 +10168,13 @@
       </c>
       <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="BL31" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="BM31" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS31" headerRowCount="1">
-  <autoFilter ref="A1:CS31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS38" headerRowCount="1">
+  <autoFilter ref="A1:CS38"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$31)</f>
+        <f>COUNTA('Picks'!$A$2:$A$38)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$31,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$38,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")+COUNTIFS('Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")+COUNTIFS('Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$31,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$38,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")/(COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")+COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")/(COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")+COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$31)/SUM('Picks'!$BX$2:$BX$31),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$38)/SUM('Picks'!$BX$2:$BX$38),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$31)</f>
+        <f>SUM('Picks'!$BY$2:$BY$38)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$31,"&lt;&gt;",'Picks'!$AB$2:$AB$31),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$38,"&lt;&gt;",'Picks'!$AB$2:$AB$38),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$31,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$38,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$31,'Picks'!$AM$2:$AM$31,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$38,'Picks'!$AM$2:$AM$38,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS31"/>
+  <dimension ref="A1:CS38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9218,18 +9218,38 @@
       </c>
       <c r="U28" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V28" s="24" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y28" s="25" t="n"/>
-      <c r="Z28" s="26" t="n"/>
-      <c r="AA28" s="28" t="n"/>
-      <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n"/>
-      <c r="AD28" s="24" t="n"/>
+      <c r="Z28" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="AA28" s="28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB28" s="28" t="n">
+        <v>3.3e-05</v>
+      </c>
+      <c r="AC28" s="30" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:04.537577Z</t>
+        </is>
+      </c>
       <c r="AE28" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-pla-yb-2026-08-05).</t>
@@ -9372,8 +9392,12 @@
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
       <c r="BP28" s="25" t="n"/>
-      <c r="BQ28" s="27" t="n"/>
-      <c r="BR28" s="28" t="n"/>
+      <c r="BQ28" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BR28" s="28" t="n">
+        <v>0.67</v>
+      </c>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
       <c r="BU28" s="25" t="n"/>
@@ -9409,12 +9433,12 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>b56d715e272c4466</t>
+          <t>6c2da34bbed748a7</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:09.744515Z</t>
+          <t>2026-08-06T00:24:36.791267Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -9459,23 +9483,23 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.440529</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.528031</v>
+        <v>0.527212</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>0.098846</v>
+        <v>0.086683</v>
       </c>
       <c r="R29" s="26" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="S29" s="29" t="n">
         <v>1</v>
@@ -9487,21 +9511,35 @@
       </c>
       <c r="U29" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V29" s="24" t="n"/>
-      <c r="W29" s="26" t="n"/>
-      <c r="X29" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y29" s="25" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n"/>
-      <c r="AD29" s="24" t="n"/>
+      <c r="AC29" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:55:16.797850Z</t>
+        </is>
+      </c>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-dota2-lvlup-rae-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-dota2-lvlup-rae-2026-08-06).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9511,7 +9549,7 @@
       </c>
       <c r="AG29" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH29" s="24" t="n"/>
@@ -9585,7 +9623,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9600,7 +9638,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9620,7 +9658,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:07.743708Z</t>
+          <t>2026-08-06T00:24:35.411288Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9630,13 +9668,13 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.440529</v>
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
@@ -9678,12 +9716,12 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>bb4e032c2ca34ea7</t>
+          <t>dc2f368de06048d4</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:09.744515Z</t>
+          <t>2026-08-06T00:24:36.791267Z</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -9728,20 +9766,20 @@
         </is>
       </c>
       <c r="L30" s="26" t="n">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="N30" s="28" t="n">
-        <v>0.4</v>
+        <v>0.429185</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>0.611634</v>
+        <v>0.61125</v>
       </c>
       <c r="P30" s="28" t="n"/>
       <c r="Q30" s="28" t="n">
-        <v>0.211634</v>
+        <v>0.182065</v>
       </c>
       <c r="R30" s="26" t="n">
         <v>100</v>
@@ -9756,21 +9794,35 @@
       </c>
       <c r="U30" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V30" s="24" t="n"/>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y30" s="25" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n"/>
-      <c r="AD30" s="24" t="n"/>
+      <c r="AC30" s="30" t="n">
+        <v>1.995</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:55:18.434522Z</t>
+        </is>
+      </c>
       <c r="AE30" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-rae-nh-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-dota2-rae-nh-2026-08-06).</t>
         </is>
       </c>
       <c r="AF30" s="31" t="inlineStr">
@@ -9854,7 +9906,7 @@
       </c>
       <c r="BA30" s="24" t="inlineStr">
         <is>
-          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
         </is>
       </c>
       <c r="BB30" s="24" t="inlineStr">
@@ -9869,7 +9921,7 @@
       </c>
       <c r="BD30" s="24" t="inlineStr">
         <is>
-          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
         </is>
       </c>
       <c r="BE30" s="24" t="inlineStr">
@@ -9889,7 +9941,7 @@
       </c>
       <c r="BH30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:08.266131Z</t>
+          <t>2026-08-06T00:24:35.868255Z</t>
         </is>
       </c>
       <c r="BI30" s="24" t="inlineStr">
@@ -9899,13 +9951,13 @@
       </c>
       <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="BL30" s="27" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BM30" s="28" t="n">
-        <v>0.4</v>
+        <v>0.429185</v>
       </c>
       <c r="BN30" s="28" t="n"/>
       <c r="BO30" s="28" t="n"/>
@@ -9947,12 +9999,12 @@
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>1aefac3d3c024cbd</t>
+          <t>6d583ae5811d479e</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:09.744515Z</t>
+          <t>2026-08-06T00:24:36.791267Z</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
@@ -9997,49 +10049,63 @@
         </is>
       </c>
       <c r="L31" s="26" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.724638</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.579832</v>
       </c>
       <c r="O31" s="28" t="n">
-        <v>0.557963</v>
+        <v>0.55707</v>
       </c>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="28" t="n">
-        <v>-0.012852</v>
+        <v>-0.022762</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="S31" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T31" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U31" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V31" s="24" t="n"/>
-      <c r="W31" s="26" t="n"/>
-      <c r="X31" s="26" t="n"/>
+      <c r="X31" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y31" s="25" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n"/>
-      <c r="AD31" s="24" t="n"/>
+      <c r="AC31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:00:37.794982Z</t>
+        </is>
+      </c>
       <c r="AE31" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-nh-lvlup-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-nh-lvlup-2026-08-06).</t>
         </is>
       </c>
       <c r="AF31" s="31" t="inlineStr">
@@ -10075,7 +10141,7 @@
       </c>
       <c r="AO31" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP31" s="24" t="inlineStr">
@@ -10123,7 +10189,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -10138,7 +10204,7 @@
       </c>
       <c r="BD31" s="24" t="inlineStr">
         <is>
-          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
         </is>
       </c>
       <c r="BE31" s="24" t="inlineStr">
@@ -10158,7 +10224,7 @@
       </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:08.986800Z</t>
+          <t>2026-08-06T00:24:36.336119Z</t>
         </is>
       </c>
       <c r="BI31" s="24" t="inlineStr">
@@ -10168,13 +10234,13 @@
       </c>
       <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="BL31" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.724638</v>
       </c>
       <c r="BM31" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.579832</v>
       </c>
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>
@@ -10213,6 +10279,1937 @@
         </is>
       </c>
     </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>f9b4255a13754545</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:31.608591Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>71682</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.655357</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>0.08454200000000001</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W32" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AA32" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB32" s="28" t="n">
+        <v>-0.000815</v>
+      </c>
+      <c r="AC32" s="30" t="n">
+        <v>1.3158</v>
+      </c>
+      <c r="AD32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:13:02.922338Z</t>
+        </is>
+      </c>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-nh-z10-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:28.583196Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN32" s="28" t="n"/>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BR32" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="n"/>
+      <c r="CD32" s="24" t="n"/>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="n"/>
+      <c r="CJ32" s="24" t="n"/>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>8f3474fb76404d02</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:24.357961Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>71775</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.534269</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>0.134269</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>87</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA33" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB33" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:18:45.404133Z</t>
+        </is>
+      </c>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-ill-stx-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:20.860338Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN33" s="28" t="n"/>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR33" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="n"/>
+      <c r="CD33" s="24" t="n"/>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="n"/>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
+      <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>2c074976bc35472a</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:12.940920Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>71907</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.659257</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>-0.021254</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="n"/>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n"/>
+      <c r="AD34" s="24" t="n"/>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-dota2-pr-tje-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>007188172239d3dfb1106fac54f73170318b23e441cc93d6e8e709844ef5fc38</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>007188172239d3dfb1106fac54f73170318b23e441cc93d6e8e709844ef5fc38</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:10.694583Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="BN34" s="28" t="n"/>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
+      <c r="BR34" s="28" t="n"/>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="n"/>
+      <c r="CD34" s="24" t="n"/>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="n"/>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
+      <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>9ca73c7d5d2943e8</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:55.158135Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>72081</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.602486</v>
+      </c>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n">
+        <v>0.002486</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="S35" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="n"/>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="28" t="n"/>
+      <c r="AB35" s="28" t="n"/>
+      <c r="AC35" s="30" t="n"/>
+      <c r="AD35" s="24" t="n"/>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-tje-nemiga-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG35" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AQ35" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AR35" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AS35" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AT35" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AU35" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA35" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BB35" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC35" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD35" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BE35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG35" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:53.673514Z</t>
+        </is>
+      </c>
+      <c r="BI35" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM35" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN35" s="28" t="n"/>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
+      <c r="BR35" s="28" t="n"/>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+      <c r="CB35" s="24" t="n"/>
+      <c r="CC35" s="24" t="n"/>
+      <c r="CD35" s="24" t="n"/>
+      <c r="CE35" s="24" t="n"/>
+      <c r="CF35" s="24" t="n"/>
+      <c r="CG35" s="24" t="n"/>
+      <c r="CH35" s="24" t="n"/>
+      <c r="CI35" s="24" t="n"/>
+      <c r="CJ35" s="24" t="n"/>
+      <c r="CK35" s="24" t="n"/>
+      <c r="CL35" s="24" t="n"/>
+      <c r="CM35" s="24" t="n"/>
+      <c r="CN35" s="24" t="n"/>
+      <c r="CO35" s="24" t="n"/>
+      <c r="CP35" s="24" t="n"/>
+      <c r="CQ35" s="24" t="n"/>
+      <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>374baf4ba0594e7d</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:55.158135Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>74328</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.535813</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>-0.013737</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="n"/>
+      <c r="W36" s="26" t="n"/>
+      <c r="X36" s="26" t="n"/>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n"/>
+      <c r="AD36" s="24" t="n"/>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-dota2-pckcp-lynx-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:54.153981Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN36" s="28" t="n"/>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
+      <c r="BR36" s="28" t="n"/>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+      <c r="CB36" s="24" t="n"/>
+      <c r="CC36" s="24" t="n"/>
+      <c r="CD36" s="24" t="n"/>
+      <c r="CE36" s="24" t="n"/>
+      <c r="CF36" s="24" t="n"/>
+      <c r="CG36" s="24" t="n"/>
+      <c r="CH36" s="24" t="n"/>
+      <c r="CI36" s="24" t="n"/>
+      <c r="CJ36" s="24" t="n"/>
+      <c r="CK36" s="24" t="n"/>
+      <c r="CL36" s="24" t="n"/>
+      <c r="CM36" s="24" t="n"/>
+      <c r="CN36" s="24" t="n"/>
+      <c r="CO36" s="24" t="n"/>
+      <c r="CP36" s="24" t="n"/>
+      <c r="CQ36" s="24" t="n"/>
+      <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>f2a22c6d33dc4a36</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:55.158135Z</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>72729</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N37" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <v>0.645469</v>
+      </c>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n">
+        <v>0.265241</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S37" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U37" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="n"/>
+      <c r="W37" s="26" t="n"/>
+      <c r="X37" s="26" t="n"/>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="26" t="n"/>
+      <c r="AA37" s="28" t="n"/>
+      <c r="AB37" s="28" t="n"/>
+      <c r="AC37" s="30" t="n"/>
+      <c r="AD37" s="24" t="n"/>
+      <c r="AE37" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-dota2-pr-stx-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF37" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG37" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="31" t="n"/>
+      <c r="AJ37" s="31" t="n"/>
+      <c r="AK37" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN37" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP37" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AQ37" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AR37" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AS37" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AT37" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AU37" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA37" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BB37" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC37" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD37" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BE37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG37" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:54.650443Z</t>
+        </is>
+      </c>
+      <c r="BI37" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ37" s="25" t="n"/>
+      <c r="BK37" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL37" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM37" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN37" s="28" t="n"/>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
+      <c r="BR37" s="28" t="n"/>
+      <c r="BS37" s="28" t="n"/>
+      <c r="BT37" s="28" t="n"/>
+      <c r="BU37" s="25" t="n"/>
+      <c r="BV37" s="29" t="n"/>
+      <c r="BW37" s="24" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
+      <c r="BZ37" s="24" t="n"/>
+      <c r="CA37" s="31" t="n"/>
+      <c r="CB37" s="24" t="n"/>
+      <c r="CC37" s="24" t="n"/>
+      <c r="CD37" s="24" t="n"/>
+      <c r="CE37" s="24" t="n"/>
+      <c r="CF37" s="24" t="n"/>
+      <c r="CG37" s="24" t="n"/>
+      <c r="CH37" s="24" t="n"/>
+      <c r="CI37" s="24" t="n"/>
+      <c r="CJ37" s="24" t="n"/>
+      <c r="CK37" s="24" t="n"/>
+      <c r="CL37" s="24" t="n"/>
+      <c r="CM37" s="24" t="n"/>
+      <c r="CN37" s="24" t="n"/>
+      <c r="CO37" s="24" t="n"/>
+      <c r="CP37" s="24" t="n"/>
+      <c r="CQ37" s="24" t="n"/>
+      <c r="CR37" s="24" t="n"/>
+      <c r="CS37" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>5a53c162faa5448f</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:55.158135Z</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>74329</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N38" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <v>0.681484</v>
+      </c>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n">
+        <v>0.301256</v>
+      </c>
+      <c r="R38" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S38" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U38" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="n"/>
+      <c r="W38" s="26" t="n"/>
+      <c r="X38" s="26" t="n"/>
+      <c r="Y38" s="25" t="n"/>
+      <c r="Z38" s="26" t="n"/>
+      <c r="AA38" s="28" t="n"/>
+      <c r="AB38" s="28" t="n"/>
+      <c r="AC38" s="30" t="n"/>
+      <c r="AD38" s="24" t="n"/>
+      <c r="AE38" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-dota2-ill-nh-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF38" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG38" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH38" s="24" t="n"/>
+      <c r="AI38" s="31" t="n"/>
+      <c r="AJ38" s="31" t="n"/>
+      <c r="AK38" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN38" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP38" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AQ38" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AR38" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AS38" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AT38" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AU38" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AV38" s="24" t="n"/>
+      <c r="AW38" s="24" t="n"/>
+      <c r="AX38" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY38" s="24" t="n"/>
+      <c r="AZ38" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA38" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BB38" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC38" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD38" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BE38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG38" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:55.156966Z</t>
+        </is>
+      </c>
+      <c r="BI38" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ38" s="25" t="n"/>
+      <c r="BK38" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL38" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM38" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN38" s="28" t="n"/>
+      <c r="BO38" s="28" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
+      <c r="BR38" s="28" t="n"/>
+      <c r="BS38" s="28" t="n"/>
+      <c r="BT38" s="28" t="n"/>
+      <c r="BU38" s="25" t="n"/>
+      <c r="BV38" s="29" t="n"/>
+      <c r="BW38" s="24" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
+      <c r="BZ38" s="24" t="n"/>
+      <c r="CA38" s="31" t="n"/>
+      <c r="CB38" s="24" t="n"/>
+      <c r="CC38" s="24" t="n"/>
+      <c r="CD38" s="24" t="n"/>
+      <c r="CE38" s="24" t="n"/>
+      <c r="CF38" s="24" t="n"/>
+      <c r="CG38" s="24" t="n"/>
+      <c r="CH38" s="24" t="n"/>
+      <c r="CI38" s="24" t="n"/>
+      <c r="CJ38" s="24" t="n"/>
+      <c r="CK38" s="24" t="n"/>
+      <c r="CL38" s="24" t="n"/>
+      <c r="CM38" s="24" t="n"/>
+      <c r="CN38" s="24" t="n"/>
+      <c r="CO38" s="24" t="n"/>
+      <c r="CP38" s="24" t="n"/>
+      <c r="CQ38" s="24" t="n"/>
+      <c r="CR38" s="24" t="n"/>
+      <c r="CS38" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -10946,18 +10946,38 @@
       </c>
       <c r="U34" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V34" s="24" t="n"/>
-      <c r="W34" s="26" t="n"/>
-      <c r="X34" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y34" s="25" t="n"/>
-      <c r="Z34" s="26" t="n"/>
-      <c r="AA34" s="28" t="n"/>
-      <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="30" t="n"/>
-      <c r="AD34" s="24" t="n"/>
+      <c r="Z34" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="AA34" s="28" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AB34" s="28" t="n">
+        <v>-0.000511</v>
+      </c>
+      <c r="AC34" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:26:23.598929Z</t>
+        </is>
+      </c>
       <c r="AE34" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-dota2-pr-tje-2026-08-07).</t>
@@ -11100,8 +11120,12 @@
       <c r="BN34" s="28" t="n"/>
       <c r="BO34" s="28" t="n"/>
       <c r="BP34" s="25" t="n"/>
-      <c r="BQ34" s="27" t="n"/>
-      <c r="BR34" s="28" t="n"/>
+      <c r="BQ34" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BR34" s="28" t="n">
+        <v>0.68</v>
+      </c>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
       <c r="BU34" s="25" t="n"/>
@@ -11675,12 +11699,12 @@
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>f2a22c6d33dc4a36</t>
+          <t>53aa932f6d9e41c3</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:55.158135Z</t>
+          <t>2026-08-07T18:31:07.919250Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
@@ -11725,20 +11749,20 @@
         </is>
       </c>
       <c r="L37" s="26" t="n">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>2.63</v>
+        <v>2.13</v>
       </c>
       <c r="N37" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.469484</v>
       </c>
       <c r="O37" s="28" t="n">
-        <v>0.645469</v>
+        <v>0.665399</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>0.265241</v>
+        <v>0.195915</v>
       </c>
       <c r="R37" s="26" t="n">
         <v>100</v>
@@ -11767,7 +11791,7 @@
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-dota2-pr-stx-2026-08-08).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-dota2-pr-stx-2026-08-08).</t>
         </is>
       </c>
       <c r="AF37" s="31" t="inlineStr">
@@ -11851,7 +11875,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+          <t>7611cb925b0bdd8cda78eee9a465c4db63ed56bf3e0e41982af2c70978a81fdb</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -11866,7 +11890,7 @@
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+          <t>7611cb925b0bdd8cda78eee9a465c4db63ed56bf3e0e41982af2c70978a81fdb</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
@@ -11886,7 +11910,7 @@
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:54.650443Z</t>
+          <t>2026-08-07T18:31:07.387751Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">
@@ -11896,13 +11920,13 @@
       </c>
       <c r="BJ37" s="25" t="n"/>
       <c r="BK37" s="26" t="n">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="BL37" s="27" t="n">
-        <v>2.63</v>
+        <v>2.13</v>
       </c>
       <c r="BM37" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.469484</v>
       </c>
       <c r="BN37" s="28" t="n"/>
       <c r="BO37" s="28" t="n"/>
@@ -11944,12 +11968,12 @@
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>5a53c162faa5448f</t>
+          <t>989b48273cb1417d</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:55.158135Z</t>
+          <t>2026-08-07T18:31:07.919250Z</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
@@ -11994,26 +12018,26 @@
         </is>
       </c>
       <c r="L38" s="26" t="n">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="M38" s="27" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.409836</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>0.681484</v>
+        <v>0.681177</v>
       </c>
       <c r="P38" s="28" t="n"/>
       <c r="Q38" s="28" t="n">
-        <v>0.301256</v>
+        <v>0.271341</v>
       </c>
       <c r="R38" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S38" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T38" s="24" t="inlineStr">
         <is>
@@ -12036,7 +12060,7 @@
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-dota2-ill-nh-2026-08-08).</t>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-dota2-ill-nh-2026-08-08).</t>
         </is>
       </c>
       <c r="AF38" s="31" t="inlineStr">
@@ -12120,7 +12144,7 @@
       </c>
       <c r="BA38" s="24" t="inlineStr">
         <is>
-          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+          <t>7611cb925b0bdd8cda78eee9a465c4db63ed56bf3e0e41982af2c70978a81fdb</t>
         </is>
       </c>
       <c r="BB38" s="24" t="inlineStr">
@@ -12135,7 +12159,7 @@
       </c>
       <c r="BD38" s="24" t="inlineStr">
         <is>
-          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+          <t>7611cb925b0bdd8cda78eee9a465c4db63ed56bf3e0e41982af2c70978a81fdb</t>
         </is>
       </c>
       <c r="BE38" s="24" t="inlineStr">
@@ -12155,7 +12179,7 @@
       </c>
       <c r="BH38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:55.156966Z</t>
+          <t>2026-08-07T18:31:07.918561Z</t>
         </is>
       </c>
       <c r="BI38" s="24" t="inlineStr">
@@ -12165,13 +12189,13 @@
       </c>
       <c r="BJ38" s="25" t="n"/>
       <c r="BK38" s="26" t="n">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="BL38" s="27" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="BM38" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.409836</v>
       </c>
       <c r="BN38" s="28" t="n"/>
       <c r="BO38" s="28" t="n"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS25" headerRowCount="1">
-  <autoFilter ref="A1:CS25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS47" headerRowCount="1">
+  <autoFilter ref="A1:CS47"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$25)</f>
+        <f>COUNTA('Picks'!$A$2:$A$47)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$25,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$47,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$47,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"win")+COUNTIFS('Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$25,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$47,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$47,"&gt;0",'Picks'!$V$2:$V$47,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$47,"&gt;0",'Picks'!$V$2:$V$47,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")/(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$47,"&gt;0",'Picks'!$V$2:$V$47,"win")/(COUNTIFS('Picks'!$BX$2:$BX$47,"&gt;0",'Picks'!$V$2:$V$47,"win")+COUNTIFS('Picks'!$BX$2:$BX$47,"&gt;0",'Picks'!$V$2:$V$47,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$25)/SUM('Picks'!$BX$2:$BX$25),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$47)/SUM('Picks'!$BX$2:$BX$47),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$25)</f>
+        <f>SUM('Picks'!$BY$2:$BY$47)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$25,"&lt;&gt;",'Picks'!$AB$2:$AB$25),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$47,"&lt;&gt;",'Picks'!$AB$2:$AB$47),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$47,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$47,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$25,'Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$47,'Picks'!$AM$2:$AM$47,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$47,$A14,'Picks'!$U$2:$U$47,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$47,$A14,'Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$47,$A14,'Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$47,'Picks'!$H$2:$H$47,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$47,'Picks'!$H$2:$H$47,$A14,'Picks'!$U$2:$U$47,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$47,$A15,'Picks'!$U$2:$U$47,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$47,$A15,'Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$47,$A15,'Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$47,'Picks'!$H$2:$H$47,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$47,'Picks'!$H$2:$H$47,$A15,'Picks'!$U$2:$U$47,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$47,$A16,'Picks'!$U$2:$U$47,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$47,$A16,'Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$47,$A16,'Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$47,'Picks'!$H$2:$H$47,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$47,'Picks'!$H$2:$H$47,$A16,'Picks'!$U$2:$U$47,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS25"/>
+  <dimension ref="A1:CS47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1869,8 +1869,12 @@
       <c r="BU2" s="25" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="30" t="n"/>
-      <c r="BY2" s="27" t="n"/>
+      <c r="BX2" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY2" s="27" t="n">
+        <v>-1</v>
+      </c>
       <c r="BZ2" s="24" t="n"/>
       <c r="CA2" s="31" t="n"/>
       <c r="CB2" s="24" t="n"/>
@@ -2158,8 +2162,12 @@
       <c r="BU3" s="25" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="30" t="n"/>
-      <c r="BY3" s="27" t="n"/>
+      <c r="BX3" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY3" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ3" s="24" t="n"/>
       <c r="CA3" s="31" t="n"/>
       <c r="CB3" s="24" t="n"/>
@@ -2447,8 +2455,12 @@
       <c r="BU4" s="25" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="30" t="n"/>
-      <c r="BY4" s="27" t="n"/>
+      <c r="BX4" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY4" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ4" s="24" t="n"/>
       <c r="CA4" s="31" t="n"/>
       <c r="CB4" s="24" t="n"/>
@@ -2736,8 +2748,12 @@
       <c r="BU5" s="25" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="30" t="n"/>
-      <c r="BY5" s="27" t="n"/>
+      <c r="BX5" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY5" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ5" s="24" t="n"/>
       <c r="CA5" s="31" t="n"/>
       <c r="CB5" s="24" t="n"/>
@@ -3025,8 +3041,12 @@
       <c r="BU6" s="25" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="30" t="n"/>
-      <c r="BY6" s="27" t="n"/>
+      <c r="BX6" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY6" s="27" t="n">
+        <v>-1</v>
+      </c>
       <c r="BZ6" s="24" t="n"/>
       <c r="CA6" s="31" t="n"/>
       <c r="CB6" s="24" t="n"/>
@@ -3304,8 +3324,12 @@
       <c r="BU7" s="25" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="30" t="n"/>
-      <c r="BY7" s="27" t="n"/>
+      <c r="BX7" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY7" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ7" s="24" t="n"/>
       <c r="CA7" s="31" t="n"/>
       <c r="CB7" s="24" t="n"/>
@@ -3583,8 +3607,12 @@
       <c r="BU8" s="25" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n"/>
-      <c r="BY8" s="27" t="n"/>
+      <c r="BX8" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY8" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ8" s="24" t="n"/>
       <c r="CA8" s="31" t="n"/>
       <c r="CB8" s="24" t="n"/>
@@ -3872,8 +3900,12 @@
       <c r="BU9" s="25" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n"/>
-      <c r="BY9" s="27" t="n"/>
+      <c r="BX9" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY9" s="27" t="n">
+        <v>-1</v>
+      </c>
       <c r="BZ9" s="24" t="n"/>
       <c r="CA9" s="31" t="n"/>
       <c r="CB9" s="24" t="n"/>
@@ -4161,8 +4193,12 @@
       <c r="BU10" s="25" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n"/>
-      <c r="BY10" s="27" t="n"/>
+      <c r="BX10" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY10" s="27" t="n">
+        <v>-1</v>
+      </c>
       <c r="BZ10" s="24" t="n"/>
       <c r="CA10" s="31" t="n"/>
       <c r="CB10" s="24" t="n"/>
@@ -4450,8 +4486,12 @@
       <c r="BU11" s="25" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n"/>
-      <c r="BY11" s="27" t="n"/>
+      <c r="BX11" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY11" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ11" s="24" t="n"/>
       <c r="CA11" s="31" t="n"/>
       <c r="CB11" s="24" t="n"/>
@@ -4739,8 +4779,12 @@
       <c r="BU12" s="25" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n"/>
-      <c r="BY12" s="27" t="n"/>
+      <c r="BX12" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY12" s="27" t="n">
+        <v>-1</v>
+      </c>
       <c r="BZ12" s="24" t="n"/>
       <c r="CA12" s="31" t="n"/>
       <c r="CB12" s="24" t="n"/>
@@ -5028,8 +5072,12 @@
       <c r="BU13" s="25" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n"/>
-      <c r="BY13" s="27" t="n"/>
+      <c r="BX13" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY13" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ13" s="24" t="n"/>
       <c r="CA13" s="31" t="n"/>
       <c r="CB13" s="24" t="n"/>
@@ -5317,8 +5365,12 @@
       <c r="BU14" s="25" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="30" t="n"/>
-      <c r="BY14" s="27" t="n"/>
+      <c r="BX14" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY14" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ14" s="24" t="n"/>
       <c r="CA14" s="31" t="n"/>
       <c r="CB14" s="24" t="n"/>
@@ -5606,8 +5658,12 @@
       <c r="BU15" s="25" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n"/>
-      <c r="BY15" s="27" t="n"/>
+      <c r="BX15" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY15" s="27" t="n">
+        <v>-1</v>
+      </c>
       <c r="BZ15" s="24" t="n"/>
       <c r="CA15" s="31" t="n"/>
       <c r="CB15" s="24" t="n"/>
@@ -5895,8 +5951,12 @@
       <c r="BU16" s="25" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n"/>
-      <c r="BY16" s="27" t="n"/>
+      <c r="BX16" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY16" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ16" s="24" t="n"/>
       <c r="CA16" s="31" t="n"/>
       <c r="CB16" s="24" t="n"/>
@@ -6184,8 +6244,12 @@
       <c r="BU17" s="25" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n"/>
-      <c r="BY17" s="27" t="n"/>
+      <c r="BX17" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY17" s="27" t="n">
+        <v>-1</v>
+      </c>
       <c r="BZ17" s="24" t="n"/>
       <c r="CA17" s="31" t="n"/>
       <c r="CB17" s="24" t="n"/>
@@ -6473,8 +6537,12 @@
       <c r="BU18" s="25" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n"/>
-      <c r="BY18" s="27" t="n"/>
+      <c r="BX18" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY18" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ18" s="24" t="n"/>
       <c r="CA18" s="31" t="n"/>
       <c r="CB18" s="24" t="n"/>
@@ -6766,8 +6834,12 @@
       <c r="BU19" s="25" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="30" t="n"/>
-      <c r="BY19" s="27" t="n"/>
+      <c r="BX19" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY19" s="27" t="n">
+        <v>-1</v>
+      </c>
       <c r="BZ19" s="24" t="n"/>
       <c r="CA19" s="31" t="n"/>
       <c r="CB19" s="24" t="n"/>
@@ -7059,8 +7131,12 @@
       <c r="BU20" s="25" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="30" t="n"/>
-      <c r="BY20" s="27" t="n"/>
+      <c r="BX20" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY20" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ20" s="24" t="n"/>
       <c r="CA20" s="31" t="n"/>
       <c r="CB20" s="24" t="n"/>
@@ -7352,8 +7428,12 @@
       <c r="BU21" s="25" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
+      <c r="BX21" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY21" s="27" t="n">
+        <v>-1</v>
+      </c>
       <c r="BZ21" s="24" t="n"/>
       <c r="CA21" s="31" t="n"/>
       <c r="CB21" s="24" t="n"/>
@@ -7645,8 +7725,12 @@
       <c r="BU22" s="25" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
+      <c r="BX22" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY22" s="27" t="n">
+        <v>-1</v>
+      </c>
       <c r="BZ22" s="24" t="n"/>
       <c r="CA22" s="31" t="n"/>
       <c r="CB22" s="24" t="n"/>
@@ -7938,8 +8022,12 @@
       <c r="BU23" s="25" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n"/>
-      <c r="BY23" s="27" t="n"/>
+      <c r="BX23" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY23" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ23" s="24" t="n"/>
       <c r="CA23" s="31" t="n"/>
       <c r="CB23" s="24" t="n"/>
@@ -8046,18 +8134,38 @@
       </c>
       <c r="U24" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y24" s="25" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="28" t="n"/>
-      <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="24" t="n"/>
+      <c r="Z24" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="AA24" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB24" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:02.952248Z</t>
+        </is>
+      </c>
       <c r="AE24" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-yb-re-2026-08-04).</t>
@@ -8070,7 +8178,7 @@
       </c>
       <c r="AG24" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH24" s="24" t="n"/>
@@ -8200,15 +8308,23 @@
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
       <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
-      <c r="BR24" s="28" t="n"/>
+      <c r="BQ24" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BR24" s="28" t="n">
+        <v>0.6</v>
+      </c>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
       <c r="BU24" s="25" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="30" t="n"/>
-      <c r="BY24" s="27" t="n"/>
+      <c r="BX24" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY24" s="27" t="n">
+        <v>-1</v>
+      </c>
       <c r="BZ24" s="24" t="n"/>
       <c r="CA24" s="31" t="n"/>
       <c r="CB24" s="24" t="n"/>
@@ -8315,18 +8431,38 @@
       </c>
       <c r="U25" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y25" s="25" t="n"/>
-      <c r="Z25" s="26" t="n"/>
-      <c r="AA25" s="28" t="n"/>
-      <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n"/>
-      <c r="AD25" s="24" t="n"/>
+      <c r="Z25" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="AA25" s="28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AB25" s="28" t="n">
+        <v>-0.00035</v>
+      </c>
+      <c r="AC25" s="30" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:05.209291Z</t>
+        </is>
+      </c>
       <c r="AE25" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-dota2-flc-liquid-2026-08-04).</t>
@@ -8469,15 +8605,23 @@
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
       <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
-      <c r="BR25" s="28" t="n"/>
+      <c r="BQ25" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BR25" s="28" t="n">
+        <v>0.65</v>
+      </c>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
       <c r="BU25" s="25" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="30" t="n"/>
-      <c r="BY25" s="27" t="n"/>
+      <c r="BX25" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY25" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ25" s="24" t="n"/>
       <c r="CA25" s="31" t="n"/>
       <c r="CB25" s="24" t="n"/>
@@ -8503,6 +8647,6506 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>8804b09f2e484069</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>72079</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.500216</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>0.049766</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA26" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB26" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC26" s="30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:17:02.060126Z</t>
+        </is>
+      </c>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-tr-re-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:08.611098Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR26" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY26" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>38b2b0d956f84f99</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>71970</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.658681</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>0.128165</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA27" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB27" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC27" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:50:43.202468Z</t>
+        </is>
+      </c>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-1win-bb-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:09.196950Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR27" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY27" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>8300edfe97dd4fab</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:31.198892Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>72080</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.805779</v>
+      </c>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n">
+        <v>0.135812</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="AA28" s="28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB28" s="28" t="n">
+        <v>3.3e-05</v>
+      </c>
+      <c r="AC28" s="30" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:04.537577Z</t>
+        </is>
+      </c>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-pla-yb-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:27.725458Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN28" s="28" t="n"/>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BR28" s="28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY28" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="n"/>
+      <c r="CD28" s="24" t="n"/>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="n"/>
+      <c r="CJ28" s="24" t="n"/>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>6c2da34bbed748a7</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:36.791267Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>70575</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.527212</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>0.086683</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>63</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:55:16.797850Z</t>
+        </is>
+      </c>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-dota2-lvlup-rae-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:35.411288Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY29" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="n"/>
+      <c r="CD29" s="24" t="n"/>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="n"/>
+      <c r="CJ29" s="24" t="n"/>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>dc2f368de06048d4</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:36.791267Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>70648</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.61125</v>
+      </c>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n">
+        <v>0.182065</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n">
+        <v>1.995</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:55:18.434522Z</t>
+        </is>
+      </c>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-dota2-rae-nh-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:35.868255Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="BN30" s="28" t="n"/>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY30" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="n"/>
+      <c r="CD30" s="24" t="n"/>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="n"/>
+      <c r="CJ30" s="24" t="n"/>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>6d583ae5811d479e</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:36.791267Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.55707</v>
+      </c>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n">
+        <v>-0.022762</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="28" t="n"/>
+      <c r="AC31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:00:37.794982Z</t>
+        </is>
+      </c>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-nh-lvlup-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:36.336119Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN31" s="28" t="n"/>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY31" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="n"/>
+      <c r="CD31" s="24" t="n"/>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="n"/>
+      <c r="CJ31" s="24" t="n"/>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>f9b4255a13754545</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:31.608591Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>71682</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.655357</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>0.08454200000000001</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W32" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AA32" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB32" s="28" t="n">
+        <v>-0.000815</v>
+      </c>
+      <c r="AC32" s="30" t="n">
+        <v>1.3158</v>
+      </c>
+      <c r="AD32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:13:02.922338Z</t>
+        </is>
+      </c>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-nh-z10-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:28.583196Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN32" s="28" t="n"/>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BR32" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY32" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="n"/>
+      <c r="CD32" s="24" t="n"/>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="n"/>
+      <c r="CJ32" s="24" t="n"/>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>8f3474fb76404d02</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:24.357961Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>71775</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.534269</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>0.134269</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>87</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA33" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB33" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:18:45.404133Z</t>
+        </is>
+      </c>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-ill-stx-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:20.860338Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN33" s="28" t="n"/>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR33" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY33" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="n"/>
+      <c r="CD33" s="24" t="n"/>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="n"/>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
+      <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>2c074976bc35472a</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:12.940920Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>71907</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.659257</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>-0.021254</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="AA34" s="28" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AB34" s="28" t="n">
+        <v>-0.000511</v>
+      </c>
+      <c r="AC34" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:26:23.598929Z</t>
+        </is>
+      </c>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-dota2-pr-tje-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>007188172239d3dfb1106fac54f73170318b23e441cc93d6e8e709844ef5fc38</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>007188172239d3dfb1106fac54f73170318b23e441cc93d6e8e709844ef5fc38</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:10.694583Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="BN34" s="28" t="n"/>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BR34" s="28" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY34" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="n"/>
+      <c r="CD34" s="24" t="n"/>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="n"/>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
+      <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>9ca73c7d5d2943e8</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:55.158135Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>72081</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.602486</v>
+      </c>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n">
+        <v>0.002486</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="S35" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="AA35" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB35" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:54:41.451613Z</t>
+        </is>
+      </c>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-tje-nemiga-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG35" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AQ35" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AR35" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AS35" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AT35" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AU35" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA35" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BB35" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC35" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD35" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BE35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG35" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:53.673514Z</t>
+        </is>
+      </c>
+      <c r="BI35" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM35" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN35" s="28" t="n"/>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BR35" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY35" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+      <c r="CB35" s="24" t="n"/>
+      <c r="CC35" s="24" t="n"/>
+      <c r="CD35" s="24" t="n"/>
+      <c r="CE35" s="24" t="n"/>
+      <c r="CF35" s="24" t="n"/>
+      <c r="CG35" s="24" t="n"/>
+      <c r="CH35" s="24" t="n"/>
+      <c r="CI35" s="24" t="n"/>
+      <c r="CJ35" s="24" t="n"/>
+      <c r="CK35" s="24" t="n"/>
+      <c r="CL35" s="24" t="n"/>
+      <c r="CM35" s="24" t="n"/>
+      <c r="CN35" s="24" t="n"/>
+      <c r="CO35" s="24" t="n"/>
+      <c r="CP35" s="24" t="n"/>
+      <c r="CQ35" s="24" t="n"/>
+      <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>374baf4ba0594e7d</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:55.158135Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>74328</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.535813</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>-0.013737</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="AA36" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AB36" s="28" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AC36" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T00:59:28.831999Z</t>
+        </is>
+      </c>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-dota2-pckcp-lynx-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:54.153981Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN36" s="28" t="n"/>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BR36" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY36" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+      <c r="CB36" s="24" t="n"/>
+      <c r="CC36" s="24" t="n"/>
+      <c r="CD36" s="24" t="n"/>
+      <c r="CE36" s="24" t="n"/>
+      <c r="CF36" s="24" t="n"/>
+      <c r="CG36" s="24" t="n"/>
+      <c r="CH36" s="24" t="n"/>
+      <c r="CI36" s="24" t="n"/>
+      <c r="CJ36" s="24" t="n"/>
+      <c r="CK36" s="24" t="n"/>
+      <c r="CL36" s="24" t="n"/>
+      <c r="CM36" s="24" t="n"/>
+      <c r="CN36" s="24" t="n"/>
+      <c r="CO36" s="24" t="n"/>
+      <c r="CP36" s="24" t="n"/>
+      <c r="CQ36" s="24" t="n"/>
+      <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>b89b6694dfff4234</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:07:53.607771Z</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>74329</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N37" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <v>0.694921</v>
+      </c>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n">
+        <v>0.274753</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S37" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U37" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W37" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="AA37" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB37" s="28" t="n">
+        <v>-0.000168</v>
+      </c>
+      <c r="AC37" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:34:03.559160Z</t>
+        </is>
+      </c>
+      <c r="AE37" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-dota2-ill-nh-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF37" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG37" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="31" t="n"/>
+      <c r="AJ37" s="31" t="n"/>
+      <c r="AK37" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN37" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP37" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AQ37" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AR37" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AS37" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AT37" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AU37" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA37" s="24" t="inlineStr">
+        <is>
+          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
+        </is>
+      </c>
+      <c r="BB37" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC37" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD37" s="24" t="inlineStr">
+        <is>
+          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
+        </is>
+      </c>
+      <c r="BE37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG37" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:07:52.173653Z</t>
+        </is>
+      </c>
+      <c r="BI37" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ37" s="25" t="n"/>
+      <c r="BK37" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL37" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM37" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN37" s="28" t="n"/>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BR37" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BS37" s="28" t="n"/>
+      <c r="BT37" s="28" t="n"/>
+      <c r="BU37" s="25" t="n"/>
+      <c r="BV37" s="29" t="n"/>
+      <c r="BW37" s="24" t="n"/>
+      <c r="BX37" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY37" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ37" s="24" t="n"/>
+      <c r="CA37" s="31" t="n"/>
+      <c r="CB37" s="24" t="n"/>
+      <c r="CC37" s="24" t="n"/>
+      <c r="CD37" s="24" t="n"/>
+      <c r="CE37" s="24" t="n"/>
+      <c r="CF37" s="24" t="n"/>
+      <c r="CG37" s="24" t="n"/>
+      <c r="CH37" s="24" t="n"/>
+      <c r="CI37" s="24" t="n"/>
+      <c r="CJ37" s="24" t="n"/>
+      <c r="CK37" s="24" t="n"/>
+      <c r="CL37" s="24" t="n"/>
+      <c r="CM37" s="24" t="n"/>
+      <c r="CN37" s="24" t="n"/>
+      <c r="CO37" s="24" t="n"/>
+      <c r="CP37" s="24" t="n"/>
+      <c r="CQ37" s="24" t="n"/>
+      <c r="CR37" s="24" t="n"/>
+      <c r="CS37" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>31194c9091464e31</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:07:53.607771Z</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>74944</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>FTS</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N38" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <v>0.533843</v>
+      </c>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n">
+        <v>0.143218</v>
+      </c>
+      <c r="R38" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="S38" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U38" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" s="25" t="n"/>
+      <c r="Z38" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA38" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB38" s="28" t="n">
+        <v>0.009375</v>
+      </c>
+      <c r="AC38" s="30" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:34:05.005944Z</t>
+        </is>
+      </c>
+      <c r="AE38" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-fts-pckcp-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF38" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG38" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH38" s="24" t="n"/>
+      <c r="AI38" s="31" t="n"/>
+      <c r="AJ38" s="31" t="n"/>
+      <c r="AK38" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN38" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP38" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AQ38" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AR38" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AS38" s="24" t="inlineStr">
+        <is>
+          <t>FTS</t>
+        </is>
+      </c>
+      <c r="AT38" s="24" t="inlineStr">
+        <is>
+          <t>FTS</t>
+        </is>
+      </c>
+      <c r="AU38" s="24" t="inlineStr">
+        <is>
+          <t>FTS</t>
+        </is>
+      </c>
+      <c r="AV38" s="24" t="n"/>
+      <c r="AW38" s="24" t="n"/>
+      <c r="AX38" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY38" s="24" t="n"/>
+      <c r="AZ38" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA38" s="24" t="inlineStr">
+        <is>
+          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
+        </is>
+      </c>
+      <c r="BB38" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC38" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD38" s="24" t="inlineStr">
+        <is>
+          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
+        </is>
+      </c>
+      <c r="BE38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG38" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:07:52.761230Z</t>
+        </is>
+      </c>
+      <c r="BI38" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ38" s="25" t="n"/>
+      <c r="BK38" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL38" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM38" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN38" s="28" t="n"/>
+      <c r="BO38" s="28" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR38" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BS38" s="28" t="n"/>
+      <c r="BT38" s="28" t="n"/>
+      <c r="BU38" s="25" t="n"/>
+      <c r="BV38" s="29" t="n"/>
+      <c r="BW38" s="24" t="n"/>
+      <c r="BX38" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY38" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ38" s="24" t="n"/>
+      <c r="CA38" s="31" t="n"/>
+      <c r="CB38" s="24" t="n"/>
+      <c r="CC38" s="24" t="n"/>
+      <c r="CD38" s="24" t="n"/>
+      <c r="CE38" s="24" t="n"/>
+      <c r="CF38" s="24" t="n"/>
+      <c r="CG38" s="24" t="n"/>
+      <c r="CH38" s="24" t="n"/>
+      <c r="CI38" s="24" t="n"/>
+      <c r="CJ38" s="24" t="n"/>
+      <c r="CK38" s="24" t="n"/>
+      <c r="CL38" s="24" t="n"/>
+      <c r="CM38" s="24" t="n"/>
+      <c r="CN38" s="24" t="n"/>
+      <c r="CO38" s="24" t="n"/>
+      <c r="CP38" s="24" t="n"/>
+      <c r="CQ38" s="24" t="n"/>
+      <c r="CR38" s="24" t="n"/>
+      <c r="CS38" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>498cd253705a4950</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:18:31.005738Z</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>75946</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J39" s="25" t="n"/>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N39" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O39" s="28" t="n">
+        <v>0.564048</v>
+      </c>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="28" t="n">
+        <v>0.014498</v>
+      </c>
+      <c r="R39" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="S39" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U39" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V39" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W39" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="25" t="n"/>
+      <c r="Z39" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="AA39" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AB39" s="28" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AC39" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T13:55:56.963082Z</t>
+        </is>
+      </c>
+      <c r="AE39" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-dota2-pr-yes-2026-08-09).</t>
+        </is>
+      </c>
+      <c r="AF39" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG39" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH39" s="24" t="n"/>
+      <c r="AI39" s="31" t="n"/>
+      <c r="AJ39" s="31" t="n"/>
+      <c r="AK39" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL39" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM39" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN39" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO39" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP39" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AQ39" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AR39" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AS39" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AT39" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AU39" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AV39" s="24" t="n"/>
+      <c r="AW39" s="24" t="n"/>
+      <c r="AX39" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY39" s="24" t="n"/>
+      <c r="AZ39" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA39" s="24" t="inlineStr">
+        <is>
+          <t>f61d33108d741f882603707769cb7ff07bbf39b21ddf16b7bc925dd926d15ddb</t>
+        </is>
+      </c>
+      <c r="BB39" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC39" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD39" s="24" t="inlineStr">
+        <is>
+          <t>f61d33108d741f882603707769cb7ff07bbf39b21ddf16b7bc925dd926d15ddb</t>
+        </is>
+      </c>
+      <c r="BE39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG39" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:18:27.012322Z</t>
+        </is>
+      </c>
+      <c r="BI39" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ39" s="25" t="n"/>
+      <c r="BK39" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL39" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM39" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN39" s="28" t="n"/>
+      <c r="BO39" s="28" t="n"/>
+      <c r="BP39" s="25" t="n"/>
+      <c r="BQ39" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BR39" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BS39" s="28" t="n"/>
+      <c r="BT39" s="28" t="n"/>
+      <c r="BU39" s="25" t="n"/>
+      <c r="BV39" s="29" t="n"/>
+      <c r="BW39" s="24" t="n"/>
+      <c r="BX39" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY39" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ39" s="24" t="n"/>
+      <c r="CA39" s="31" t="n"/>
+      <c r="CB39" s="24" t="n"/>
+      <c r="CC39" s="24" t="n"/>
+      <c r="CD39" s="24" t="n"/>
+      <c r="CE39" s="24" t="n"/>
+      <c r="CF39" s="24" t="n"/>
+      <c r="CG39" s="24" t="n"/>
+      <c r="CH39" s="24" t="n"/>
+      <c r="CI39" s="24" t="n"/>
+      <c r="CJ39" s="24" t="n"/>
+      <c r="CK39" s="24" t="n"/>
+      <c r="CL39" s="24" t="n"/>
+      <c r="CM39" s="24" t="n"/>
+      <c r="CN39" s="24" t="n"/>
+      <c r="CO39" s="24" t="n"/>
+      <c r="CP39" s="24" t="n"/>
+      <c r="CQ39" s="24" t="n"/>
+      <c r="CR39" s="24" t="n"/>
+      <c r="CS39" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>17945d149d364c4a</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:18:31.005738Z</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>75947</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>FTS</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J40" s="25" t="n"/>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M40" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N40" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O40" s="28" t="n">
+        <v>0.527271</v>
+      </c>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="28" t="n">
+        <v>-0.003245</v>
+      </c>
+      <c r="R40" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="S40" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U40" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V40" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" s="25" t="n"/>
+      <c r="Z40" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA40" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB40" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC40" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:04:09.445721Z</t>
+        </is>
+      </c>
+      <c r="AE40" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-nh-fts-2026-08-09).</t>
+        </is>
+      </c>
+      <c r="AF40" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG40" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH40" s="24" t="n"/>
+      <c r="AI40" s="31" t="n"/>
+      <c r="AJ40" s="31" t="n"/>
+      <c r="AK40" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL40" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM40" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN40" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO40" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP40" s="24" t="inlineStr">
+        <is>
+          <t>FTS</t>
+        </is>
+      </c>
+      <c r="AQ40" s="24" t="inlineStr">
+        <is>
+          <t>FTS</t>
+        </is>
+      </c>
+      <c r="AR40" s="24" t="inlineStr">
+        <is>
+          <t>FTS</t>
+        </is>
+      </c>
+      <c r="AS40" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AT40" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AU40" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AV40" s="24" t="n"/>
+      <c r="AW40" s="24" t="n"/>
+      <c r="AX40" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY40" s="24" t="n"/>
+      <c r="AZ40" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA40" s="24" t="inlineStr">
+        <is>
+          <t>f61d33108d741f882603707769cb7ff07bbf39b21ddf16b7bc925dd926d15ddb</t>
+        </is>
+      </c>
+      <c r="BB40" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC40" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD40" s="24" t="inlineStr">
+        <is>
+          <t>f61d33108d741f882603707769cb7ff07bbf39b21ddf16b7bc925dd926d15ddb</t>
+        </is>
+      </c>
+      <c r="BE40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG40" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:18:27.708910Z</t>
+        </is>
+      </c>
+      <c r="BI40" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ40" s="25" t="n"/>
+      <c r="BK40" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL40" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM40" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN40" s="28" t="n"/>
+      <c r="BO40" s="28" t="n"/>
+      <c r="BP40" s="25" t="n"/>
+      <c r="BQ40" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR40" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BS40" s="28" t="n"/>
+      <c r="BT40" s="28" t="n"/>
+      <c r="BU40" s="25" t="n"/>
+      <c r="BV40" s="29" t="n"/>
+      <c r="BW40" s="24" t="n"/>
+      <c r="BX40" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY40" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ40" s="24" t="n"/>
+      <c r="CA40" s="31" t="n"/>
+      <c r="CB40" s="24" t="n"/>
+      <c r="CC40" s="24" t="n"/>
+      <c r="CD40" s="24" t="n"/>
+      <c r="CE40" s="24" t="n"/>
+      <c r="CF40" s="24" t="n"/>
+      <c r="CG40" s="24" t="n"/>
+      <c r="CH40" s="24" t="n"/>
+      <c r="CI40" s="24" t="n"/>
+      <c r="CJ40" s="24" t="n"/>
+      <c r="CK40" s="24" t="n"/>
+      <c r="CL40" s="24" t="n"/>
+      <c r="CM40" s="24" t="n"/>
+      <c r="CN40" s="24" t="n"/>
+      <c r="CO40" s="24" t="n"/>
+      <c r="CP40" s="24" t="n"/>
+      <c r="CQ40" s="24" t="n"/>
+      <c r="CR40" s="24" t="n"/>
+      <c r="CS40" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>4a1e3c7d1c9b4155</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:08:12.247912Z</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>75151</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J41" s="25" t="n"/>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M41" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N41" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O41" s="28" t="n">
+        <v>0.504538</v>
+      </c>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="28" t="n">
+        <v>-0.165429</v>
+      </c>
+      <c r="R41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U41" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V41" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" s="25" t="n"/>
+      <c r="Z41" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="AA41" s="28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB41" s="28" t="n">
+        <v>3.3e-05</v>
+      </c>
+      <c r="AC41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T23:30:28.508007Z</t>
+        </is>
+      </c>
+      <c r="AE41" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-rae-ill-2026-08-09).</t>
+        </is>
+      </c>
+      <c r="AF41" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG41" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH41" s="24" t="n"/>
+      <c r="AI41" s="31" t="n"/>
+      <c r="AJ41" s="31" t="n"/>
+      <c r="AK41" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL41" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM41" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN41" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO41" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP41" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AQ41" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AR41" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AS41" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AT41" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AU41" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AV41" s="24" t="n"/>
+      <c r="AW41" s="24" t="n"/>
+      <c r="AX41" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY41" s="24" t="n"/>
+      <c r="AZ41" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA41" s="24" t="inlineStr">
+        <is>
+          <t>b3e966da2714bd7fcf36794fa00bf8ff367c9e7acb64b21fcab64e7b7cbb4474</t>
+        </is>
+      </c>
+      <c r="BB41" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC41" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD41" s="24" t="inlineStr">
+        <is>
+          <t>b3e966da2714bd7fcf36794fa00bf8ff367c9e7acb64b21fcab64e7b7cbb4474</t>
+        </is>
+      </c>
+      <c r="BE41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG41" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:08:10.205915Z</t>
+        </is>
+      </c>
+      <c r="BI41" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ41" s="25" t="n"/>
+      <c r="BK41" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL41" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM41" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN41" s="28" t="n"/>
+      <c r="BO41" s="28" t="n"/>
+      <c r="BP41" s="25" t="n"/>
+      <c r="BQ41" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BR41" s="28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BS41" s="28" t="n"/>
+      <c r="BT41" s="28" t="n"/>
+      <c r="BU41" s="25" t="n"/>
+      <c r="BV41" s="29" t="n"/>
+      <c r="BW41" s="24" t="n"/>
+      <c r="BX41" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY41" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ41" s="24" t="n"/>
+      <c r="CA41" s="31" t="n"/>
+      <c r="CB41" s="24" t="n"/>
+      <c r="CC41" s="24" t="n"/>
+      <c r="CD41" s="24" t="n"/>
+      <c r="CE41" s="24" t="n"/>
+      <c r="CF41" s="24" t="n"/>
+      <c r="CG41" s="24" t="n"/>
+      <c r="CH41" s="24" t="n"/>
+      <c r="CI41" s="24" t="n"/>
+      <c r="CJ41" s="24" t="n"/>
+      <c r="CK41" s="24" t="n"/>
+      <c r="CL41" s="24" t="n"/>
+      <c r="CM41" s="24" t="n"/>
+      <c r="CN41" s="24" t="n"/>
+      <c r="CO41" s="24" t="n"/>
+      <c r="CP41" s="24" t="n"/>
+      <c r="CQ41" s="24" t="n"/>
+      <c r="CR41" s="24" t="n"/>
+      <c r="CS41" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>3aa260f4b4544e6b</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:41:14.399564Z</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>76395</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M42" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N42" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O42" s="28" t="n">
+        <v>0.617196</v>
+      </c>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="28" t="n">
+        <v>0.166746</v>
+      </c>
+      <c r="R42" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S42" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T42" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U42" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W42" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="25" t="n"/>
+      <c r="Z42" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA42" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB42" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC42" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:32:31.697144Z</t>
+        </is>
+      </c>
+      <c r="AE42" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-pr-mouz-2026-08-10).</t>
+        </is>
+      </c>
+      <c r="AF42" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG42" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH42" s="24" t="n"/>
+      <c r="AI42" s="31" t="n"/>
+      <c r="AJ42" s="31" t="n"/>
+      <c r="AK42" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM42" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN42" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO42" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP42" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AQ42" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AR42" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AS42" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AT42" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AU42" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AV42" s="24" t="n"/>
+      <c r="AW42" s="24" t="n"/>
+      <c r="AX42" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY42" s="24" t="n"/>
+      <c r="AZ42" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA42" s="24" t="inlineStr">
+        <is>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
+        </is>
+      </c>
+      <c r="BB42" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC42" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD42" s="24" t="inlineStr">
+        <is>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
+        </is>
+      </c>
+      <c r="BE42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG42" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:41:11.396742Z</t>
+        </is>
+      </c>
+      <c r="BI42" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ42" s="25" t="n"/>
+      <c r="BK42" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL42" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM42" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN42" s="28" t="n"/>
+      <c r="BO42" s="28" t="n"/>
+      <c r="BP42" s="25" t="n"/>
+      <c r="BQ42" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR42" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BS42" s="28" t="n"/>
+      <c r="BT42" s="28" t="n"/>
+      <c r="BU42" s="25" t="n"/>
+      <c r="BV42" s="29" t="n"/>
+      <c r="BW42" s="24" t="n"/>
+      <c r="BX42" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY42" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ42" s="24" t="n"/>
+      <c r="CA42" s="31" t="n"/>
+      <c r="CB42" s="24" t="n"/>
+      <c r="CC42" s="24" t="n"/>
+      <c r="CD42" s="24" t="n"/>
+      <c r="CE42" s="24" t="n"/>
+      <c r="CF42" s="24" t="n"/>
+      <c r="CG42" s="24" t="n"/>
+      <c r="CH42" s="24" t="n"/>
+      <c r="CI42" s="24" t="n"/>
+      <c r="CJ42" s="24" t="n"/>
+      <c r="CK42" s="24" t="n"/>
+      <c r="CL42" s="24" t="n"/>
+      <c r="CM42" s="24" t="n"/>
+      <c r="CN42" s="24" t="n"/>
+      <c r="CO42" s="24" t="n"/>
+      <c r="CP42" s="24" t="n"/>
+      <c r="CQ42" s="24" t="n"/>
+      <c r="CR42" s="24" t="n"/>
+      <c r="CS42" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>10b350a8956c47aa</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:41:14.399564Z</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>76906</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J43" s="25" t="n"/>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L43" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M43" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N43" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O43" s="28" t="n">
+        <v>0.602651</v>
+      </c>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="28" t="n">
+        <v>0.012487</v>
+      </c>
+      <c r="R43" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="S43" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T43" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U43" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V43" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W43" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="25" t="n"/>
+      <c r="Z43" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="AA43" s="28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AB43" s="28" t="n">
+        <v>-0.000164</v>
+      </c>
+      <c r="AC43" s="30" t="n">
+        <v>0.8681</v>
+      </c>
+      <c r="AD43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:32:33.207622Z</t>
+        </is>
+      </c>
+      <c r="AE43" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-ill-z10-2026-08-10).</t>
+        </is>
+      </c>
+      <c r="AF43" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG43" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH43" s="24" t="n"/>
+      <c r="AI43" s="31" t="n"/>
+      <c r="AJ43" s="31" t="n"/>
+      <c r="AK43" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL43" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM43" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN43" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO43" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP43" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AQ43" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AR43" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AS43" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AT43" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AU43" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AV43" s="24" t="n"/>
+      <c r="AW43" s="24" t="n"/>
+      <c r="AX43" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY43" s="24" t="n"/>
+      <c r="AZ43" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA43" s="24" t="inlineStr">
+        <is>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
+        </is>
+      </c>
+      <c r="BB43" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC43" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD43" s="24" t="inlineStr">
+        <is>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
+        </is>
+      </c>
+      <c r="BE43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG43" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:41:12.161251Z</t>
+        </is>
+      </c>
+      <c r="BI43" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ43" s="25" t="n"/>
+      <c r="BK43" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL43" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM43" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN43" s="28" t="n"/>
+      <c r="BO43" s="28" t="n"/>
+      <c r="BP43" s="25" t="n"/>
+      <c r="BQ43" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BR43" s="28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BS43" s="28" t="n"/>
+      <c r="BT43" s="28" t="n"/>
+      <c r="BU43" s="25" t="n"/>
+      <c r="BV43" s="29" t="n"/>
+      <c r="BW43" s="24" t="n"/>
+      <c r="BX43" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY43" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ43" s="24" t="n"/>
+      <c r="CA43" s="31" t="n"/>
+      <c r="CB43" s="24" t="n"/>
+      <c r="CC43" s="24" t="n"/>
+      <c r="CD43" s="24" t="n"/>
+      <c r="CE43" s="24" t="n"/>
+      <c r="CF43" s="24" t="n"/>
+      <c r="CG43" s="24" t="n"/>
+      <c r="CH43" s="24" t="n"/>
+      <c r="CI43" s="24" t="n"/>
+      <c r="CJ43" s="24" t="n"/>
+      <c r="CK43" s="24" t="n"/>
+      <c r="CL43" s="24" t="n"/>
+      <c r="CM43" s="24" t="n"/>
+      <c r="CN43" s="24" t="n"/>
+      <c r="CO43" s="24" t="n"/>
+      <c r="CP43" s="24" t="n"/>
+      <c r="CQ43" s="24" t="n"/>
+      <c r="CR43" s="24" t="n"/>
+      <c r="CS43" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>cb6d9e8e41754df2</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:41:14.399564Z</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>76981</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="H44" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L44" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M44" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N44" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O44" s="28" t="n">
+        <v>0.561717</v>
+      </c>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="28" t="n">
+        <v>-0.067913</v>
+      </c>
+      <c r="R44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U44" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V44" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W44" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="25" t="n"/>
+      <c r="Z44" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA44" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB44" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC44" s="30" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="AD44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:32:34.639724Z</t>
+        </is>
+      </c>
+      <c r="AE44" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-lynx-rae-2026-08-10).</t>
+        </is>
+      </c>
+      <c r="AF44" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG44" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH44" s="24" t="n"/>
+      <c r="AI44" s="31" t="n"/>
+      <c r="AJ44" s="31" t="n"/>
+      <c r="AK44" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL44" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM44" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN44" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO44" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP44" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AQ44" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AR44" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AS44" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AT44" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AU44" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AV44" s="24" t="n"/>
+      <c r="AW44" s="24" t="n"/>
+      <c r="AX44" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY44" s="24" t="n"/>
+      <c r="AZ44" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA44" s="24" t="inlineStr">
+        <is>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
+        </is>
+      </c>
+      <c r="BB44" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC44" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD44" s="24" t="inlineStr">
+        <is>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
+        </is>
+      </c>
+      <c r="BE44" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF44" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG44" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:41:12.712148Z</t>
+        </is>
+      </c>
+      <c r="BI44" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ44" s="25" t="n"/>
+      <c r="BK44" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL44" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM44" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN44" s="28" t="n"/>
+      <c r="BO44" s="28" t="n"/>
+      <c r="BP44" s="25" t="n"/>
+      <c r="BQ44" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR44" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BS44" s="28" t="n"/>
+      <c r="BT44" s="28" t="n"/>
+      <c r="BU44" s="25" t="n"/>
+      <c r="BV44" s="29" t="n"/>
+      <c r="BW44" s="24" t="n"/>
+      <c r="BX44" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY44" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ44" s="24" t="n"/>
+      <c r="CA44" s="31" t="n"/>
+      <c r="CB44" s="24" t="n"/>
+      <c r="CC44" s="24" t="n"/>
+      <c r="CD44" s="24" t="n"/>
+      <c r="CE44" s="24" t="n"/>
+      <c r="CF44" s="24" t="n"/>
+      <c r="CG44" s="24" t="n"/>
+      <c r="CH44" s="24" t="n"/>
+      <c r="CI44" s="24" t="n"/>
+      <c r="CJ44" s="24" t="n"/>
+      <c r="CK44" s="24" t="n"/>
+      <c r="CL44" s="24" t="n"/>
+      <c r="CM44" s="24" t="n"/>
+      <c r="CN44" s="24" t="n"/>
+      <c r="CO44" s="24" t="n"/>
+      <c r="CP44" s="24" t="n"/>
+      <c r="CQ44" s="24" t="n"/>
+      <c r="CR44" s="24" t="n"/>
+      <c r="CS44" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>e01c6da8c9ba4085</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:41:14.399564Z</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>76396</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I45" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J45" s="25" t="n"/>
+      <c r="K45" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L45" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M45" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O45" s="28" t="n">
+        <v>0.5843469999999999</v>
+      </c>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="28" t="n">
+        <v>0.08434700000000001</v>
+      </c>
+      <c r="R45" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S45" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T45" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U45" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V45" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W45" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="25" t="n"/>
+      <c r="Z45" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA45" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB45" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T13:07:44.660021Z</t>
+        </is>
+      </c>
+      <c r="AE45" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-dota2-yes-lvlup-2026-08-10).</t>
+        </is>
+      </c>
+      <c r="AF45" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG45" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH45" s="24" t="n"/>
+      <c r="AI45" s="31" t="n"/>
+      <c r="AJ45" s="31" t="n"/>
+      <c r="AK45" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL45" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM45" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN45" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO45" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP45" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AQ45" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AR45" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AS45" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AT45" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AU45" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AV45" s="24" t="n"/>
+      <c r="AW45" s="24" t="n"/>
+      <c r="AX45" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY45" s="24" t="n"/>
+      <c r="AZ45" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA45" s="24" t="inlineStr">
+        <is>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
+        </is>
+      </c>
+      <c r="BB45" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC45" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD45" s="24" t="inlineStr">
+        <is>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
+        </is>
+      </c>
+      <c r="BE45" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF45" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG45" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:41:13.718619Z</t>
+        </is>
+      </c>
+      <c r="BI45" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ45" s="25" t="n"/>
+      <c r="BK45" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL45" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM45" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN45" s="28" t="n"/>
+      <c r="BO45" s="28" t="n"/>
+      <c r="BP45" s="25" t="n"/>
+      <c r="BQ45" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR45" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BS45" s="28" t="n"/>
+      <c r="BT45" s="28" t="n"/>
+      <c r="BU45" s="25" t="n"/>
+      <c r="BV45" s="29" t="n"/>
+      <c r="BW45" s="24" t="n"/>
+      <c r="BX45" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY45" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ45" s="24" t="n"/>
+      <c r="CA45" s="31" t="n"/>
+      <c r="CB45" s="24" t="n"/>
+      <c r="CC45" s="24" t="n"/>
+      <c r="CD45" s="24" t="n"/>
+      <c r="CE45" s="24" t="n"/>
+      <c r="CF45" s="24" t="n"/>
+      <c r="CG45" s="24" t="n"/>
+      <c r="CH45" s="24" t="n"/>
+      <c r="CI45" s="24" t="n"/>
+      <c r="CJ45" s="24" t="n"/>
+      <c r="CK45" s="24" t="n"/>
+      <c r="CL45" s="24" t="n"/>
+      <c r="CM45" s="24" t="n"/>
+      <c r="CN45" s="24" t="n"/>
+      <c r="CO45" s="24" t="n"/>
+      <c r="CP45" s="24" t="n"/>
+      <c r="CQ45" s="24" t="n"/>
+      <c r="CR45" s="24" t="n"/>
+      <c r="CS45" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>a8268eb2d82d4dec</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:36:30.771344Z</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>76907</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="H46" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I46" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J46" s="25" t="n"/>
+      <c r="K46" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L46" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M46" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N46" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O46" s="28" t="n">
+        <v>0.691469</v>
+      </c>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="28" t="n">
+        <v>-0.008231</v>
+      </c>
+      <c r="R46" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="S46" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T46" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U46" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V46" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W46" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="25" t="n"/>
+      <c r="Z46" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="AA46" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB46" s="28" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="AC46" s="30" t="n">
+        <v>0.8584000000000001</v>
+      </c>
+      <c r="AD46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T13:07:46.086827Z</t>
+        </is>
+      </c>
+      <c r="AE46" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-re-navi-2026-08-10).</t>
+        </is>
+      </c>
+      <c r="AF46" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG46" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH46" s="24" t="n"/>
+      <c r="AI46" s="31" t="n"/>
+      <c r="AJ46" s="31" t="n"/>
+      <c r="AK46" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM46" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN46" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO46" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP46" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AQ46" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AR46" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AS46" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AT46" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AU46" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AV46" s="24" t="n"/>
+      <c r="AW46" s="24" t="n"/>
+      <c r="AX46" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY46" s="24" t="n"/>
+      <c r="AZ46" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA46" s="24" t="inlineStr">
+        <is>
+          <t>b55bd0eb25b8db13b26b84033d5d815ee06f77aac1fa364d04f301723e69eb8f</t>
+        </is>
+      </c>
+      <c r="BB46" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC46" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD46" s="24" t="inlineStr">
+        <is>
+          <t>b55bd0eb25b8db13b26b84033d5d815ee06f77aac1fa364d04f301723e69eb8f</t>
+        </is>
+      </c>
+      <c r="BE46" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF46" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG46" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:36:30.771106Z</t>
+        </is>
+      </c>
+      <c r="BI46" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ46" s="25" t="n"/>
+      <c r="BK46" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL46" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM46" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN46" s="28" t="n"/>
+      <c r="BO46" s="28" t="n"/>
+      <c r="BP46" s="25" t="n"/>
+      <c r="BQ46" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BR46" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BS46" s="28" t="n"/>
+      <c r="BT46" s="28" t="n"/>
+      <c r="BU46" s="25" t="n"/>
+      <c r="BV46" s="29" t="n"/>
+      <c r="BW46" s="24" t="n"/>
+      <c r="BX46" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY46" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ46" s="24" t="n"/>
+      <c r="CA46" s="31" t="n"/>
+      <c r="CB46" s="24" t="n"/>
+      <c r="CC46" s="24" t="n"/>
+      <c r="CD46" s="24" t="n"/>
+      <c r="CE46" s="24" t="n"/>
+      <c r="CF46" s="24" t="n"/>
+      <c r="CG46" s="24" t="n"/>
+      <c r="CH46" s="24" t="n"/>
+      <c r="CI46" s="24" t="n"/>
+      <c r="CJ46" s="24" t="n"/>
+      <c r="CK46" s="24" t="n"/>
+      <c r="CL46" s="24" t="n"/>
+      <c r="CM46" s="24" t="n"/>
+      <c r="CN46" s="24" t="n"/>
+      <c r="CO46" s="24" t="n"/>
+      <c r="CP46" s="24" t="n"/>
+      <c r="CQ46" s="24" t="n"/>
+      <c r="CR46" s="24" t="n"/>
+      <c r="CS46" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>3c9edd2587e84ba4</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:22:28.832657Z</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>79381</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I47" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J47" s="25" t="n"/>
+      <c r="K47" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M47" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N47" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O47" s="28" t="n">
+        <v>0.5450159999999999</v>
+      </c>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="28" t="n">
+        <v>0.094566</v>
+      </c>
+      <c r="R47" s="26" t="n">
+        <v>67</v>
+      </c>
+      <c r="S47" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U47" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V47" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y47" s="25" t="n"/>
+      <c r="Z47" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA47" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB47" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC47" s="30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:32:25.172024Z</t>
+        </is>
+      </c>
+      <c r="AE47" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lvlup-re-2026-08-12).</t>
+        </is>
+      </c>
+      <c r="AF47" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG47" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH47" s="24" t="n"/>
+      <c r="AI47" s="31" t="n"/>
+      <c r="AJ47" s="31" t="n"/>
+      <c r="AK47" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL47" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM47" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN47" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO47" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP47" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AQ47" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AR47" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AS47" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AT47" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AU47" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AV47" s="24" t="n"/>
+      <c r="AW47" s="24" t="n"/>
+      <c r="AX47" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY47" s="24" t="n"/>
+      <c r="AZ47" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA47" s="24" t="inlineStr">
+        <is>
+          <t>4806051748ca0e0e71f7a78cdec3088c19d0b8147cff09cd9e9a8b19e8dc6791</t>
+        </is>
+      </c>
+      <c r="BB47" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC47" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD47" s="24" t="inlineStr">
+        <is>
+          <t>4806051748ca0e0e71f7a78cdec3088c19d0b8147cff09cd9e9a8b19e8dc6791</t>
+        </is>
+      </c>
+      <c r="BE47" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF47" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG47" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:22:23.388322Z</t>
+        </is>
+      </c>
+      <c r="BI47" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ47" s="25" t="n"/>
+      <c r="BK47" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL47" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM47" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN47" s="28" t="n"/>
+      <c r="BO47" s="28" t="n"/>
+      <c r="BP47" s="25" t="n"/>
+      <c r="BQ47" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR47" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BS47" s="28" t="n"/>
+      <c r="BT47" s="28" t="n"/>
+      <c r="BU47" s="25" t="n"/>
+      <c r="BV47" s="29" t="n"/>
+      <c r="BW47" s="24" t="n"/>
+      <c r="BX47" s="30" t="n"/>
+      <c r="BY47" s="27" t="n"/>
+      <c r="BZ47" s="24" t="n"/>
+      <c r="CA47" s="31" t="n"/>
+      <c r="CB47" s="24" t="n"/>
+      <c r="CC47" s="24" t="n"/>
+      <c r="CD47" s="24" t="n"/>
+      <c r="CE47" s="24" t="n"/>
+      <c r="CF47" s="24" t="n"/>
+      <c r="CG47" s="24" t="n"/>
+      <c r="CH47" s="24" t="n"/>
+      <c r="CI47" s="24" t="n"/>
+      <c r="CJ47" s="24" t="n"/>
+      <c r="CK47" s="24" t="n"/>
+      <c r="CL47" s="24" t="n"/>
+      <c r="CM47" s="24" t="n"/>
+      <c r="CN47" s="24" t="n"/>
+      <c r="CO47" s="24" t="n"/>
+      <c r="CP47" s="24" t="n"/>
+      <c r="CQ47" s="24" t="n"/>
+      <c r="CR47" s="24" t="n"/>
+      <c r="CS47" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/dota2.xlsx
+++ b/data/research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS47" headerRowCount="1">
-  <autoFilter ref="A1:CS47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS48" headerRowCount="1">
+  <autoFilter ref="A1:CS48"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$47)</f>
+        <f>COUNTA('Picks'!$A$2:$A$48)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$47,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$48,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$47,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"win")+COUNTIFS('Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")+COUNTIFS('Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$47,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$48,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$47,"&gt;0",'Picks'!$V$2:$V$47,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$47,"&gt;0",'Picks'!$V$2:$V$47,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$47,"&gt;0",'Picks'!$V$2:$V$47,"win")/(COUNTIFS('Picks'!$BX$2:$BX$47,"&gt;0",'Picks'!$V$2:$V$47,"win")+COUNTIFS('Picks'!$BX$2:$BX$47,"&gt;0",'Picks'!$V$2:$V$47,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")/(COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")+COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$47)/SUM('Picks'!$BX$2:$BX$47),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$48)/SUM('Picks'!$BX$2:$BX$48),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$47)</f>
+        <f>SUM('Picks'!$BY$2:$BY$48)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$47,"&lt;&gt;",'Picks'!$AB$2:$AB$47),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$48,"&lt;&gt;",'Picks'!$AB$2:$AB$48),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$47,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$47,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$48,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$47,'Picks'!$AM$2:$AM$47,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$48,'Picks'!$AM$2:$AM$48,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$47,$A14,'Picks'!$U$2:$U$47,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$47,$A14,'Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$47,$A14,'Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$47,'Picks'!$H$2:$H$47,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$47,'Picks'!$H$2:$H$47,$A14,'Picks'!$U$2:$U$47,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$47,$A15,'Picks'!$U$2:$U$47,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$47,$A15,'Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$47,$A15,'Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$47,'Picks'!$H$2:$H$47,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$47,'Picks'!$H$2:$H$47,$A15,'Picks'!$U$2:$U$47,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$47,$A16,'Picks'!$U$2:$U$47,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$47,$A16,'Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$47,$A16,'Picks'!$U$2:$U$47,"settled",'Picks'!$V$2:$V$47,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$47,'Picks'!$H$2:$H$47,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$47,'Picks'!$H$2:$H$47,$A16,'Picks'!$U$2:$U$47,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS47"/>
+  <dimension ref="A1:CS48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15147,6 +15147,275 @@
         </is>
       </c>
     </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>b1e36d69182641ed</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:34:36.268320Z</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>77167</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="H48" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I48" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J48" s="25" t="n"/>
+      <c r="K48" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L48" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M48" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N48" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O48" s="28" t="n">
+        <v>0.738453</v>
+      </c>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="28" t="n">
+        <v>0.038753</v>
+      </c>
+      <c r="R48" s="26" t="n">
+        <v>39</v>
+      </c>
+      <c r="S48" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T48" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U48" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V48" s="24" t="n"/>
+      <c r="W48" s="26" t="n"/>
+      <c r="X48" s="26" t="n"/>
+      <c r="Y48" s="25" t="n"/>
+      <c r="Z48" s="26" t="n"/>
+      <c r="AA48" s="28" t="n"/>
+      <c r="AB48" s="28" t="n"/>
+      <c r="AC48" s="30" t="n"/>
+      <c r="AD48" s="24" t="n"/>
+      <c r="AE48" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-ts-xtreme-2026-08-13).</t>
+        </is>
+      </c>
+      <c r="AF48" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG48" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH48" s="24" t="n"/>
+      <c r="AI48" s="31" t="n"/>
+      <c r="AJ48" s="31" t="n"/>
+      <c r="AK48" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL48" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM48" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN48" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO48" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP48" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="AQ48" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="AR48" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="AS48" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="AT48" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="AU48" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="AV48" s="24" t="n"/>
+      <c r="AW48" s="24" t="n"/>
+      <c r="AX48" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY48" s="24" t="n"/>
+      <c r="AZ48" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA48" s="24" t="inlineStr">
+        <is>
+          <t>ceea9688d905d0ad390cdd3daf87ff0098fa5c01330be03572f98270d67ece12</t>
+        </is>
+      </c>
+      <c r="BB48" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC48" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD48" s="24" t="inlineStr">
+        <is>
+          <t>ceea9688d905d0ad390cdd3daf87ff0098fa5c01330be03572f98270d67ece12</t>
+        </is>
+      </c>
+      <c r="BE48" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF48" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG48" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:34:35.104443Z</t>
+        </is>
+      </c>
+      <c r="BI48" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ48" s="25" t="n"/>
+      <c r="BK48" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL48" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM48" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN48" s="28" t="n"/>
+      <c r="BO48" s="28" t="n"/>
+      <c r="BP48" s="25" t="n"/>
+      <c r="BQ48" s="27" t="n"/>
+      <c r="BR48" s="28" t="n"/>
+      <c r="BS48" s="28" t="n"/>
+      <c r="BT48" s="28" t="n"/>
+      <c r="BU48" s="25" t="n"/>
+      <c r="BV48" s="29" t="n"/>
+      <c r="BW48" s="24" t="n"/>
+      <c r="BX48" s="30" t="n"/>
+      <c r="BY48" s="27" t="n"/>
+      <c r="BZ48" s="24" t="n"/>
+      <c r="CA48" s="31" t="n"/>
+      <c r="CB48" s="24" t="n"/>
+      <c r="CC48" s="24" t="n"/>
+      <c r="CD48" s="24" t="n"/>
+      <c r="CE48" s="24" t="n"/>
+      <c r="CF48" s="24" t="n"/>
+      <c r="CG48" s="24" t="n"/>
+      <c r="CH48" s="24" t="n"/>
+      <c r="CI48" s="24" t="n"/>
+      <c r="CJ48" s="24" t="n"/>
+      <c r="CK48" s="24" t="n"/>
+      <c r="CL48" s="24" t="n"/>
+      <c r="CM48" s="24" t="n"/>
+      <c r="CN48" s="24" t="n"/>
+      <c r="CO48" s="24" t="n"/>
+      <c r="CP48" s="24" t="n"/>
+      <c r="CQ48" s="24" t="n"/>
+      <c r="CR48" s="24" t="n"/>
+      <c r="CS48" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
